--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="F14" t="n">
-        <v>5.64</v>
+        <v>5.15</v>
       </c>
       <c r="G14" t="n">
-        <v>255.7</v>
+        <v>241.6</v>
       </c>
       <c r="H14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>21.96</v>
+        <v>14.3</v>
       </c>
       <c r="K14" t="n">
-        <v>74.34999999999999</v>
+        <v>133.63</v>
       </c>
       <c r="L14" t="n">
-        <v>77.53</v>
+        <v>134.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:34:06</t>
+          <t>04:34:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.96</v>
+        <v>5.57</v>
       </c>
       <c r="G15" t="n">
-        <v>268</v>
+        <v>254.7</v>
       </c>
       <c r="H15" t="n">
-        <v>24.7</v>
+        <v>17.8</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.64</v>
+        <v>72.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.32</v>
+        <v>1.07</v>
       </c>
       <c r="L15" t="n">
-        <v>9.17</v>
+        <v>72.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:07</t>
+          <t>04:35:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="F16" t="n">
-        <v>6.02</v>
+        <v>5.24</v>
       </c>
       <c r="G16" t="n">
-        <v>239.5</v>
+        <v>241.2</v>
       </c>
       <c r="H16" t="n">
-        <v>24.8</v>
+        <v>22.5</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>86.39</v>
+        <v>-36.69</v>
       </c>
       <c r="K16" t="n">
-        <v>-96.45999999999999</v>
+        <v>30.62</v>
       </c>
       <c r="L16" t="n">
-        <v>129.5</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:48</t>
+          <t>04:40:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.41</v>
+        <v>1.43</v>
       </c>
       <c r="F17" t="n">
-        <v>5.12</v>
+        <v>5.67</v>
       </c>
       <c r="G17" t="n">
-        <v>238.7</v>
+        <v>247</v>
       </c>
       <c r="H17" t="n">
-        <v>19.5</v>
+        <v>18.4</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>127.51</v>
+        <v>-87.05</v>
       </c>
       <c r="K17" t="n">
-        <v>-152.73</v>
+        <v>-6.12</v>
       </c>
       <c r="L17" t="n">
-        <v>198.96</v>
+        <v>87.26000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:41:46</t>
+          <t>04:43:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="F18" t="n">
-        <v>5.67</v>
+        <v>5.06</v>
       </c>
       <c r="G18" t="n">
-        <v>241.9</v>
+        <v>250.9</v>
       </c>
       <c r="H18" t="n">
-        <v>24.6</v>
+        <v>25.2</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.95</v>
+        <v>-51.95</v>
       </c>
       <c r="K18" t="n">
-        <v>-43.04</v>
+        <v>-40.36</v>
       </c>
       <c r="L18" t="n">
-        <v>43.14</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:43:19</t>
+          <t>04:44:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="F19" t="n">
-        <v>5.74</v>
+        <v>5.28</v>
       </c>
       <c r="G19" t="n">
-        <v>245.6</v>
+        <v>253.4</v>
       </c>
       <c r="H19" t="n">
-        <v>23.4</v>
+        <v>27.6</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-39.71</v>
+        <v>-44.73</v>
       </c>
       <c r="K19" t="n">
-        <v>-113.89</v>
+        <v>-130.13</v>
       </c>
       <c r="L19" t="n">
-        <v>120.62</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:47:20</t>
+          <t>04:49:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="F20" t="n">
-        <v>5.69</v>
+        <v>4.95</v>
       </c>
       <c r="G20" t="n">
-        <v>256.6</v>
+        <v>253</v>
       </c>
       <c r="H20" t="n">
-        <v>20.2</v>
+        <v>30.1</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>193.65</v>
+        <v>-29.17</v>
       </c>
       <c r="K20" t="n">
-        <v>-19.1</v>
+        <v>95.67</v>
       </c>
       <c r="L20" t="n">
-        <v>194.59</v>
+        <v>100.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:49:09</t>
+          <t>04:51:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="F21" t="n">
-        <v>4.36</v>
+        <v>4.86</v>
       </c>
       <c r="G21" t="n">
-        <v>243.8</v>
+        <v>261.6</v>
       </c>
       <c r="H21" t="n">
-        <v>22.7</v>
+        <v>16.8</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>48.32</v>
+        <v>-54.85</v>
       </c>
       <c r="K21" t="n">
-        <v>-189.4</v>
+        <v>-20.9</v>
       </c>
       <c r="L21" t="n">
-        <v>195.47</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:50:50</t>
+          <t>04:53:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="F22" t="n">
-        <v>4.82</v>
+        <v>5.86</v>
       </c>
       <c r="G22" t="n">
-        <v>248.3</v>
+        <v>257.3</v>
       </c>
       <c r="H22" t="n">
-        <v>21.6</v>
+        <v>25</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>55.03</v>
+        <v>198.08</v>
       </c>
       <c r="K22" t="n">
-        <v>-68.27</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>87.69</v>
+        <v>198.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:54:13</t>
+          <t>04:57:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="F23" t="n">
-        <v>5.8</v>
+        <v>5.29</v>
       </c>
       <c r="G23" t="n">
-        <v>252.1</v>
+        <v>252.8</v>
       </c>
       <c r="H23" t="n">
-        <v>21.1</v>
+        <v>23.9</v>
       </c>
       <c r="I23" t="n">
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-267.18</v>
+        <v>150.44</v>
       </c>
       <c r="K23" t="n">
-        <v>-76.7</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>277.97</v>
+        <v>150.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:56:21</t>
+          <t>04:59:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.89</v>
+        <v>1.15</v>
       </c>
       <c r="F24" t="n">
-        <v>5.09</v>
+        <v>4.85</v>
       </c>
       <c r="G24" t="n">
-        <v>243.9</v>
+        <v>242.2</v>
       </c>
       <c r="H24" t="n">
-        <v>20.8</v>
+        <v>22</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-37.2</v>
+        <v>-95.87</v>
       </c>
       <c r="K24" t="n">
-        <v>444.85</v>
+        <v>-120.86</v>
       </c>
       <c r="L24" t="n">
-        <v>446.4</v>
+        <v>154.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:58:39</t>
+          <t>05:00:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="F25" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
       <c r="G25" t="n">
-        <v>259.9</v>
+        <v>257.8</v>
       </c>
       <c r="H25" t="n">
-        <v>20.8</v>
+        <v>26.5</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.15</v>
+        <v>-41.8</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.18</v>
+        <v>20.76</v>
       </c>
       <c r="L25" t="n">
-        <v>9.16</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:03:47</t>
+          <t>05:05:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="F26" t="n">
-        <v>5.05</v>
+        <v>5.74</v>
       </c>
       <c r="G26" t="n">
-        <v>249.3</v>
+        <v>255.6</v>
       </c>
       <c r="H26" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.300000000000001</v>
+        <v>-299.71</v>
       </c>
       <c r="K26" t="n">
-        <v>192.57</v>
+        <v>-74.31</v>
       </c>
       <c r="L26" t="n">
-        <v>192.75</v>
+        <v>308.78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:04:52</t>
+          <t>05:08:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="F27" t="n">
-        <v>5.7</v>
+        <v>5.47</v>
       </c>
       <c r="G27" t="n">
-        <v>246.9</v>
+        <v>250.7</v>
       </c>
       <c r="H27" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-41.59</v>
+        <v>-307.39</v>
       </c>
       <c r="K27" t="n">
-        <v>-26.17</v>
+        <v>-67.02</v>
       </c>
       <c r="L27" t="n">
-        <v>49.14</v>
+        <v>314.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:07:00</t>
+          <t>05:09:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="F28" t="n">
-        <v>5.63</v>
+        <v>5.65</v>
       </c>
       <c r="G28" t="n">
-        <v>254.9</v>
+        <v>253.2</v>
       </c>
       <c r="H28" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-493.5</v>
+        <v>264.2</v>
       </c>
       <c r="K28" t="n">
-        <v>218.99</v>
+        <v>291.61</v>
       </c>
       <c r="L28" t="n">
-        <v>539.91</v>
+        <v>393.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:17:17</t>
+          <t>05:20:53</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.43</v>
+        <v>1.92</v>
       </c>
       <c r="F29" t="n">
-        <v>5.11</v>
+        <v>5.61</v>
       </c>
       <c r="G29" t="n">
-        <v>242.7</v>
+        <v>265.8</v>
       </c>
       <c r="H29" t="n">
         <v>20.7</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.2</v>
+        <v>-24.23</v>
       </c>
       <c r="K29" t="n">
-        <v>50.16</v>
+        <v>61.16</v>
       </c>
       <c r="L29" t="n">
-        <v>56.59</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:18:43</t>
+          <t>05:22:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="F30" t="n">
-        <v>5.39</v>
+        <v>5.23</v>
       </c>
       <c r="G30" t="n">
-        <v>243.9</v>
+        <v>231.7</v>
       </c>
       <c r="H30" t="n">
-        <v>27.4</v>
+        <v>22.5</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>7.5</v>
+        <v>-13.74</v>
       </c>
       <c r="K30" t="n">
-        <v>-17.37</v>
+        <v>174.94</v>
       </c>
       <c r="L30" t="n">
-        <v>18.92</v>
+        <v>175.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:19:45</t>
+          <t>05:24:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="F31" t="n">
-        <v>4.89</v>
+        <v>5.37</v>
       </c>
       <c r="G31" t="n">
-        <v>240.4</v>
+        <v>246.1</v>
       </c>
       <c r="H31" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>75.73</v>
+        <v>-93.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.800000000000001</v>
+        <v>-71.54000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>76.36</v>
+        <v>117.97</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:23:15</t>
+          <t>05:28:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="F32" t="n">
-        <v>5.01</v>
+        <v>5.26</v>
       </c>
       <c r="G32" t="n">
-        <v>237.7</v>
+        <v>242.4</v>
       </c>
       <c r="H32" t="n">
-        <v>30.2</v>
+        <v>20.4</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>91.09999999999999</v>
+        <v>-7.48</v>
       </c>
       <c r="K32" t="n">
-        <v>90.88</v>
+        <v>126.59</v>
       </c>
       <c r="L32" t="n">
-        <v>128.68</v>
+        <v>126.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:25:27</t>
+          <t>05:30:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="F33" t="n">
-        <v>5.83</v>
+        <v>6.07</v>
       </c>
       <c r="G33" t="n">
-        <v>238.3</v>
+        <v>242.5</v>
       </c>
       <c r="H33" t="n">
-        <v>24.3</v>
+        <v>25.6</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>80.56</v>
+        <v>123.17</v>
       </c>
       <c r="K33" t="n">
-        <v>135.57</v>
+        <v>5.88</v>
       </c>
       <c r="L33" t="n">
-        <v>157.7</v>
+        <v>123.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:27:35</t>
+          <t>05:31:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="F34" t="n">
-        <v>5.1</v>
+        <v>5.54</v>
       </c>
       <c r="G34" t="n">
-        <v>252.8</v>
+        <v>243</v>
       </c>
       <c r="H34" t="n">
-        <v>21.9</v>
+        <v>26.6</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.39</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-60.62</v>
+        <v>173.18</v>
       </c>
       <c r="L34" t="n">
-        <v>60.96</v>
+        <v>188.52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:31:48</t>
+          <t>05:35:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="F35" t="n">
-        <v>4.66</v>
+        <v>5.13</v>
       </c>
       <c r="G35" t="n">
-        <v>227.9</v>
+        <v>233.2</v>
       </c>
       <c r="H35" t="n">
-        <v>19.6</v>
+        <v>22.3</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-144.64</v>
+        <v>-142</v>
       </c>
       <c r="K35" t="n">
-        <v>-156.18</v>
+        <v>92.39</v>
       </c>
       <c r="L35" t="n">
-        <v>212.87</v>
+        <v>169.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:32:58</t>
+          <t>05:37:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="F36" t="n">
-        <v>5.58</v>
+        <v>5.33</v>
       </c>
       <c r="G36" t="n">
-        <v>244</v>
+        <v>251.6</v>
       </c>
       <c r="H36" t="n">
-        <v>21</v>
+        <v>21.9</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>92.06</v>
+        <v>24.54</v>
       </c>
       <c r="K36" t="n">
-        <v>-21.33</v>
+        <v>-18.03</v>
       </c>
       <c r="L36" t="n">
-        <v>94.5</v>
+        <v>30.45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:35:01</t>
+          <t>05:39:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="F37" t="n">
-        <v>5.27</v>
+        <v>5.57</v>
       </c>
       <c r="G37" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H37" t="n">
-        <v>20.9</v>
+        <v>25.5</v>
       </c>
       <c r="I37" t="n">
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-179.58</v>
+        <v>-121.58</v>
       </c>
       <c r="K37" t="n">
-        <v>-194.1</v>
+        <v>-32.87</v>
       </c>
       <c r="L37" t="n">
-        <v>264.44</v>
+        <v>125.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:40:02</t>
+          <t>05:44:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="F38" t="n">
-        <v>4.64</v>
+        <v>5.19</v>
       </c>
       <c r="G38" t="n">
-        <v>247</v>
+        <v>261.2</v>
       </c>
       <c r="H38" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-74.66</v>
+        <v>-94.83</v>
       </c>
       <c r="K38" t="n">
-        <v>50.4</v>
+        <v>-166.33</v>
       </c>
       <c r="L38" t="n">
-        <v>90.08</v>
+        <v>191.46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:41:26</t>
+          <t>05:46:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="F39" t="n">
-        <v>5.32</v>
+        <v>5.49</v>
       </c>
       <c r="G39" t="n">
-        <v>251.7</v>
+        <v>251.3</v>
       </c>
       <c r="H39" t="n">
-        <v>26.8</v>
+        <v>33.6</v>
       </c>
       <c r="I39" t="n">
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>293.49</v>
+        <v>-109.29</v>
       </c>
       <c r="K39" t="n">
-        <v>392.16</v>
+        <v>172.58</v>
       </c>
       <c r="L39" t="n">
-        <v>489.82</v>
+        <v>204.27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:43:30</t>
+          <t>05:48:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="F40" t="n">
-        <v>5.54</v>
+        <v>5.84</v>
       </c>
       <c r="G40" t="n">
-        <v>248.2</v>
+        <v>246.8</v>
       </c>
       <c r="H40" t="n">
-        <v>27.4</v>
+        <v>18.1</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.67</v>
+        <v>66.42</v>
       </c>
       <c r="K40" t="n">
-        <v>-217.02</v>
+        <v>1.23</v>
       </c>
       <c r="L40" t="n">
-        <v>217.12</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:47:31</t>
+          <t>05:53:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="F41" t="n">
-        <v>5.48</v>
+        <v>4.97</v>
       </c>
       <c r="G41" t="n">
-        <v>254.8</v>
+        <v>256.2</v>
       </c>
       <c r="H41" t="n">
-        <v>27</v>
+        <v>22.4</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>86.38</v>
+        <v>-50.84</v>
       </c>
       <c r="K41" t="n">
-        <v>100.46</v>
+        <v>-266.31</v>
       </c>
       <c r="L41" t="n">
-        <v>132.49</v>
+        <v>271.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:48:30</t>
+          <t>05:55:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="F42" t="n">
-        <v>5.74</v>
+        <v>5.17</v>
       </c>
       <c r="G42" t="n">
-        <v>240.6</v>
+        <v>242.7</v>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>23.7</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-6.07</v>
+        <v>-106.36</v>
       </c>
       <c r="K42" t="n">
-        <v>272.87</v>
+        <v>240.68</v>
       </c>
       <c r="L42" t="n">
-        <v>272.93</v>
+        <v>263.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:49:28</t>
+          <t>05:57:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="F43" t="n">
-        <v>5.51</v>
+        <v>5.95</v>
       </c>
       <c r="G43" t="n">
-        <v>248</v>
+        <v>242.2</v>
       </c>
       <c r="H43" t="n">
-        <v>17.7</v>
+        <v>24.2</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-159.71</v>
+        <v>20.52</v>
       </c>
       <c r="K43" t="n">
-        <v>-308.17</v>
+        <v>623.87</v>
       </c>
       <c r="L43" t="n">
-        <v>347.1</v>
+        <v>624.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:02:06</t>
+          <t>06:08:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="F44" t="n">
-        <v>4.5</v>
+        <v>6.22</v>
       </c>
       <c r="G44" t="n">
-        <v>242.6</v>
+        <v>247</v>
       </c>
       <c r="H44" t="n">
-        <v>15.4</v>
+        <v>20.4</v>
       </c>
       <c r="I44" t="n">
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>38.03</v>
+        <v>-52.86</v>
       </c>
       <c r="K44" t="n">
-        <v>139.32</v>
+        <v>-54.82</v>
       </c>
       <c r="L44" t="n">
-        <v>144.42</v>
+        <v>76.15000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:03:32</t>
+          <t>06:10:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="F45" t="n">
-        <v>5.31</v>
+        <v>5.99</v>
       </c>
       <c r="G45" t="n">
-        <v>236.2</v>
+        <v>239.8</v>
       </c>
       <c r="H45" t="n">
-        <v>17.7</v>
+        <v>15.7</v>
       </c>
       <c r="I45" t="n">
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>13.81</v>
+        <v>3.69</v>
       </c>
       <c r="K45" t="n">
-        <v>7.26</v>
+        <v>129.71</v>
       </c>
       <c r="L45" t="n">
-        <v>15.6</v>
+        <v>129.76</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:05:56</t>
+          <t>06:12:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="F46" t="n">
-        <v>5.38</v>
+        <v>5.19</v>
       </c>
       <c r="G46" t="n">
-        <v>251</v>
+        <v>244.1</v>
       </c>
       <c r="H46" t="n">
-        <v>19.8</v>
+        <v>23.1</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>42.55</v>
+        <v>-120.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-59.5</v>
+        <v>-139.09</v>
       </c>
       <c r="L46" t="n">
-        <v>73.15000000000001</v>
+        <v>184.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:10:52</t>
+          <t>06:17:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="F47" t="n">
-        <v>5.61</v>
+        <v>5.15</v>
       </c>
       <c r="G47" t="n">
-        <v>259</v>
+        <v>262.7</v>
       </c>
       <c r="H47" t="n">
-        <v>19.6</v>
+        <v>20.3</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-34.52</v>
+        <v>119.84</v>
       </c>
       <c r="K47" t="n">
-        <v>159.1</v>
+        <v>133.05</v>
       </c>
       <c r="L47" t="n">
-        <v>162.8</v>
+        <v>179.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:11:48</t>
+          <t>06:18:39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="F48" t="n">
-        <v>5.9</v>
+        <v>5.34</v>
       </c>
       <c r="G48" t="n">
-        <v>250</v>
+        <v>247.8</v>
       </c>
       <c r="H48" t="n">
-        <v>27.2</v>
+        <v>19.6</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-122.08</v>
+        <v>-164.34</v>
       </c>
       <c r="K48" t="n">
-        <v>-40.37</v>
+        <v>-52.63</v>
       </c>
       <c r="L48" t="n">
-        <v>128.58</v>
+        <v>172.56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:13:09</t>
+          <t>06:20:29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="F49" t="n">
-        <v>5.46</v>
+        <v>5.86</v>
       </c>
       <c r="G49" t="n">
-        <v>256</v>
+        <v>243.9</v>
       </c>
       <c r="H49" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I49" t="n">
         <v>21</v>
       </c>
-      <c r="I49" t="n">
-        <v>26</v>
-      </c>
       <c r="J49" t="n">
-        <v>4.24</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>57.75</v>
+        <v>4.11</v>
       </c>
       <c r="L49" t="n">
-        <v>57.91</v>
+        <v>78.26000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:18:25</t>
+          <t>06:23:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="F50" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="G50" t="n">
-        <v>250.4</v>
+        <v>248.8</v>
       </c>
       <c r="H50" t="n">
-        <v>18.4</v>
+        <v>21.8</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>33.42</v>
+        <v>53.36</v>
       </c>
       <c r="K50" t="n">
-        <v>63.62</v>
+        <v>276.82</v>
       </c>
       <c r="L50" t="n">
-        <v>71.87</v>
+        <v>281.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:20:54</t>
+          <t>06:25:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="F51" t="n">
-        <v>5.29</v>
+        <v>5.89</v>
       </c>
       <c r="G51" t="n">
-        <v>236</v>
+        <v>264.9</v>
       </c>
       <c r="H51" t="n">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-353.85</v>
+        <v>103.44</v>
       </c>
       <c r="K51" t="n">
-        <v>185.39</v>
+        <v>-91.36</v>
       </c>
       <c r="L51" t="n">
-        <v>399.47</v>
+        <v>138.01</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:22:46</t>
+          <t>06:27:26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="F52" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="G52" t="n">
-        <v>250.2</v>
+        <v>256</v>
       </c>
       <c r="H52" t="n">
-        <v>26.1</v>
+        <v>27.7</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-17.12</v>
+        <v>-52.77</v>
       </c>
       <c r="K52" t="n">
-        <v>-233.64</v>
+        <v>-209.47</v>
       </c>
       <c r="L52" t="n">
-        <v>234.27</v>
+        <v>216.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:28:27</t>
+          <t>06:32:06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="F53" t="n">
         <v>5.12</v>
       </c>
       <c r="G53" t="n">
-        <v>241.7</v>
+        <v>244.5</v>
       </c>
       <c r="H53" t="n">
-        <v>20.5</v>
+        <v>23.8</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>219.6</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>239.06</v>
+        <v>-24.43</v>
       </c>
       <c r="L53" t="n">
-        <v>324.61</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:30:19</t>
+          <t>06:33:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="F54" t="n">
-        <v>5.24</v>
+        <v>4.68</v>
       </c>
       <c r="G54" t="n">
-        <v>261.2</v>
+        <v>237.1</v>
       </c>
       <c r="H54" t="n">
-        <v>29.1</v>
+        <v>21.5</v>
       </c>
       <c r="I54" t="n">
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.71</v>
+        <v>230.11</v>
       </c>
       <c r="K54" t="n">
-        <v>131.65</v>
+        <v>211.05</v>
       </c>
       <c r="L54" t="n">
-        <v>131.82</v>
+        <v>312.24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:32:19</t>
+          <t>06:35:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="F55" t="n">
-        <v>5.59</v>
+        <v>5.83</v>
       </c>
       <c r="G55" t="n">
-        <v>243.7</v>
+        <v>244.1</v>
       </c>
       <c r="H55" t="n">
-        <v>22.8</v>
+        <v>18</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>147.06</v>
+        <v>-166.11</v>
       </c>
       <c r="K55" t="n">
-        <v>147.52</v>
+        <v>-55.36</v>
       </c>
       <c r="L55" t="n">
-        <v>208.3</v>
+        <v>175.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:36:28</t>
+          <t>06:40:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="F56" t="n">
-        <v>5.39</v>
+        <v>5.46</v>
       </c>
       <c r="G56" t="n">
-        <v>245.3</v>
+        <v>252</v>
       </c>
       <c r="H56" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>402.23</v>
+        <v>-217.11</v>
       </c>
       <c r="K56" t="n">
-        <v>-8.789999999999999</v>
+        <v>-169.34</v>
       </c>
       <c r="L56" t="n">
-        <v>402.33</v>
+        <v>275.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:38:40</t>
+          <t>06:42:37</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="F57" t="n">
-        <v>6.09</v>
+        <v>5.41</v>
       </c>
       <c r="G57" t="n">
-        <v>254.2</v>
+        <v>237.8</v>
       </c>
       <c r="H57" t="n">
-        <v>16.2</v>
+        <v>26.5</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-23.24</v>
+        <v>-425.86</v>
       </c>
       <c r="K57" t="n">
-        <v>211.16</v>
+        <v>-69.97</v>
       </c>
       <c r="L57" t="n">
-        <v>212.44</v>
+        <v>431.57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:33</t>
+          <t>06:44:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="F58" t="n">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>229.7</v>
+        <v>254.1</v>
       </c>
       <c r="H58" t="n">
-        <v>22.3</v>
+        <v>15.7</v>
       </c>
       <c r="I58" t="n">
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>121.25</v>
+        <v>-233.61</v>
       </c>
       <c r="K58" t="n">
-        <v>-532.4</v>
+        <v>-24.02</v>
       </c>
       <c r="L58" t="n">
-        <v>546.03</v>
+        <v>234.84</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:48:19</t>
+          <t>06:56:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="F59" t="n">
-        <v>4.78</v>
+        <v>5.5</v>
       </c>
       <c r="G59" t="n">
-        <v>246.9</v>
+        <v>239.4</v>
       </c>
       <c r="H59" t="n">
-        <v>28.7</v>
+        <v>22.3</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>16.25</v>
+        <v>-91.92</v>
       </c>
       <c r="K59" t="n">
-        <v>6.75</v>
+        <v>55.71</v>
       </c>
       <c r="L59" t="n">
-        <v>17.6</v>
+        <v>107.49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:50:35</t>
+          <t>06:58:52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="F60" t="n">
-        <v>4.88</v>
+        <v>5.77</v>
       </c>
       <c r="G60" t="n">
-        <v>243</v>
+        <v>251.4</v>
       </c>
       <c r="H60" t="n">
-        <v>25.7</v>
+        <v>26.3</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-103.65</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-26.17</v>
+        <v>8.01</v>
       </c>
       <c r="L60" t="n">
-        <v>106.9</v>
+        <v>69.45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:51:37</t>
+          <t>07:00:47</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="F61" t="n">
-        <v>5.21</v>
+        <v>5.28</v>
       </c>
       <c r="G61" t="n">
-        <v>249.3</v>
+        <v>243.7</v>
       </c>
       <c r="H61" t="n">
-        <v>24.9</v>
+        <v>21.4</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>139.78</v>
+        <v>-85.33</v>
       </c>
       <c r="K61" t="n">
-        <v>-15.52</v>
+        <v>-170.64</v>
       </c>
       <c r="L61" t="n">
-        <v>140.64</v>
+        <v>190.78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:56:58</t>
+          <t>07:04:17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2</v>
+        <v>5.46</v>
       </c>
       <c r="G62" t="n">
-        <v>251.7</v>
+        <v>264</v>
       </c>
       <c r="H62" t="n">
-        <v>16.6</v>
+        <v>20.6</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-95.03</v>
+        <v>-111.74</v>
       </c>
       <c r="K62" t="n">
-        <v>28.76</v>
+        <v>0.19</v>
       </c>
       <c r="L62" t="n">
-        <v>99.28</v>
+        <v>111.74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:57:59</t>
+          <t>07:05:28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="F63" t="n">
-        <v>5.16</v>
+        <v>4.96</v>
       </c>
       <c r="G63" t="n">
-        <v>246.5</v>
+        <v>241.1</v>
       </c>
       <c r="H63" t="n">
-        <v>19.8</v>
+        <v>18.6</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>0.65</v>
+        <v>137.95</v>
       </c>
       <c r="K63" t="n">
-        <v>-75.52</v>
+        <v>15.7</v>
       </c>
       <c r="L63" t="n">
-        <v>75.53</v>
+        <v>138.84</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:00:25</t>
+          <t>07:07:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="F64" t="n">
-        <v>5.55</v>
+        <v>5.49</v>
       </c>
       <c r="G64" t="n">
-        <v>246.8</v>
+        <v>249.2</v>
       </c>
       <c r="H64" t="n">
-        <v>24.1</v>
+        <v>19.3</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>71.37</v>
+        <v>-53.45</v>
       </c>
       <c r="K64" t="n">
-        <v>133.08</v>
+        <v>-58.75</v>
       </c>
       <c r="L64" t="n">
-        <v>151.01</v>
+        <v>79.43000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:05:34</t>
+          <t>07:10:53</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="F65" t="n">
-        <v>5.31</v>
+        <v>5.3</v>
       </c>
       <c r="G65" t="n">
-        <v>249.7</v>
+        <v>244</v>
       </c>
       <c r="H65" t="n">
-        <v>23.5</v>
+        <v>22.1</v>
       </c>
       <c r="I65" t="n">
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-79.47</v>
+        <v>-24.27</v>
       </c>
       <c r="K65" t="n">
-        <v>-12.36</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>80.43000000000001</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:07:40</t>
+          <t>07:12:48</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="F66" t="n">
-        <v>5.49</v>
+        <v>5.12</v>
       </c>
       <c r="G66" t="n">
-        <v>249</v>
+        <v>246.3</v>
       </c>
       <c r="H66" t="n">
-        <v>16.7</v>
+        <v>22.5</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>163.73</v>
+        <v>-226.86</v>
       </c>
       <c r="K66" t="n">
-        <v>-46.51</v>
+        <v>195.01</v>
       </c>
       <c r="L66" t="n">
-        <v>170.21</v>
+        <v>299.16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:09:29</t>
+          <t>07:13:50</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="F67" t="n">
-        <v>5.76</v>
+        <v>4.89</v>
       </c>
       <c r="G67" t="n">
-        <v>254</v>
+        <v>241.5</v>
       </c>
       <c r="H67" t="n">
-        <v>18.6</v>
+        <v>20.4</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-27.42</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-67.76000000000001</v>
+        <v>-84.98999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>73.09999999999999</v>
+        <v>125.56</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:15:14</t>
+          <t>07:18:33</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="F68" t="n">
-        <v>5.16</v>
+        <v>5.23</v>
       </c>
       <c r="G68" t="n">
-        <v>244.9</v>
+        <v>258.1</v>
       </c>
       <c r="H68" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I68" t="n">
         <v>22</v>
       </c>
-      <c r="I68" t="n">
-        <v>25</v>
-      </c>
       <c r="J68" t="n">
-        <v>198.69</v>
+        <v>-120.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-48.79</v>
+        <v>-505.2</v>
       </c>
       <c r="L68" t="n">
-        <v>204.59</v>
+        <v>519.4400000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:17:27</t>
+          <t>07:20:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="F69" t="n">
-        <v>4.92</v>
+        <v>4.65</v>
       </c>
       <c r="G69" t="n">
-        <v>252.8</v>
+        <v>230.1</v>
       </c>
       <c r="H69" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-76.54000000000001</v>
+        <v>82.44</v>
       </c>
       <c r="K69" t="n">
-        <v>193</v>
+        <v>-193.5</v>
       </c>
       <c r="L69" t="n">
-        <v>207.63</v>
+        <v>210.33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:18:35</t>
+          <t>07:22:45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="F70" t="n">
-        <v>4.92</v>
+        <v>5.24</v>
       </c>
       <c r="G70" t="n">
-        <v>251.9</v>
+        <v>232.8</v>
       </c>
       <c r="H70" t="n">
-        <v>23.2</v>
+        <v>18.4</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>283.66</v>
+        <v>86.23</v>
       </c>
       <c r="K70" t="n">
-        <v>68.08</v>
+        <v>133.43</v>
       </c>
       <c r="L70" t="n">
-        <v>291.71</v>
+        <v>158.87</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:23:54</t>
+          <t>07:28:13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,13 +3019,13 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="F71" t="n">
-        <v>5.33</v>
+        <v>5.04</v>
       </c>
       <c r="G71" t="n">
-        <v>251</v>
+        <v>247.1</v>
       </c>
       <c r="H71" t="n">
         <v>22.9</v>
@@ -3034,19 +3034,19 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>111.75</v>
+        <v>257.29</v>
       </c>
       <c r="K71" t="n">
-        <v>-94.79000000000001</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>146.54</v>
+        <v>266.83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:25:11</t>
+          <t>07:29:50</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="F72" t="n">
-        <v>5.72</v>
+        <v>4.99</v>
       </c>
       <c r="G72" t="n">
-        <v>258</v>
+        <v>245.4</v>
       </c>
       <c r="H72" t="n">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>66.67</v>
+        <v>-216.57</v>
       </c>
       <c r="K72" t="n">
-        <v>151.86</v>
+        <v>-280.55</v>
       </c>
       <c r="L72" t="n">
-        <v>165.85</v>
+        <v>354.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:26:42</t>
+          <t>07:31:56</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.63</v>
+        <v>2.06</v>
       </c>
       <c r="F73" t="n">
-        <v>4.32</v>
+        <v>5.11</v>
       </c>
       <c r="G73" t="n">
-        <v>246</v>
+        <v>243.5</v>
       </c>
       <c r="H73" t="n">
-        <v>15.2</v>
+        <v>26</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-321.15</v>
+        <v>-384</v>
       </c>
       <c r="K73" t="n">
-        <v>1.29</v>
+        <v>41.37</v>
       </c>
       <c r="L73" t="n">
-        <v>321.15</v>
+        <v>386.22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:34:39</t>
+          <t>07:43:37</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="F74" t="n">
-        <v>4.84</v>
+        <v>4.66</v>
       </c>
       <c r="G74" t="n">
-        <v>251</v>
+        <v>252.1</v>
       </c>
       <c r="H74" t="n">
-        <v>19.6</v>
+        <v>25.4</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-15.88</v>
+        <v>56.98</v>
       </c>
       <c r="K74" t="n">
-        <v>-33.09</v>
+        <v>-70.89</v>
       </c>
       <c r="L74" t="n">
-        <v>36.7</v>
+        <v>90.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:36:50</t>
+          <t>07:44:46</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="F75" t="n">
-        <v>4.83</v>
+        <v>5.16</v>
       </c>
       <c r="G75" t="n">
-        <v>231.8</v>
+        <v>251.8</v>
       </c>
       <c r="H75" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>57.5</v>
+        <v>-76.05</v>
       </c>
       <c r="K75" t="n">
-        <v>-39.07</v>
+        <v>13.57</v>
       </c>
       <c r="L75" t="n">
-        <v>69.51000000000001</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:38:53</t>
+          <t>07:46:11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="F76" t="n">
-        <v>5.2</v>
+        <v>4.74</v>
       </c>
       <c r="G76" t="n">
-        <v>245.7</v>
+        <v>249.3</v>
       </c>
       <c r="H76" t="n">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
       <c r="I76" t="n">
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.97</v>
+        <v>13.98</v>
       </c>
       <c r="K76" t="n">
-        <v>98.37</v>
+        <v>-32.11</v>
       </c>
       <c r="L76" t="n">
-        <v>102</v>
+        <v>35.02</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:44:07</t>
+          <t>07:50:39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="F77" t="n">
-        <v>5.23</v>
+        <v>5.55</v>
       </c>
       <c r="G77" t="n">
-        <v>249.7</v>
+        <v>258</v>
       </c>
       <c r="H77" t="n">
-        <v>27.3</v>
+        <v>23.8</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>105.29</v>
+        <v>-55.27</v>
       </c>
       <c r="K77" t="n">
-        <v>108.51</v>
+        <v>-18.52</v>
       </c>
       <c r="L77" t="n">
-        <v>151.2</v>
+        <v>58.29</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:44:50</t>
+          <t>07:51:36</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="F78" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="G78" t="n">
-        <v>254.3</v>
+        <v>249.8</v>
       </c>
       <c r="H78" t="n">
-        <v>23.2</v>
+        <v>26.4</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>164.06</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-41.72</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>169.28</v>
+        <v>106.04</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:47:05</t>
+          <t>07:53:33</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.67</v>
+        <v>2.01</v>
       </c>
       <c r="F79" t="n">
-        <v>5.37</v>
+        <v>5.42</v>
       </c>
       <c r="G79" t="n">
-        <v>240.6</v>
+        <v>250.4</v>
       </c>
       <c r="H79" t="n">
-        <v>28.7</v>
+        <v>19.6</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-80.27</v>
+        <v>39.77</v>
       </c>
       <c r="K79" t="n">
-        <v>-120.93</v>
+        <v>-110.79</v>
       </c>
       <c r="L79" t="n">
-        <v>145.14</v>
+        <v>117.71</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:52:48</t>
+          <t>07:57:17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="F80" t="n">
-        <v>5.62</v>
+        <v>5.33</v>
       </c>
       <c r="G80" t="n">
-        <v>250.2</v>
+        <v>249.5</v>
       </c>
       <c r="H80" t="n">
-        <v>20.9</v>
+        <v>20.3</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>56.73</v>
+        <v>73.83</v>
       </c>
       <c r="K80" t="n">
-        <v>170.54</v>
+        <v>-109.51</v>
       </c>
       <c r="L80" t="n">
-        <v>179.73</v>
+        <v>132.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:54:45</t>
+          <t>07:58:09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.72</v>
+        <v>2.29</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="G81" t="n">
-        <v>240.9</v>
+        <v>239.4</v>
       </c>
       <c r="H81" t="n">
-        <v>31.1</v>
+        <v>31.9</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>23.81</v>
+        <v>-60.58</v>
       </c>
       <c r="K81" t="n">
-        <v>168.9</v>
+        <v>-184.31</v>
       </c>
       <c r="L81" t="n">
-        <v>170.57</v>
+        <v>194.01</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:57:00</t>
+          <t>08:00:38</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="F82" t="n">
-        <v>5.94</v>
+        <v>5.41</v>
       </c>
       <c r="G82" t="n">
-        <v>251.6</v>
+        <v>256.3</v>
       </c>
       <c r="H82" t="n">
-        <v>20.9</v>
+        <v>25.8</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-17.97</v>
+        <v>-246.63</v>
       </c>
       <c r="K82" t="n">
-        <v>52.22</v>
+        <v>-115.39</v>
       </c>
       <c r="L82" t="n">
-        <v>55.22</v>
+        <v>272.29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:02:37</t>
+          <t>08:05:42</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,31 +3526,31 @@
         <v>1.87</v>
       </c>
       <c r="F83" t="n">
-        <v>5.28</v>
+        <v>5.03</v>
       </c>
       <c r="G83" t="n">
-        <v>237.5</v>
+        <v>242.4</v>
       </c>
       <c r="H83" t="n">
-        <v>19.1</v>
+        <v>28.4</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>259.99</v>
+        <v>-128.45</v>
       </c>
       <c r="K83" t="n">
-        <v>-188.84</v>
+        <v>222.14</v>
       </c>
       <c r="L83" t="n">
-        <v>321.33</v>
+        <v>256.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:04:22</t>
+          <t>08:07:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="F84" t="n">
-        <v>5.82</v>
+        <v>4.86</v>
       </c>
       <c r="G84" t="n">
-        <v>248.5</v>
+        <v>249.2</v>
       </c>
       <c r="H84" t="n">
-        <v>22.7</v>
+        <v>16.5</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>118.82</v>
+        <v>-130</v>
       </c>
       <c r="K84" t="n">
-        <v>-348.49</v>
+        <v>-129.91</v>
       </c>
       <c r="L84" t="n">
-        <v>368.19</v>
+        <v>183.78</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:05:42</t>
+          <t>08:09:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="F85" t="n">
-        <v>4.82</v>
+        <v>5.22</v>
       </c>
       <c r="G85" t="n">
-        <v>233.4</v>
+        <v>254.3</v>
       </c>
       <c r="H85" t="n">
-        <v>24.9</v>
+        <v>19.7</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-45.81</v>
+        <v>-191.72</v>
       </c>
       <c r="K85" t="n">
-        <v>303.14</v>
+        <v>-57.76</v>
       </c>
       <c r="L85" t="n">
-        <v>306.58</v>
+        <v>200.23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:11:00</t>
+          <t>08:14:40</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="F86" t="n">
-        <v>4.81</v>
+        <v>5.11</v>
       </c>
       <c r="G86" t="n">
-        <v>235.7</v>
+        <v>256.2</v>
       </c>
       <c r="H86" t="n">
-        <v>19.1</v>
+        <v>18.6</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-266.43</v>
+        <v>-205.72</v>
       </c>
       <c r="K86" t="n">
-        <v>45.74</v>
+        <v>362.08</v>
       </c>
       <c r="L86" t="n">
-        <v>270.33</v>
+        <v>416.44</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:12:47</t>
+          <t>08:16:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.17</v>
+        <v>1.82</v>
       </c>
       <c r="F87" t="n">
-        <v>5.84</v>
+        <v>5.37</v>
       </c>
       <c r="G87" t="n">
-        <v>254.7</v>
+        <v>260</v>
       </c>
       <c r="H87" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="I87" t="n">
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-130.95</v>
+        <v>-110.93</v>
       </c>
       <c r="K87" t="n">
-        <v>-108.12</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>169.82</v>
+        <v>133.89</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:14:22</t>
+          <t>08:19:21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="F88" t="n">
-        <v>5.39</v>
+        <v>5.63</v>
       </c>
       <c r="G88" t="n">
-        <v>253</v>
+        <v>242.4</v>
       </c>
       <c r="H88" t="n">
-        <v>22.1</v>
+        <v>16.6</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>305.04</v>
+        <v>138.57</v>
       </c>
       <c r="K88" t="n">
-        <v>302.89</v>
+        <v>132.04</v>
       </c>
       <c r="L88" t="n">
-        <v>429.87</v>
+        <v>191.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>14.3</v>
+        <v>10.92</v>
       </c>
       <c r="K14" t="n">
-        <v>133.63</v>
+        <v>102.04</v>
       </c>
       <c r="L14" t="n">
-        <v>134.39</v>
+        <v>102.63</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>72.11</v>
+        <v>62.37</v>
       </c>
       <c r="K15" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="L15" t="n">
-        <v>72.12</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-36.69</v>
+        <v>-40.16</v>
       </c>
       <c r="K16" t="n">
-        <v>30.62</v>
+        <v>33.52</v>
       </c>
       <c r="L16" t="n">
-        <v>47.79</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-87.05</v>
+        <v>-85.98999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.12</v>
+        <v>-6.04</v>
       </c>
       <c r="L17" t="n">
-        <v>87.26000000000001</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-51.95</v>
+        <v>-63.05</v>
       </c>
       <c r="K18" t="n">
-        <v>-40.36</v>
+        <v>-48.98</v>
       </c>
       <c r="L18" t="n">
-        <v>65.79000000000001</v>
+        <v>79.84</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-44.73</v>
+        <v>-39.07</v>
       </c>
       <c r="K19" t="n">
-        <v>-130.13</v>
+        <v>-113.66</v>
       </c>
       <c r="L19" t="n">
-        <v>137.6</v>
+        <v>120.19</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-29.17</v>
+        <v>-33</v>
       </c>
       <c r="K20" t="n">
-        <v>95.67</v>
+        <v>108.23</v>
       </c>
       <c r="L20" t="n">
-        <v>100.02</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-54.85</v>
+        <v>-75.17</v>
       </c>
       <c r="K21" t="n">
-        <v>-20.9</v>
+        <v>-28.65</v>
       </c>
       <c r="L21" t="n">
-        <v>58.69</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>198.08</v>
+        <v>192.9</v>
       </c>
       <c r="K22" t="n">
-        <v>9.970000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>198.33</v>
+        <v>193.14</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>150.44</v>
+        <v>203.58</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.140000000000001</v>
+        <v>-11.02</v>
       </c>
       <c r="L23" t="n">
-        <v>150.66</v>
+        <v>203.88</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-95.87</v>
+        <v>-133.85</v>
       </c>
       <c r="K24" t="n">
-        <v>-120.86</v>
+        <v>-168.74</v>
       </c>
       <c r="L24" t="n">
-        <v>154.27</v>
+        <v>215.38</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-41.8</v>
+        <v>-92.94</v>
       </c>
       <c r="K25" t="n">
-        <v>20.76</v>
+        <v>46.15</v>
       </c>
       <c r="L25" t="n">
-        <v>46.67</v>
+        <v>103.77</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-299.71</v>
+        <v>-340.55</v>
       </c>
       <c r="K26" t="n">
-        <v>-74.31</v>
+        <v>-84.43000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>308.78</v>
+        <v>350.86</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-307.39</v>
+        <v>-399.57</v>
       </c>
       <c r="K27" t="n">
-        <v>-67.02</v>
+        <v>-87.12</v>
       </c>
       <c r="L27" t="n">
-        <v>314.62</v>
+        <v>408.96</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>264.2</v>
+        <v>305.65</v>
       </c>
       <c r="K28" t="n">
-        <v>291.61</v>
+        <v>337.36</v>
       </c>
       <c r="L28" t="n">
-        <v>393.5</v>
+        <v>455.24</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.23</v>
+        <v>-21.63</v>
       </c>
       <c r="K29" t="n">
-        <v>61.16</v>
+        <v>54.6</v>
       </c>
       <c r="L29" t="n">
-        <v>65.79000000000001</v>
+        <v>58.73</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.74</v>
+        <v>-8.17</v>
       </c>
       <c r="K30" t="n">
-        <v>174.94</v>
+        <v>104.04</v>
       </c>
       <c r="L30" t="n">
-        <v>175.48</v>
+        <v>104.36</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-93.8</v>
+        <v>-67.34999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-71.54000000000001</v>
+        <v>-51.37</v>
       </c>
       <c r="L31" t="n">
-        <v>117.97</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.48</v>
+        <v>-5.9</v>
       </c>
       <c r="K32" t="n">
-        <v>126.59</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>126.81</v>
+        <v>100.02</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>123.17</v>
+        <v>94.75</v>
       </c>
       <c r="K33" t="n">
-        <v>5.88</v>
+        <v>4.52</v>
       </c>
       <c r="L33" t="n">
-        <v>123.31</v>
+        <v>94.86</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-74.48999999999999</v>
+        <v>-56.34</v>
       </c>
       <c r="K34" t="n">
-        <v>173.18</v>
+        <v>130.98</v>
       </c>
       <c r="L34" t="n">
-        <v>188.52</v>
+        <v>142.58</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-142</v>
+        <v>-139.38</v>
       </c>
       <c r="K35" t="n">
-        <v>92.39</v>
+        <v>90.69</v>
       </c>
       <c r="L35" t="n">
-        <v>169.41</v>
+        <v>166.29</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>24.54</v>
+        <v>61.17</v>
       </c>
       <c r="K36" t="n">
-        <v>-18.03</v>
+        <v>-44.94</v>
       </c>
       <c r="L36" t="n">
-        <v>30.45</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-121.58</v>
+        <v>-139.6</v>
       </c>
       <c r="K37" t="n">
-        <v>-32.87</v>
+        <v>-37.74</v>
       </c>
       <c r="L37" t="n">
-        <v>125.94</v>
+        <v>144.62</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-94.83</v>
+        <v>-92.55</v>
       </c>
       <c r="K38" t="n">
-        <v>-166.33</v>
+        <v>-162.34</v>
       </c>
       <c r="L38" t="n">
-        <v>191.46</v>
+        <v>186.87</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-109.29</v>
+        <v>-134.16</v>
       </c>
       <c r="K39" t="n">
-        <v>172.58</v>
+        <v>211.86</v>
       </c>
       <c r="L39" t="n">
-        <v>204.27</v>
+        <v>250.77</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>66.42</v>
+        <v>119.08</v>
       </c>
       <c r="K40" t="n">
-        <v>1.23</v>
+        <v>2.2</v>
       </c>
       <c r="L40" t="n">
-        <v>66.44</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-50.84</v>
+        <v>-59.86</v>
       </c>
       <c r="K41" t="n">
-        <v>-266.31</v>
+        <v>-313.59</v>
       </c>
       <c r="L41" t="n">
-        <v>271.12</v>
+        <v>319.25</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-106.36</v>
+        <v>-139.58</v>
       </c>
       <c r="K42" t="n">
-        <v>240.68</v>
+        <v>315.86</v>
       </c>
       <c r="L42" t="n">
-        <v>263.14</v>
+        <v>345.32</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>20.52</v>
+        <v>20.21</v>
       </c>
       <c r="K43" t="n">
-        <v>623.87</v>
+        <v>614.41</v>
       </c>
       <c r="L43" t="n">
-        <v>624.21</v>
+        <v>614.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-52.86</v>
+        <v>-44.28</v>
       </c>
       <c r="K44" t="n">
-        <v>-54.82</v>
+        <v>-45.93</v>
       </c>
       <c r="L44" t="n">
-        <v>76.15000000000001</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>3.69</v>
+        <v>2.52</v>
       </c>
       <c r="K45" t="n">
-        <v>129.71</v>
+        <v>88.66</v>
       </c>
       <c r="L45" t="n">
-        <v>129.76</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-120.98</v>
+        <v>-82.39</v>
       </c>
       <c r="K46" t="n">
-        <v>-139.09</v>
+        <v>-94.72</v>
       </c>
       <c r="L46" t="n">
-        <v>184.34</v>
+        <v>125.54</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>119.84</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>133.05</v>
+        <v>104.71</v>
       </c>
       <c r="L47" t="n">
-        <v>179.06</v>
+        <v>140.93</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-164.34</v>
+        <v>-140.02</v>
       </c>
       <c r="K48" t="n">
-        <v>-52.63</v>
+        <v>-44.84</v>
       </c>
       <c r="L48" t="n">
-        <v>172.56</v>
+        <v>147.03</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>78.15000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="K49" t="n">
-        <v>4.11</v>
+        <v>4.67</v>
       </c>
       <c r="L49" t="n">
-        <v>78.26000000000001</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>53.36</v>
+        <v>43.76</v>
       </c>
       <c r="K50" t="n">
-        <v>276.82</v>
+        <v>227.04</v>
       </c>
       <c r="L50" t="n">
-        <v>281.91</v>
+        <v>231.21</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>103.44</v>
+        <v>117.47</v>
       </c>
       <c r="K51" t="n">
-        <v>-91.36</v>
+        <v>-103.75</v>
       </c>
       <c r="L51" t="n">
-        <v>138.01</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-52.77</v>
+        <v>-46.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-209.47</v>
+        <v>-185.33</v>
       </c>
       <c r="L52" t="n">
-        <v>216.01</v>
+        <v>191.12</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>83.98999999999999</v>
+        <v>147.75</v>
       </c>
       <c r="K53" t="n">
-        <v>-24.43</v>
+        <v>-42.98</v>
       </c>
       <c r="L53" t="n">
-        <v>87.47</v>
+        <v>153.88</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>230.11</v>
+        <v>205.23</v>
       </c>
       <c r="K54" t="n">
-        <v>211.05</v>
+        <v>188.23</v>
       </c>
       <c r="L54" t="n">
-        <v>312.24</v>
+        <v>278.48</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-166.11</v>
+        <v>-184.68</v>
       </c>
       <c r="K55" t="n">
-        <v>-55.36</v>
+        <v>-61.55</v>
       </c>
       <c r="L55" t="n">
-        <v>175.09</v>
+        <v>194.66</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-217.11</v>
+        <v>-275.81</v>
       </c>
       <c r="K56" t="n">
-        <v>-169.34</v>
+        <v>-215.12</v>
       </c>
       <c r="L56" t="n">
-        <v>275.34</v>
+        <v>349.78</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-425.86</v>
+        <v>-412.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-69.97</v>
+        <v>-67.8</v>
       </c>
       <c r="L57" t="n">
-        <v>431.57</v>
+        <v>418.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-233.61</v>
+        <v>-293.69</v>
       </c>
       <c r="K58" t="n">
-        <v>-24.02</v>
+        <v>-30.2</v>
       </c>
       <c r="L58" t="n">
-        <v>234.84</v>
+        <v>295.24</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-91.92</v>
+        <v>-67.09</v>
       </c>
       <c r="K59" t="n">
-        <v>55.71</v>
+        <v>40.66</v>
       </c>
       <c r="L59" t="n">
-        <v>107.49</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>68.98999999999999</v>
+        <v>63.46</v>
       </c>
       <c r="K60" t="n">
-        <v>8.01</v>
+        <v>7.37</v>
       </c>
       <c r="L60" t="n">
-        <v>69.45</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-85.33</v>
+        <v>-61.69</v>
       </c>
       <c r="K61" t="n">
-        <v>-170.64</v>
+        <v>-123.37</v>
       </c>
       <c r="L61" t="n">
-        <v>190.78</v>
+        <v>137.94</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-111.74</v>
+        <v>-91.91</v>
       </c>
       <c r="K62" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="L62" t="n">
-        <v>111.74</v>
+        <v>91.91</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>137.95</v>
+        <v>102.02</v>
       </c>
       <c r="K63" t="n">
-        <v>15.7</v>
+        <v>11.61</v>
       </c>
       <c r="L63" t="n">
-        <v>138.84</v>
+        <v>102.68</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-53.45</v>
+        <v>-47.58</v>
       </c>
       <c r="K64" t="n">
-        <v>-58.75</v>
+        <v>-52.29</v>
       </c>
       <c r="L64" t="n">
-        <v>79.43000000000001</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-24.27</v>
+        <v>-33.79</v>
       </c>
       <c r="K65" t="n">
-        <v>66.29000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="L65" t="n">
-        <v>70.59</v>
+        <v>98.29000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-226.86</v>
+        <v>-200.01</v>
       </c>
       <c r="K66" t="n">
-        <v>195.01</v>
+        <v>171.93</v>
       </c>
       <c r="L66" t="n">
-        <v>299.16</v>
+        <v>263.75</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>92.43000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="K67" t="n">
-        <v>-84.98999999999999</v>
+        <v>-95.67</v>
       </c>
       <c r="L67" t="n">
-        <v>125.56</v>
+        <v>141.34</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-120.81</v>
+        <v>-106.17</v>
       </c>
       <c r="K68" t="n">
-        <v>-505.2</v>
+        <v>-443.97</v>
       </c>
       <c r="L68" t="n">
-        <v>519.4400000000001</v>
+        <v>456.49</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>82.44</v>
+        <v>84.98</v>
       </c>
       <c r="K69" t="n">
-        <v>-193.5</v>
+        <v>-199.47</v>
       </c>
       <c r="L69" t="n">
-        <v>210.33</v>
+        <v>216.82</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>86.23</v>
+        <v>100.87</v>
       </c>
       <c r="K70" t="n">
-        <v>133.43</v>
+        <v>156.08</v>
       </c>
       <c r="L70" t="n">
-        <v>158.87</v>
+        <v>185.83</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>257.29</v>
+        <v>321.91</v>
       </c>
       <c r="K71" t="n">
-        <v>70.70999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>266.83</v>
+        <v>333.85</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-216.57</v>
+        <v>-268.79</v>
       </c>
       <c r="K72" t="n">
-        <v>-280.55</v>
+        <v>-348.19</v>
       </c>
       <c r="L72" t="n">
-        <v>354.41</v>
+        <v>439.87</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-384</v>
+        <v>-367.18</v>
       </c>
       <c r="K73" t="n">
-        <v>41.37</v>
+        <v>39.56</v>
       </c>
       <c r="L73" t="n">
-        <v>386.22</v>
+        <v>369.3</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>56.98</v>
+        <v>44.92</v>
       </c>
       <c r="K74" t="n">
-        <v>-70.89</v>
+        <v>-55.88</v>
       </c>
       <c r="L74" t="n">
-        <v>90.95</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-76.05</v>
+        <v>-66.11</v>
       </c>
       <c r="K75" t="n">
-        <v>13.57</v>
+        <v>11.8</v>
       </c>
       <c r="L75" t="n">
-        <v>77.25</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>13.98</v>
+        <v>18.4</v>
       </c>
       <c r="K76" t="n">
-        <v>-32.11</v>
+        <v>-42.28</v>
       </c>
       <c r="L76" t="n">
-        <v>35.02</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-55.27</v>
+        <v>-56.4</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.52</v>
+        <v>-18.89</v>
       </c>
       <c r="L77" t="n">
-        <v>58.29</v>
+        <v>59.48</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>69.01000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="K78" t="n">
-        <v>80.51000000000001</v>
+        <v>64.33</v>
       </c>
       <c r="L78" t="n">
-        <v>106.04</v>
+        <v>84.72</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>39.77</v>
+        <v>33.04</v>
       </c>
       <c r="K79" t="n">
-        <v>-110.79</v>
+        <v>-92.04000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>117.71</v>
+        <v>97.79000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>73.83</v>
+        <v>84.02</v>
       </c>
       <c r="K80" t="n">
-        <v>-109.51</v>
+        <v>-124.63</v>
       </c>
       <c r="L80" t="n">
-        <v>132.08</v>
+        <v>150.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-60.58</v>
+        <v>-51.21</v>
       </c>
       <c r="K81" t="n">
-        <v>-184.31</v>
+        <v>-155.81</v>
       </c>
       <c r="L81" t="n">
-        <v>194.01</v>
+        <v>164.01</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-246.63</v>
+        <v>-217.12</v>
       </c>
       <c r="K82" t="n">
-        <v>-115.39</v>
+        <v>-101.58</v>
       </c>
       <c r="L82" t="n">
-        <v>272.29</v>
+        <v>239.71</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-128.45</v>
+        <v>-120.15</v>
       </c>
       <c r="K83" t="n">
-        <v>222.14</v>
+        <v>207.8</v>
       </c>
       <c r="L83" t="n">
-        <v>256.6</v>
+        <v>240.04</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-130</v>
+        <v>-145.58</v>
       </c>
       <c r="K84" t="n">
-        <v>-129.91</v>
+        <v>-145.49</v>
       </c>
       <c r="L84" t="n">
-        <v>183.78</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-191.72</v>
+        <v>-233.59</v>
       </c>
       <c r="K85" t="n">
-        <v>-57.76</v>
+        <v>-70.38</v>
       </c>
       <c r="L85" t="n">
-        <v>200.23</v>
+        <v>243.96</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-205.72</v>
+        <v>-240.02</v>
       </c>
       <c r="K86" t="n">
-        <v>362.08</v>
+        <v>422.45</v>
       </c>
       <c r="L86" t="n">
-        <v>416.44</v>
+        <v>485.88</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-110.93</v>
+        <v>-196.55</v>
       </c>
       <c r="K87" t="n">
-        <v>74.95999999999999</v>
+        <v>132.81</v>
       </c>
       <c r="L87" t="n">
-        <v>133.89</v>
+        <v>237.21</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>138.57</v>
+        <v>178.63</v>
       </c>
       <c r="K88" t="n">
-        <v>132.04</v>
+        <v>170.22</v>
       </c>
       <c r="L88" t="n">
-        <v>191.41</v>
+        <v>246.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>10.92</v>
+        <v>9.4</v>
       </c>
       <c r="K14" t="n">
-        <v>102.04</v>
+        <v>87.83</v>
       </c>
       <c r="L14" t="n">
-        <v>102.63</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>62.37</v>
+        <v>53.33</v>
       </c>
       <c r="K15" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="L15" t="n">
-        <v>62.38</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.16</v>
+        <v>-31.98</v>
       </c>
       <c r="K16" t="n">
-        <v>33.52</v>
+        <v>26.7</v>
       </c>
       <c r="L16" t="n">
-        <v>52.31</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-85.98999999999999</v>
+        <v>-68.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.04</v>
+        <v>-4.79</v>
       </c>
       <c r="L17" t="n">
-        <v>86.2</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-63.05</v>
+        <v>-47.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-48.98</v>
+        <v>-36.92</v>
       </c>
       <c r="L18" t="n">
-        <v>79.84</v>
+        <v>60.17</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-39.07</v>
+        <v>-29.45</v>
       </c>
       <c r="K19" t="n">
-        <v>-113.66</v>
+        <v>-85.7</v>
       </c>
       <c r="L19" t="n">
-        <v>120.19</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-33</v>
+        <v>-23.81</v>
       </c>
       <c r="K20" t="n">
-        <v>108.23</v>
+        <v>78.09</v>
       </c>
       <c r="L20" t="n">
-        <v>113.15</v>
+        <v>81.64</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-75.17</v>
+        <v>-63.02</v>
       </c>
       <c r="K21" t="n">
-        <v>-28.65</v>
+        <v>-24.01</v>
       </c>
       <c r="L21" t="n">
-        <v>80.45</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>192.9</v>
+        <v>125.64</v>
       </c>
       <c r="K22" t="n">
-        <v>9.710000000000001</v>
+        <v>6.32</v>
       </c>
       <c r="L22" t="n">
-        <v>193.14</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>203.58</v>
+        <v>109.01</v>
       </c>
       <c r="K23" t="n">
-        <v>-11.02</v>
+        <v>-5.9</v>
       </c>
       <c r="L23" t="n">
-        <v>203.88</v>
+        <v>109.17</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-133.85</v>
+        <v>-71.95</v>
       </c>
       <c r="K24" t="n">
-        <v>-168.74</v>
+        <v>-90.70999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>215.38</v>
+        <v>115.78</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-92.94</v>
+        <v>-59.13</v>
       </c>
       <c r="K25" t="n">
-        <v>46.15</v>
+        <v>29.36</v>
       </c>
       <c r="L25" t="n">
-        <v>103.77</v>
+        <v>66.02</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-340.55</v>
+        <v>-192.28</v>
       </c>
       <c r="K26" t="n">
-        <v>-84.43000000000001</v>
+        <v>-47.67</v>
       </c>
       <c r="L26" t="n">
-        <v>350.86</v>
+        <v>198.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-399.57</v>
+        <v>-198.66</v>
       </c>
       <c r="K27" t="n">
-        <v>-87.12</v>
+        <v>-43.32</v>
       </c>
       <c r="L27" t="n">
-        <v>408.96</v>
+        <v>203.32</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>305.65</v>
+        <v>155.85</v>
       </c>
       <c r="K28" t="n">
-        <v>337.36</v>
+        <v>172.02</v>
       </c>
       <c r="L28" t="n">
-        <v>455.24</v>
+        <v>232.12</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-21.63</v>
+        <v>-18.54</v>
       </c>
       <c r="K29" t="n">
-        <v>54.6</v>
+        <v>46.79</v>
       </c>
       <c r="L29" t="n">
-        <v>58.73</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.17</v>
+        <v>-7.91</v>
       </c>
       <c r="K30" t="n">
-        <v>104.04</v>
+        <v>100.75</v>
       </c>
       <c r="L30" t="n">
-        <v>104.36</v>
+        <v>101.06</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-67.34999999999999</v>
+        <v>-59.71</v>
       </c>
       <c r="K31" t="n">
-        <v>-51.37</v>
+        <v>-45.54</v>
       </c>
       <c r="L31" t="n">
-        <v>84.7</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.9</v>
+        <v>-5.14</v>
       </c>
       <c r="K32" t="n">
-        <v>99.84999999999999</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>100.02</v>
+        <v>87.17</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>94.75</v>
+        <v>86.67</v>
       </c>
       <c r="K33" t="n">
-        <v>4.52</v>
+        <v>4.13</v>
       </c>
       <c r="L33" t="n">
-        <v>94.86</v>
+        <v>86.77</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-56.34</v>
+        <v>-45.41</v>
       </c>
       <c r="K34" t="n">
-        <v>130.98</v>
+        <v>105.56</v>
       </c>
       <c r="L34" t="n">
-        <v>142.58</v>
+        <v>114.91</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-139.38</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>90.69</v>
+        <v>60.58</v>
       </c>
       <c r="L35" t="n">
-        <v>166.29</v>
+        <v>111.07</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>61.17</v>
+        <v>41.02</v>
       </c>
       <c r="K36" t="n">
-        <v>-44.94</v>
+        <v>-30.13</v>
       </c>
       <c r="L36" t="n">
-        <v>75.90000000000001</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-139.6</v>
+        <v>-91.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-37.74</v>
+        <v>-24.66</v>
       </c>
       <c r="L37" t="n">
-        <v>144.62</v>
+        <v>94.48999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-92.55</v>
+        <v>-64.3</v>
       </c>
       <c r="K38" t="n">
-        <v>-162.34</v>
+        <v>-112.78</v>
       </c>
       <c r="L38" t="n">
-        <v>186.87</v>
+        <v>129.82</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-134.16</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>211.86</v>
+        <v>113.53</v>
       </c>
       <c r="L39" t="n">
-        <v>250.77</v>
+        <v>134.38</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>119.08</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="L40" t="n">
-        <v>119.1</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-59.86</v>
+        <v>-34.54</v>
       </c>
       <c r="K41" t="n">
-        <v>-313.59</v>
+        <v>-180.93</v>
       </c>
       <c r="L41" t="n">
-        <v>319.25</v>
+        <v>184.2</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-139.58</v>
+        <v>-73.70999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>315.86</v>
+        <v>166.8</v>
       </c>
       <c r="L42" t="n">
-        <v>345.32</v>
+        <v>182.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>20.21</v>
+        <v>10.65</v>
       </c>
       <c r="K43" t="n">
-        <v>614.41</v>
+        <v>323.61</v>
       </c>
       <c r="L43" t="n">
-        <v>614.74</v>
+        <v>323.79</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-44.28</v>
+        <v>-39.41</v>
       </c>
       <c r="K44" t="n">
-        <v>-45.93</v>
+        <v>-40.88</v>
       </c>
       <c r="L44" t="n">
-        <v>63.8</v>
+        <v>56.78</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="K45" t="n">
-        <v>88.66</v>
+        <v>80.14</v>
       </c>
       <c r="L45" t="n">
-        <v>88.7</v>
+        <v>80.18000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-82.39</v>
+        <v>-70.38</v>
       </c>
       <c r="K46" t="n">
-        <v>-94.72</v>
+        <v>-80.91</v>
       </c>
       <c r="L46" t="n">
-        <v>125.54</v>
+        <v>107.24</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>94.31999999999999</v>
+        <v>75.09</v>
       </c>
       <c r="K47" t="n">
-        <v>104.71</v>
+        <v>83.37</v>
       </c>
       <c r="L47" t="n">
-        <v>140.93</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-140.02</v>
+        <v>-103.38</v>
       </c>
       <c r="K48" t="n">
-        <v>-44.84</v>
+        <v>-33.11</v>
       </c>
       <c r="L48" t="n">
-        <v>147.03</v>
+        <v>108.55</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>88.7</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>4.67</v>
+        <v>3.44</v>
       </c>
       <c r="L49" t="n">
-        <v>88.83</v>
+        <v>65.52</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>43.76</v>
+        <v>30.18</v>
       </c>
       <c r="K50" t="n">
-        <v>227.04</v>
+        <v>156.59</v>
       </c>
       <c r="L50" t="n">
-        <v>231.21</v>
+        <v>159.47</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>117.47</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-103.75</v>
+        <v>-65</v>
       </c>
       <c r="L51" t="n">
-        <v>156.73</v>
+        <v>98.19</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-46.69</v>
+        <v>-32.25</v>
       </c>
       <c r="K52" t="n">
-        <v>-185.33</v>
+        <v>-128.01</v>
       </c>
       <c r="L52" t="n">
-        <v>191.12</v>
+        <v>132.01</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>147.75</v>
+        <v>84.3</v>
       </c>
       <c r="K53" t="n">
-        <v>-42.98</v>
+        <v>-24.52</v>
       </c>
       <c r="L53" t="n">
-        <v>153.88</v>
+        <v>87.79000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>205.23</v>
+        <v>130.86</v>
       </c>
       <c r="K54" t="n">
-        <v>188.23</v>
+        <v>120.03</v>
       </c>
       <c r="L54" t="n">
-        <v>278.48</v>
+        <v>177.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-184.68</v>
+        <v>-117.39</v>
       </c>
       <c r="K55" t="n">
-        <v>-61.55</v>
+        <v>-39.12</v>
       </c>
       <c r="L55" t="n">
-        <v>194.66</v>
+        <v>123.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-275.81</v>
+        <v>-147.68</v>
       </c>
       <c r="K56" t="n">
-        <v>-215.12</v>
+        <v>-115.18</v>
       </c>
       <c r="L56" t="n">
-        <v>349.78</v>
+        <v>187.29</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-412.65</v>
+        <v>-252.92</v>
       </c>
       <c r="K57" t="n">
-        <v>-67.8</v>
+        <v>-41.56</v>
       </c>
       <c r="L57" t="n">
-        <v>418.19</v>
+        <v>256.31</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-293.69</v>
+        <v>-174.48</v>
       </c>
       <c r="K58" t="n">
-        <v>-30.2</v>
+        <v>-17.94</v>
       </c>
       <c r="L58" t="n">
-        <v>295.24</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-67.09</v>
+        <v>-59.59</v>
       </c>
       <c r="K59" t="n">
-        <v>40.66</v>
+        <v>36.12</v>
       </c>
       <c r="L59" t="n">
-        <v>78.45</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>63.46</v>
+        <v>50.48</v>
       </c>
       <c r="K60" t="n">
-        <v>7.37</v>
+        <v>5.86</v>
       </c>
       <c r="L60" t="n">
-        <v>63.89</v>
+        <v>50.82</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-61.69</v>
+        <v>-53.39</v>
       </c>
       <c r="K61" t="n">
-        <v>-123.37</v>
+        <v>-106.77</v>
       </c>
       <c r="L61" t="n">
-        <v>137.94</v>
+        <v>119.37</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-91.91</v>
+        <v>-80.69</v>
       </c>
       <c r="K62" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="L62" t="n">
-        <v>91.91</v>
+        <v>80.69</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>102.02</v>
+        <v>97.52</v>
       </c>
       <c r="K63" t="n">
-        <v>11.61</v>
+        <v>11.1</v>
       </c>
       <c r="L63" t="n">
-        <v>102.68</v>
+        <v>98.15000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-47.58</v>
+        <v>-43.08</v>
       </c>
       <c r="K64" t="n">
-        <v>-52.29</v>
+        <v>-47.35</v>
       </c>
       <c r="L64" t="n">
-        <v>70.69</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-33.79</v>
+        <v>-24.96</v>
       </c>
       <c r="K65" t="n">
-        <v>92.3</v>
+        <v>68.2</v>
       </c>
       <c r="L65" t="n">
-        <v>98.29000000000001</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-200.01</v>
+        <v>-125.54</v>
       </c>
       <c r="K66" t="n">
-        <v>171.93</v>
+        <v>107.92</v>
       </c>
       <c r="L66" t="n">
-        <v>263.75</v>
+        <v>165.55</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>104.04</v>
+        <v>67.55</v>
       </c>
       <c r="K67" t="n">
-        <v>-95.67</v>
+        <v>-62.12</v>
       </c>
       <c r="L67" t="n">
-        <v>141.34</v>
+        <v>91.77</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-106.17</v>
+        <v>-61.23</v>
       </c>
       <c r="K68" t="n">
-        <v>-443.97</v>
+        <v>-256.06</v>
       </c>
       <c r="L68" t="n">
-        <v>456.49</v>
+        <v>263.28</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>84.98</v>
+        <v>54.02</v>
       </c>
       <c r="K69" t="n">
-        <v>-199.47</v>
+        <v>-126.79</v>
       </c>
       <c r="L69" t="n">
-        <v>216.82</v>
+        <v>137.82</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>100.87</v>
+        <v>61.66</v>
       </c>
       <c r="K70" t="n">
-        <v>156.08</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>185.83</v>
+        <v>113.59</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>321.91</v>
+        <v>175.64</v>
       </c>
       <c r="K71" t="n">
-        <v>88.45999999999999</v>
+        <v>48.27</v>
       </c>
       <c r="L71" t="n">
-        <v>333.85</v>
+        <v>182.15</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-268.79</v>
+        <v>-133.22</v>
       </c>
       <c r="K72" t="n">
-        <v>-348.19</v>
+        <v>-172.58</v>
       </c>
       <c r="L72" t="n">
-        <v>439.87</v>
+        <v>218.02</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-367.18</v>
+        <v>-235.33</v>
       </c>
       <c r="K73" t="n">
-        <v>39.56</v>
+        <v>25.35</v>
       </c>
       <c r="L73" t="n">
-        <v>369.3</v>
+        <v>236.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>44.92</v>
+        <v>38.36</v>
       </c>
       <c r="K74" t="n">
-        <v>-55.88</v>
+        <v>-47.72</v>
       </c>
       <c r="L74" t="n">
-        <v>71.7</v>
+        <v>61.22</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-66.11</v>
+        <v>-53.49</v>
       </c>
       <c r="K75" t="n">
-        <v>11.8</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>67.15000000000001</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>18.4</v>
+        <v>14.17</v>
       </c>
       <c r="K76" t="n">
-        <v>-42.28</v>
+        <v>-32.55</v>
       </c>
       <c r="L76" t="n">
-        <v>46.11</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-56.4</v>
+        <v>-51.02</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.89</v>
+        <v>-17.09</v>
       </c>
       <c r="L77" t="n">
-        <v>59.48</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>55.13</v>
+        <v>49.91</v>
       </c>
       <c r="K78" t="n">
-        <v>64.33</v>
+        <v>58.23</v>
       </c>
       <c r="L78" t="n">
-        <v>84.72</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>33.04</v>
+        <v>28.61</v>
       </c>
       <c r="K79" t="n">
-        <v>-92.04000000000001</v>
+        <v>-79.7</v>
       </c>
       <c r="L79" t="n">
-        <v>97.79000000000001</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>84.02</v>
+        <v>52.64</v>
       </c>
       <c r="K80" t="n">
-        <v>-124.63</v>
+        <v>-78.08</v>
       </c>
       <c r="L80" t="n">
-        <v>150.31</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-51.21</v>
+        <v>-41.85</v>
       </c>
       <c r="K81" t="n">
-        <v>-155.81</v>
+        <v>-127.32</v>
       </c>
       <c r="L81" t="n">
-        <v>164.01</v>
+        <v>134.02</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-217.12</v>
+        <v>-144.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-101.58</v>
+        <v>-67.62</v>
       </c>
       <c r="L82" t="n">
-        <v>239.71</v>
+        <v>159.56</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-120.15</v>
+        <v>-76.93000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>207.8</v>
+        <v>133.05</v>
       </c>
       <c r="L83" t="n">
-        <v>240.04</v>
+        <v>153.69</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-145.58</v>
+        <v>-98.56999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-145.49</v>
+        <v>-98.5</v>
       </c>
       <c r="L84" t="n">
-        <v>205.82</v>
+        <v>139.35</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-233.59</v>
+        <v>-147.89</v>
       </c>
       <c r="K85" t="n">
-        <v>-70.38</v>
+        <v>-44.56</v>
       </c>
       <c r="L85" t="n">
-        <v>243.96</v>
+        <v>154.46</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-240.02</v>
+        <v>-124.68</v>
       </c>
       <c r="K86" t="n">
-        <v>422.45</v>
+        <v>219.44</v>
       </c>
       <c r="L86" t="n">
-        <v>485.88</v>
+        <v>252.39</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-196.55</v>
+        <v>-103.32</v>
       </c>
       <c r="K87" t="n">
-        <v>132.81</v>
+        <v>69.81</v>
       </c>
       <c r="L87" t="n">
-        <v>237.21</v>
+        <v>124.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>178.63</v>
+        <v>114.62</v>
       </c>
       <c r="K88" t="n">
-        <v>170.22</v>
+        <v>109.23</v>
       </c>
       <c r="L88" t="n">
-        <v>246.75</v>
+        <v>158.33</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>9.4</v>
+        <v>8.66</v>
       </c>
       <c r="K14" t="n">
-        <v>87.83</v>
+        <v>80.95</v>
       </c>
       <c r="L14" t="n">
-        <v>88.33</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>53.33</v>
+        <v>49.55</v>
       </c>
       <c r="K15" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="L15" t="n">
-        <v>53.34</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-31.98</v>
+        <v>-30.28</v>
       </c>
       <c r="K16" t="n">
-        <v>26.7</v>
+        <v>25.28</v>
       </c>
       <c r="L16" t="n">
-        <v>41.66</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-68.2</v>
+        <v>-65.53</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.79</v>
+        <v>-4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>68.37</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-47.52</v>
+        <v>-46.92</v>
       </c>
       <c r="K18" t="n">
-        <v>-36.92</v>
+        <v>-36.45</v>
       </c>
       <c r="L18" t="n">
-        <v>60.17</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-29.45</v>
+        <v>-28.93</v>
       </c>
       <c r="K19" t="n">
-        <v>-85.7</v>
+        <v>-84.18000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>90.62</v>
+        <v>89.02</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-23.81</v>
+        <v>-24.42</v>
       </c>
       <c r="K20" t="n">
-        <v>78.09</v>
+        <v>80.11</v>
       </c>
       <c r="L20" t="n">
-        <v>81.64</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-63.02</v>
+        <v>-62.74</v>
       </c>
       <c r="K21" t="n">
-        <v>-24.01</v>
+        <v>-23.91</v>
       </c>
       <c r="L21" t="n">
-        <v>67.44</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>125.64</v>
+        <v>129.85</v>
       </c>
       <c r="K22" t="n">
-        <v>6.32</v>
+        <v>6.54</v>
       </c>
       <c r="L22" t="n">
-        <v>125.8</v>
+        <v>130.02</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>109.01</v>
+        <v>117.22</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.9</v>
+        <v>-6.35</v>
       </c>
       <c r="L23" t="n">
-        <v>109.17</v>
+        <v>117.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-71.95</v>
+        <v>-77.20999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-90.70999999999999</v>
+        <v>-97.34</v>
       </c>
       <c r="L24" t="n">
-        <v>115.78</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-59.13</v>
+        <v>-62.29</v>
       </c>
       <c r="K25" t="n">
-        <v>29.36</v>
+        <v>30.93</v>
       </c>
       <c r="L25" t="n">
-        <v>66.02</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-192.28</v>
+        <v>-204.1</v>
       </c>
       <c r="K26" t="n">
-        <v>-47.67</v>
+        <v>-50.6</v>
       </c>
       <c r="L26" t="n">
-        <v>198.1</v>
+        <v>210.28</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-198.66</v>
+        <v>-215.65</v>
       </c>
       <c r="K27" t="n">
-        <v>-43.32</v>
+        <v>-47.02</v>
       </c>
       <c r="L27" t="n">
-        <v>203.32</v>
+        <v>220.71</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>155.85</v>
+        <v>168.04</v>
       </c>
       <c r="K28" t="n">
-        <v>172.02</v>
+        <v>185.47</v>
       </c>
       <c r="L28" t="n">
-        <v>232.12</v>
+        <v>250.27</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-18.54</v>
+        <v>-17.52</v>
       </c>
       <c r="K29" t="n">
-        <v>46.79</v>
+        <v>44.22</v>
       </c>
       <c r="L29" t="n">
-        <v>50.33</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.91</v>
+        <v>-7.38</v>
       </c>
       <c r="K30" t="n">
-        <v>100.75</v>
+        <v>93.97</v>
       </c>
       <c r="L30" t="n">
-        <v>101.06</v>
+        <v>94.25</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-59.71</v>
+        <v>-56.89</v>
       </c>
       <c r="K31" t="n">
-        <v>-45.54</v>
+        <v>-43.39</v>
       </c>
       <c r="L31" t="n">
-        <v>75.09999999999999</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.14</v>
+        <v>-4.89</v>
       </c>
       <c r="K32" t="n">
-        <v>87.01000000000001</v>
+        <v>82.84</v>
       </c>
       <c r="L32" t="n">
-        <v>87.17</v>
+        <v>82.98</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>86.67</v>
+        <v>82.56</v>
       </c>
       <c r="K33" t="n">
-        <v>4.13</v>
+        <v>3.94</v>
       </c>
       <c r="L33" t="n">
-        <v>86.77</v>
+        <v>82.65000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-45.41</v>
+        <v>-44.1</v>
       </c>
       <c r="K34" t="n">
-        <v>105.56</v>
+        <v>102.53</v>
       </c>
       <c r="L34" t="n">
-        <v>114.91</v>
+        <v>111.61</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-93.09999999999999</v>
+        <v>-95.40000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>60.58</v>
+        <v>62.07</v>
       </c>
       <c r="L35" t="n">
-        <v>111.07</v>
+        <v>113.81</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>41.02</v>
+        <v>42.01</v>
       </c>
       <c r="K36" t="n">
-        <v>-30.13</v>
+        <v>-30.86</v>
       </c>
       <c r="L36" t="n">
-        <v>50.9</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-91.22</v>
+        <v>-94.34999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-24.66</v>
+        <v>-25.51</v>
       </c>
       <c r="L37" t="n">
-        <v>94.48999999999999</v>
+        <v>97.73</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-64.3</v>
+        <v>-66.77</v>
       </c>
       <c r="K38" t="n">
-        <v>-112.78</v>
+        <v>-117.11</v>
       </c>
       <c r="L38" t="n">
-        <v>129.82</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-71.90000000000001</v>
+        <v>-78.40000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>113.53</v>
+        <v>123.81</v>
       </c>
       <c r="L39" t="n">
-        <v>134.38</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>75.79000000000001</v>
+        <v>78.89</v>
       </c>
       <c r="K40" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="L40" t="n">
-        <v>75.81</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-34.54</v>
+        <v>-36.63</v>
       </c>
       <c r="K41" t="n">
-        <v>-180.93</v>
+        <v>-191.89</v>
       </c>
       <c r="L41" t="n">
-        <v>184.2</v>
+        <v>195.35</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-73.70999999999999</v>
+        <v>-79.39</v>
       </c>
       <c r="K42" t="n">
-        <v>166.8</v>
+        <v>179.67</v>
       </c>
       <c r="L42" t="n">
-        <v>182.36</v>
+        <v>196.43</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>10.65</v>
+        <v>11.45</v>
       </c>
       <c r="K43" t="n">
-        <v>323.61</v>
+        <v>347.99</v>
       </c>
       <c r="L43" t="n">
-        <v>323.79</v>
+        <v>348.18</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-39.41</v>
+        <v>-36.45</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.88</v>
+        <v>-37.8</v>
       </c>
       <c r="L44" t="n">
-        <v>56.78</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="K45" t="n">
-        <v>80.14</v>
+        <v>74.81</v>
       </c>
       <c r="L45" t="n">
-        <v>80.18000000000001</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-70.38</v>
+        <v>-67.7</v>
       </c>
       <c r="K46" t="n">
-        <v>-80.91</v>
+        <v>-77.83</v>
       </c>
       <c r="L46" t="n">
-        <v>107.24</v>
+        <v>103.15</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>75.09</v>
+        <v>72.88</v>
       </c>
       <c r="K47" t="n">
-        <v>83.37</v>
+        <v>80.91</v>
       </c>
       <c r="L47" t="n">
-        <v>112.2</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-103.38</v>
+        <v>-100.65</v>
       </c>
       <c r="K48" t="n">
-        <v>-33.11</v>
+        <v>-32.23</v>
       </c>
       <c r="L48" t="n">
-        <v>108.55</v>
+        <v>105.69</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>65.43000000000001</v>
+        <v>63.92</v>
       </c>
       <c r="K49" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="L49" t="n">
-        <v>65.52</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>30.18</v>
+        <v>30.75</v>
       </c>
       <c r="K50" t="n">
-        <v>156.59</v>
+        <v>159.55</v>
       </c>
       <c r="L50" t="n">
-        <v>159.47</v>
+        <v>162.48</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>73.59999999999999</v>
+        <v>76.13</v>
       </c>
       <c r="K51" t="n">
-        <v>-65</v>
+        <v>-67.23999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>98.19</v>
+        <v>101.57</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-32.25</v>
+        <v>-33.14</v>
       </c>
       <c r="K52" t="n">
-        <v>-128.01</v>
+        <v>-131.55</v>
       </c>
       <c r="L52" t="n">
-        <v>132.01</v>
+        <v>135.66</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>84.3</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-24.52</v>
+        <v>-26.12</v>
       </c>
       <c r="L53" t="n">
-        <v>87.79000000000001</v>
+        <v>93.54000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>130.86</v>
+        <v>136.79</v>
       </c>
       <c r="K54" t="n">
-        <v>120.03</v>
+        <v>125.46</v>
       </c>
       <c r="L54" t="n">
-        <v>177.57</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-117.39</v>
+        <v>-122.13</v>
       </c>
       <c r="K55" t="n">
-        <v>-39.12</v>
+        <v>-40.71</v>
       </c>
       <c r="L55" t="n">
-        <v>123.73</v>
+        <v>128.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-147.68</v>
+        <v>-158.49</v>
       </c>
       <c r="K56" t="n">
-        <v>-115.18</v>
+        <v>-123.62</v>
       </c>
       <c r="L56" t="n">
-        <v>187.29</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-252.92</v>
+        <v>-267.75</v>
       </c>
       <c r="K57" t="n">
-        <v>-41.56</v>
+        <v>-44</v>
       </c>
       <c r="L57" t="n">
-        <v>256.31</v>
+        <v>271.34</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-174.48</v>
+        <v>-182.94</v>
       </c>
       <c r="K58" t="n">
-        <v>-17.94</v>
+        <v>-18.81</v>
       </c>
       <c r="L58" t="n">
-        <v>175.4</v>
+        <v>183.91</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-59.59</v>
+        <v>-55.52</v>
       </c>
       <c r="K59" t="n">
-        <v>36.12</v>
+        <v>33.65</v>
       </c>
       <c r="L59" t="n">
-        <v>69.68000000000001</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>50.48</v>
+        <v>48.2</v>
       </c>
       <c r="K60" t="n">
-        <v>5.86</v>
+        <v>5.6</v>
       </c>
       <c r="L60" t="n">
-        <v>50.82</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-53.39</v>
+        <v>-50.75</v>
       </c>
       <c r="K61" t="n">
-        <v>-106.77</v>
+        <v>-101.5</v>
       </c>
       <c r="L61" t="n">
-        <v>119.37</v>
+        <v>113.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-80.69</v>
+        <v>-76.72</v>
       </c>
       <c r="K62" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="L62" t="n">
-        <v>80.69</v>
+        <v>76.72</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>97.52</v>
+        <v>92.97</v>
       </c>
       <c r="K63" t="n">
-        <v>11.1</v>
+        <v>10.58</v>
       </c>
       <c r="L63" t="n">
-        <v>98.15000000000001</v>
+        <v>93.56999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-43.08</v>
+        <v>-40.75</v>
       </c>
       <c r="K64" t="n">
-        <v>-47.35</v>
+        <v>-44.79</v>
       </c>
       <c r="L64" t="n">
-        <v>64.01000000000001</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-24.96</v>
+        <v>-25.45</v>
       </c>
       <c r="K65" t="n">
-        <v>68.2</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>72.62</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-125.54</v>
+        <v>-129.88</v>
       </c>
       <c r="K66" t="n">
-        <v>107.92</v>
+        <v>111.65</v>
       </c>
       <c r="L66" t="n">
-        <v>165.55</v>
+        <v>171.27</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>67.55</v>
+        <v>69.36</v>
       </c>
       <c r="K67" t="n">
-        <v>-62.12</v>
+        <v>-63.77</v>
       </c>
       <c r="L67" t="n">
-        <v>91.77</v>
+        <v>94.22</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-61.23</v>
+        <v>-65.19</v>
       </c>
       <c r="K68" t="n">
-        <v>-256.06</v>
+        <v>-272.63</v>
       </c>
       <c r="L68" t="n">
-        <v>263.28</v>
+        <v>280.32</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>54.02</v>
+        <v>56.47</v>
       </c>
       <c r="K69" t="n">
-        <v>-126.79</v>
+        <v>-132.54</v>
       </c>
       <c r="L69" t="n">
-        <v>137.82</v>
+        <v>144.07</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>61.66</v>
+        <v>64.52</v>
       </c>
       <c r="K70" t="n">
-        <v>95.40000000000001</v>
+        <v>99.83</v>
       </c>
       <c r="L70" t="n">
-        <v>113.59</v>
+        <v>118.87</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>175.64</v>
+        <v>187.94</v>
       </c>
       <c r="K71" t="n">
-        <v>48.27</v>
+        <v>51.65</v>
       </c>
       <c r="L71" t="n">
-        <v>182.15</v>
+        <v>194.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-133.22</v>
+        <v>-144.27</v>
       </c>
       <c r="K72" t="n">
-        <v>-172.58</v>
+        <v>-186.89</v>
       </c>
       <c r="L72" t="n">
-        <v>218.02</v>
+        <v>236.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-235.33</v>
+        <v>-247.85</v>
       </c>
       <c r="K73" t="n">
-        <v>25.35</v>
+        <v>26.7</v>
       </c>
       <c r="L73" t="n">
-        <v>236.7</v>
+        <v>249.28</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>38.36</v>
+        <v>36.14</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.72</v>
+        <v>-44.96</v>
       </c>
       <c r="L74" t="n">
-        <v>61.22</v>
+        <v>57.69</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-53.49</v>
+        <v>-51.33</v>
       </c>
       <c r="K75" t="n">
-        <v>9.539999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="L75" t="n">
-        <v>54.33</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>14.17</v>
+        <v>13.54</v>
       </c>
       <c r="K76" t="n">
-        <v>-32.55</v>
+        <v>-31.11</v>
       </c>
       <c r="L76" t="n">
-        <v>35.5</v>
+        <v>33.93</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-51.02</v>
+        <v>-48.59</v>
       </c>
       <c r="K77" t="n">
-        <v>-17.09</v>
+        <v>-16.28</v>
       </c>
       <c r="L77" t="n">
-        <v>53.81</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>49.91</v>
+        <v>47.75</v>
       </c>
       <c r="K78" t="n">
-        <v>58.23</v>
+        <v>55.71</v>
       </c>
       <c r="L78" t="n">
-        <v>76.7</v>
+        <v>73.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>28.61</v>
+        <v>27.51</v>
       </c>
       <c r="K79" t="n">
-        <v>-79.7</v>
+        <v>-76.63</v>
       </c>
       <c r="L79" t="n">
-        <v>84.68000000000001</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>52.64</v>
+        <v>54.29</v>
       </c>
       <c r="K80" t="n">
-        <v>-78.08</v>
+        <v>-80.53</v>
       </c>
       <c r="L80" t="n">
-        <v>94.17</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-41.85</v>
+        <v>-42.58</v>
       </c>
       <c r="K81" t="n">
-        <v>-127.32</v>
+        <v>-129.56</v>
       </c>
       <c r="L81" t="n">
-        <v>134.02</v>
+        <v>136.37</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-144.52</v>
+        <v>-150.23</v>
       </c>
       <c r="K82" t="n">
-        <v>-67.62</v>
+        <v>-70.29000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>159.56</v>
+        <v>165.86</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-76.93000000000001</v>
+        <v>-81.20999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>133.05</v>
+        <v>140.44</v>
       </c>
       <c r="L83" t="n">
-        <v>153.69</v>
+        <v>162.23</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-98.56999999999999</v>
+        <v>-101.36</v>
       </c>
       <c r="K84" t="n">
-        <v>-98.5</v>
+        <v>-101.29</v>
       </c>
       <c r="L84" t="n">
-        <v>139.35</v>
+        <v>143.3</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-147.89</v>
+        <v>-153.11</v>
       </c>
       <c r="K85" t="n">
-        <v>-44.56</v>
+        <v>-46.13</v>
       </c>
       <c r="L85" t="n">
-        <v>154.46</v>
+        <v>159.91</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-124.68</v>
+        <v>-133.59</v>
       </c>
       <c r="K86" t="n">
-        <v>219.44</v>
+        <v>235.12</v>
       </c>
       <c r="L86" t="n">
-        <v>252.39</v>
+        <v>270.42</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-103.32</v>
+        <v>-110.79</v>
       </c>
       <c r="K87" t="n">
-        <v>69.81</v>
+        <v>74.86</v>
       </c>
       <c r="L87" t="n">
-        <v>124.7</v>
+        <v>133.71</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>114.62</v>
+        <v>118.81</v>
       </c>
       <c r="K88" t="n">
-        <v>109.23</v>
+        <v>113.22</v>
       </c>
       <c r="L88" t="n">
-        <v>158.33</v>
+        <v>164.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>8.66</v>
+        <v>6.5</v>
       </c>
       <c r="K14" t="n">
-        <v>80.95</v>
+        <v>60.71</v>
       </c>
       <c r="L14" t="n">
-        <v>81.41</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>49.55</v>
+        <v>37.16</v>
       </c>
       <c r="K15" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="L15" t="n">
-        <v>49.56</v>
+        <v>37.17</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-30.28</v>
+        <v>-22.71</v>
       </c>
       <c r="K16" t="n">
-        <v>25.28</v>
+        <v>18.96</v>
       </c>
       <c r="L16" t="n">
-        <v>39.45</v>
+        <v>29.58</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-65.53</v>
+        <v>-49.15</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.6</v>
+        <v>-3.45</v>
       </c>
       <c r="L17" t="n">
-        <v>65.69</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-46.92</v>
+        <v>-33.76</v>
       </c>
       <c r="K18" t="n">
-        <v>-36.45</v>
+        <v>-26.22</v>
       </c>
       <c r="L18" t="n">
-        <v>59.42</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-28.93</v>
+        <v>-21.7</v>
       </c>
       <c r="K19" t="n">
-        <v>-84.18000000000001</v>
+        <v>-63.14</v>
       </c>
       <c r="L19" t="n">
-        <v>89.02</v>
+        <v>66.76000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-24.42</v>
+        <v>-18.32</v>
       </c>
       <c r="K20" t="n">
-        <v>80.11</v>
+        <v>60.08</v>
       </c>
       <c r="L20" t="n">
-        <v>83.75</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-62.74</v>
+        <v>-42.7</v>
       </c>
       <c r="K21" t="n">
-        <v>-23.91</v>
+        <v>-16.27</v>
       </c>
       <c r="L21" t="n">
-        <v>67.14</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>129.85</v>
+        <v>97.39</v>
       </c>
       <c r="K22" t="n">
-        <v>6.54</v>
+        <v>4.9</v>
       </c>
       <c r="L22" t="n">
-        <v>130.02</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>117.22</v>
+        <v>87.92</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.35</v>
+        <v>-4.76</v>
       </c>
       <c r="L23" t="n">
-        <v>117.39</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-77.20999999999999</v>
+        <v>-57.91</v>
       </c>
       <c r="K24" t="n">
-        <v>-97.34</v>
+        <v>-73.01000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>124.25</v>
+        <v>93.19</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-62.29</v>
+        <v>-36.88</v>
       </c>
       <c r="K25" t="n">
-        <v>30.93</v>
+        <v>18.31</v>
       </c>
       <c r="L25" t="n">
-        <v>69.54000000000001</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-204.1</v>
+        <v>-153.08</v>
       </c>
       <c r="K26" t="n">
-        <v>-50.6</v>
+        <v>-37.95</v>
       </c>
       <c r="L26" t="n">
-        <v>210.28</v>
+        <v>157.71</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-215.65</v>
+        <v>-161.73</v>
       </c>
       <c r="K27" t="n">
-        <v>-47.02</v>
+        <v>-35.26</v>
       </c>
       <c r="L27" t="n">
-        <v>220.71</v>
+        <v>165.53</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>168.04</v>
+        <v>126.03</v>
       </c>
       <c r="K28" t="n">
-        <v>185.47</v>
+        <v>139.1</v>
       </c>
       <c r="L28" t="n">
-        <v>250.27</v>
+        <v>187.71</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-17.52</v>
+        <v>-12.8</v>
       </c>
       <c r="K29" t="n">
-        <v>44.22</v>
+        <v>32.3</v>
       </c>
       <c r="L29" t="n">
-        <v>47.56</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.38</v>
+        <v>-5.37</v>
       </c>
       <c r="K30" t="n">
-        <v>93.97</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>94.25</v>
+        <v>68.61</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-56.89</v>
+        <v>-40.69</v>
       </c>
       <c r="K31" t="n">
-        <v>-43.39</v>
+        <v>-31.04</v>
       </c>
       <c r="L31" t="n">
-        <v>71.55</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.89</v>
+        <v>-3.67</v>
       </c>
       <c r="K32" t="n">
-        <v>82.84</v>
+        <v>62.13</v>
       </c>
       <c r="L32" t="n">
-        <v>82.98</v>
+        <v>62.24</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>82.56</v>
+        <v>61.92</v>
       </c>
       <c r="K33" t="n">
-        <v>3.94</v>
+        <v>2.95</v>
       </c>
       <c r="L33" t="n">
-        <v>82.65000000000001</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-44.1</v>
+        <v>-33.08</v>
       </c>
       <c r="K34" t="n">
-        <v>102.53</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>111.61</v>
+        <v>83.70999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-95.40000000000001</v>
+        <v>-71.55</v>
       </c>
       <c r="K35" t="n">
-        <v>62.07</v>
+        <v>46.55</v>
       </c>
       <c r="L35" t="n">
-        <v>113.81</v>
+        <v>85.36</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>42.01</v>
+        <v>10.4</v>
       </c>
       <c r="K36" t="n">
-        <v>-30.86</v>
+        <v>-7.64</v>
       </c>
       <c r="L36" t="n">
-        <v>52.12</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-94.34999999999999</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-25.51</v>
+        <v>-19.13</v>
       </c>
       <c r="L37" t="n">
-        <v>97.73</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-66.77</v>
+        <v>-48.59</v>
       </c>
       <c r="K38" t="n">
-        <v>-117.11</v>
+        <v>-85.22</v>
       </c>
       <c r="L38" t="n">
-        <v>134.8</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-78.40000000000001</v>
+        <v>-58.8</v>
       </c>
       <c r="K39" t="n">
-        <v>123.81</v>
+        <v>92.86</v>
       </c>
       <c r="L39" t="n">
-        <v>146.55</v>
+        <v>109.91</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>78.89</v>
+        <v>59.16</v>
       </c>
       <c r="K40" t="n">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="L40" t="n">
-        <v>78.90000000000001</v>
+        <v>59.17</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-36.63</v>
+        <v>-26.82</v>
       </c>
       <c r="K41" t="n">
-        <v>-191.89</v>
+        <v>-140.47</v>
       </c>
       <c r="L41" t="n">
-        <v>195.35</v>
+        <v>143.01</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-79.39</v>
+        <v>-59.54</v>
       </c>
       <c r="K42" t="n">
-        <v>179.67</v>
+        <v>134.75</v>
       </c>
       <c r="L42" t="n">
-        <v>196.43</v>
+        <v>147.32</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>11.45</v>
+        <v>8.57</v>
       </c>
       <c r="K43" t="n">
-        <v>347.99</v>
+        <v>260.35</v>
       </c>
       <c r="L43" t="n">
-        <v>348.18</v>
+        <v>260.49</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-36.45</v>
+        <v>-27.33</v>
       </c>
       <c r="K44" t="n">
-        <v>-37.8</v>
+        <v>-28.35</v>
       </c>
       <c r="L44" t="n">
-        <v>52.51</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
       <c r="K45" t="n">
-        <v>74.81</v>
+        <v>54.06</v>
       </c>
       <c r="L45" t="n">
-        <v>74.84</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-67.7</v>
+        <v>-46.72</v>
       </c>
       <c r="K46" t="n">
-        <v>-77.83</v>
+        <v>-53.71</v>
       </c>
       <c r="L46" t="n">
-        <v>103.15</v>
+        <v>71.19</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>72.88</v>
+        <v>52.92</v>
       </c>
       <c r="K47" t="n">
-        <v>80.91</v>
+        <v>58.75</v>
       </c>
       <c r="L47" t="n">
-        <v>108.9</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-100.65</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-32.23</v>
+        <v>-24.18</v>
       </c>
       <c r="L48" t="n">
-        <v>105.69</v>
+        <v>79.27</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>63.92</v>
+        <v>47.31</v>
       </c>
       <c r="K49" t="n">
-        <v>3.36</v>
+        <v>2.49</v>
       </c>
       <c r="L49" t="n">
-        <v>64.01000000000001</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>30.75</v>
+        <v>23.06</v>
       </c>
       <c r="K50" t="n">
-        <v>159.55</v>
+        <v>119.66</v>
       </c>
       <c r="L50" t="n">
-        <v>162.48</v>
+        <v>121.86</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>76.13</v>
+        <v>57.1</v>
       </c>
       <c r="K51" t="n">
-        <v>-67.23999999999999</v>
+        <v>-50.43</v>
       </c>
       <c r="L51" t="n">
-        <v>101.57</v>
+        <v>76.18000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-33.14</v>
+        <v>-24.85</v>
       </c>
       <c r="K52" t="n">
-        <v>-131.55</v>
+        <v>-98.66</v>
       </c>
       <c r="L52" t="n">
-        <v>135.66</v>
+        <v>101.74</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>89.81999999999999</v>
+        <v>67.36</v>
       </c>
       <c r="K53" t="n">
-        <v>-26.12</v>
+        <v>-19.59</v>
       </c>
       <c r="L53" t="n">
-        <v>93.54000000000001</v>
+        <v>70.15000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>136.79</v>
+        <v>102.33</v>
       </c>
       <c r="K54" t="n">
-        <v>125.46</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>185.62</v>
+        <v>138.85</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-122.13</v>
+        <v>-91.59999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-40.71</v>
+        <v>-30.53</v>
       </c>
       <c r="L55" t="n">
-        <v>128.73</v>
+        <v>96.55</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-158.49</v>
+        <v>-116.58</v>
       </c>
       <c r="K56" t="n">
-        <v>-123.62</v>
+        <v>-90.93000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>201</v>
+        <v>147.85</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-267.75</v>
+        <v>-200.82</v>
       </c>
       <c r="K57" t="n">
-        <v>-44</v>
+        <v>-33</v>
       </c>
       <c r="L57" t="n">
-        <v>271.34</v>
+        <v>203.51</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-182.94</v>
+        <v>-129.93</v>
       </c>
       <c r="K58" t="n">
-        <v>-18.81</v>
+        <v>-13.36</v>
       </c>
       <c r="L58" t="n">
-        <v>183.91</v>
+        <v>130.61</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-55.52</v>
+        <v>-41.64</v>
       </c>
       <c r="K59" t="n">
-        <v>33.65</v>
+        <v>25.24</v>
       </c>
       <c r="L59" t="n">
-        <v>64.92</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>48.2</v>
+        <v>36.15</v>
       </c>
       <c r="K60" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="L60" t="n">
-        <v>48.53</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-50.75</v>
+        <v>-32.29</v>
       </c>
       <c r="K61" t="n">
-        <v>-101.5</v>
+        <v>-64.56999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>113.48</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-76.72</v>
+        <v>-57.54</v>
       </c>
       <c r="K62" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="L62" t="n">
-        <v>76.72</v>
+        <v>57.54</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>92.97</v>
+        <v>63.45</v>
       </c>
       <c r="K63" t="n">
-        <v>10.58</v>
+        <v>7.22</v>
       </c>
       <c r="L63" t="n">
-        <v>93.56999999999999</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-40.75</v>
+        <v>-30.57</v>
       </c>
       <c r="K64" t="n">
-        <v>-44.79</v>
+        <v>-33.59</v>
       </c>
       <c r="L64" t="n">
-        <v>60.56</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-25.45</v>
+        <v>-17.6</v>
       </c>
       <c r="K65" t="n">
-        <v>69.51000000000001</v>
+        <v>48.08</v>
       </c>
       <c r="L65" t="n">
-        <v>74.02</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-129.88</v>
+        <v>-97.41</v>
       </c>
       <c r="K66" t="n">
-        <v>111.65</v>
+        <v>83.73</v>
       </c>
       <c r="L66" t="n">
-        <v>171.27</v>
+        <v>128.45</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>69.36</v>
+        <v>51.63</v>
       </c>
       <c r="K67" t="n">
-        <v>-63.77</v>
+        <v>-47.47</v>
       </c>
       <c r="L67" t="n">
-        <v>94.22</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-65.19</v>
+        <v>-47.56</v>
       </c>
       <c r="K68" t="n">
-        <v>-272.63</v>
+        <v>-198.89</v>
       </c>
       <c r="L68" t="n">
-        <v>280.32</v>
+        <v>204.5</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>56.47</v>
+        <v>42.35</v>
       </c>
       <c r="K69" t="n">
-        <v>-132.54</v>
+        <v>-99.41</v>
       </c>
       <c r="L69" t="n">
-        <v>144.07</v>
+        <v>108.05</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>64.52</v>
+        <v>48.39</v>
       </c>
       <c r="K70" t="n">
-        <v>99.83</v>
+        <v>74.87</v>
       </c>
       <c r="L70" t="n">
-        <v>118.87</v>
+        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>187.94</v>
+        <v>140.96</v>
       </c>
       <c r="K71" t="n">
-        <v>51.65</v>
+        <v>38.74</v>
       </c>
       <c r="L71" t="n">
-        <v>194.91</v>
+        <v>146.18</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-144.27</v>
+        <v>-108.2</v>
       </c>
       <c r="K72" t="n">
-        <v>-186.89</v>
+        <v>-140.17</v>
       </c>
       <c r="L72" t="n">
-        <v>236.09</v>
+        <v>177.07</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-247.85</v>
+        <v>-176.83</v>
       </c>
       <c r="K73" t="n">
-        <v>26.7</v>
+        <v>19.05</v>
       </c>
       <c r="L73" t="n">
-        <v>249.28</v>
+        <v>177.85</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>36.14</v>
+        <v>27.11</v>
       </c>
       <c r="K74" t="n">
-        <v>-44.96</v>
+        <v>-33.72</v>
       </c>
       <c r="L74" t="n">
-        <v>57.69</v>
+        <v>43.27</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-51.33</v>
+        <v>-38.06</v>
       </c>
       <c r="K75" t="n">
-        <v>9.16</v>
+        <v>6.79</v>
       </c>
       <c r="L75" t="n">
-        <v>52.15</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>13.54</v>
+        <v>10.16</v>
       </c>
       <c r="K76" t="n">
-        <v>-31.11</v>
+        <v>-23.33</v>
       </c>
       <c r="L76" t="n">
-        <v>33.93</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-48.59</v>
+        <v>-36.45</v>
       </c>
       <c r="K77" t="n">
-        <v>-16.28</v>
+        <v>-12.21</v>
       </c>
       <c r="L77" t="n">
-        <v>51.25</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>47.75</v>
+        <v>35.69</v>
       </c>
       <c r="K78" t="n">
-        <v>55.71</v>
+        <v>41.64</v>
       </c>
       <c r="L78" t="n">
-        <v>73.37</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>27.51</v>
+        <v>19.61</v>
       </c>
       <c r="K79" t="n">
-        <v>-76.63</v>
+        <v>-54.62</v>
       </c>
       <c r="L79" t="n">
-        <v>81.42</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>54.29</v>
+        <v>40.71</v>
       </c>
       <c r="K80" t="n">
-        <v>-80.53</v>
+        <v>-60.39</v>
       </c>
       <c r="L80" t="n">
-        <v>97.11</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-42.58</v>
+        <v>-27.59</v>
       </c>
       <c r="K81" t="n">
-        <v>-129.56</v>
+        <v>-83.94</v>
       </c>
       <c r="L81" t="n">
-        <v>136.37</v>
+        <v>88.36</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-150.23</v>
+        <v>-104.96</v>
       </c>
       <c r="K82" t="n">
-        <v>-70.29000000000001</v>
+        <v>-49.11</v>
       </c>
       <c r="L82" t="n">
-        <v>165.86</v>
+        <v>115.88</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-81.20999999999999</v>
+        <v>-60.59</v>
       </c>
       <c r="K83" t="n">
-        <v>140.44</v>
+        <v>104.79</v>
       </c>
       <c r="L83" t="n">
-        <v>162.23</v>
+        <v>121.04</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-101.36</v>
+        <v>-66.81999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-101.29</v>
+        <v>-66.78</v>
       </c>
       <c r="L84" t="n">
-        <v>143.3</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-153.11</v>
+        <v>-96.17</v>
       </c>
       <c r="K85" t="n">
-        <v>-46.13</v>
+        <v>-28.98</v>
       </c>
       <c r="L85" t="n">
-        <v>159.91</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-133.59</v>
+        <v>-91.56</v>
       </c>
       <c r="K86" t="n">
-        <v>235.12</v>
+        <v>161.15</v>
       </c>
       <c r="L86" t="n">
-        <v>270.42</v>
+        <v>185.35</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-110.79</v>
+        <v>-83.09</v>
       </c>
       <c r="K87" t="n">
-        <v>74.86</v>
+        <v>56.15</v>
       </c>
       <c r="L87" t="n">
-        <v>133.71</v>
+        <v>100.28</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>118.81</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>113.22</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>164.12</v>
+        <v>112.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>6.5</v>
+        <v>6.18</v>
       </c>
       <c r="K14" t="n">
-        <v>60.71</v>
+        <v>57.76</v>
       </c>
       <c r="L14" t="n">
-        <v>61.06</v>
+        <v>58.09</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>37.16</v>
+        <v>37.27</v>
       </c>
       <c r="K15" t="n">
         <v>0.55</v>
       </c>
       <c r="L15" t="n">
-        <v>37.17</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-22.71</v>
+        <v>-23.7</v>
       </c>
       <c r="K16" t="n">
-        <v>18.96</v>
+        <v>19.79</v>
       </c>
       <c r="L16" t="n">
-        <v>29.58</v>
+        <v>30.88</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-49.15</v>
+        <v>-49.63</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.45</v>
+        <v>-3.49</v>
       </c>
       <c r="L17" t="n">
-        <v>49.27</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-33.76</v>
+        <v>-35.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-26.22</v>
+        <v>-27.6</v>
       </c>
       <c r="L18" t="n">
-        <v>42.74</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-21.7</v>
+        <v>-21.37</v>
       </c>
       <c r="K19" t="n">
-        <v>-63.14</v>
+        <v>-62.18</v>
       </c>
       <c r="L19" t="n">
-        <v>66.76000000000001</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-18.32</v>
+        <v>-18.84</v>
       </c>
       <c r="K20" t="n">
-        <v>60.08</v>
+        <v>61.81</v>
       </c>
       <c r="L20" t="n">
-        <v>62.81</v>
+        <v>64.62</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-42.7</v>
+        <v>-46.38</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.27</v>
+        <v>-17.67</v>
       </c>
       <c r="L21" t="n">
-        <v>45.7</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>97.39</v>
+        <v>95.45</v>
       </c>
       <c r="K22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L22" t="n">
-        <v>97.51000000000001</v>
+        <v>95.58</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>87.92</v>
+        <v>90.7</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.76</v>
+        <v>-4.91</v>
       </c>
       <c r="L23" t="n">
-        <v>88.04000000000001</v>
+        <v>90.84</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-57.91</v>
+        <v>-58.98</v>
       </c>
       <c r="K24" t="n">
-        <v>-73.01000000000001</v>
+        <v>-74.34999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>93.19</v>
+        <v>94.91</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-36.88</v>
+        <v>-36.02</v>
       </c>
       <c r="K25" t="n">
-        <v>18.31</v>
+        <v>17.89</v>
       </c>
       <c r="L25" t="n">
-        <v>41.18</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-153.08</v>
+        <v>-152.55</v>
       </c>
       <c r="K26" t="n">
-        <v>-37.95</v>
+        <v>-37.82</v>
       </c>
       <c r="L26" t="n">
-        <v>157.71</v>
+        <v>157.17</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-161.73</v>
+        <v>-161.34</v>
       </c>
       <c r="K27" t="n">
-        <v>-35.26</v>
+        <v>-35.18</v>
       </c>
       <c r="L27" t="n">
-        <v>165.53</v>
+        <v>165.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>126.03</v>
+        <v>123.98</v>
       </c>
       <c r="K28" t="n">
-        <v>139.1</v>
+        <v>136.84</v>
       </c>
       <c r="L28" t="n">
-        <v>187.71</v>
+        <v>184.65</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.8</v>
+        <v>-13.09</v>
       </c>
       <c r="K29" t="n">
-        <v>32.3</v>
+        <v>33.04</v>
       </c>
       <c r="L29" t="n">
-        <v>34.75</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.37</v>
+        <v>-5.09</v>
       </c>
       <c r="K30" t="n">
-        <v>68.40000000000001</v>
+        <v>64.77</v>
       </c>
       <c r="L30" t="n">
-        <v>68.61</v>
+        <v>64.97</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-40.69</v>
+        <v>-39.83</v>
       </c>
       <c r="K31" t="n">
-        <v>-31.04</v>
+        <v>-30.38</v>
       </c>
       <c r="L31" t="n">
-        <v>51.18</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.67</v>
+        <v>-3.61</v>
       </c>
       <c r="K32" t="n">
-        <v>62.13</v>
+        <v>61.05</v>
       </c>
       <c r="L32" t="n">
-        <v>62.24</v>
+        <v>61.16</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>61.92</v>
+        <v>60.63</v>
       </c>
       <c r="K33" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="L33" t="n">
-        <v>61.99</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-33.08</v>
+        <v>-31.77</v>
       </c>
       <c r="K34" t="n">
-        <v>76.90000000000001</v>
+        <v>73.86</v>
       </c>
       <c r="L34" t="n">
-        <v>83.70999999999999</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-71.55</v>
+        <v>-71.28</v>
       </c>
       <c r="K35" t="n">
-        <v>46.55</v>
+        <v>46.37</v>
       </c>
       <c r="L35" t="n">
-        <v>85.36</v>
+        <v>85.04000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>10.4</v>
+        <v>10.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-7.64</v>
+        <v>-7.5</v>
       </c>
       <c r="L36" t="n">
-        <v>12.91</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-70.76000000000001</v>
+        <v>-71.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-19.13</v>
+        <v>-19.41</v>
       </c>
       <c r="L37" t="n">
-        <v>73.3</v>
+        <v>74.37</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-48.59</v>
+        <v>-48.8</v>
       </c>
       <c r="K38" t="n">
-        <v>-85.22</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>98.09999999999999</v>
+        <v>98.53</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-58.8</v>
+        <v>-59.02</v>
       </c>
       <c r="K39" t="n">
-        <v>92.86</v>
+        <v>93.19</v>
       </c>
       <c r="L39" t="n">
-        <v>109.91</v>
+        <v>110.31</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>59.16</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="L40" t="n">
-        <v>59.17</v>
+        <v>64.08</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-26.82</v>
+        <v>-27.16</v>
       </c>
       <c r="K41" t="n">
-        <v>-140.47</v>
+        <v>-142.29</v>
       </c>
       <c r="L41" t="n">
-        <v>143.01</v>
+        <v>144.86</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-59.54</v>
+        <v>-60.16</v>
       </c>
       <c r="K42" t="n">
-        <v>134.75</v>
+        <v>136.15</v>
       </c>
       <c r="L42" t="n">
-        <v>147.32</v>
+        <v>148.85</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>8.57</v>
+        <v>8.17</v>
       </c>
       <c r="K43" t="n">
-        <v>260.35</v>
+        <v>248.5</v>
       </c>
       <c r="L43" t="n">
-        <v>260.49</v>
+        <v>248.63</v>
       </c>
     </row>
     <row r="44">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="K45" t="n">
-        <v>54.06</v>
+        <v>52.62</v>
       </c>
       <c r="L45" t="n">
-        <v>54.09</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-46.72</v>
+        <v>-44.88</v>
       </c>
       <c r="K46" t="n">
-        <v>-53.71</v>
+        <v>-51.6</v>
       </c>
       <c r="L46" t="n">
-        <v>71.19</v>
+        <v>68.38</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>52.92</v>
+        <v>51.48</v>
       </c>
       <c r="K47" t="n">
-        <v>58.75</v>
+        <v>57.15</v>
       </c>
       <c r="L47" t="n">
-        <v>79.06999999999999</v>
+        <v>76.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-75.48999999999999</v>
+        <v>-73.31</v>
       </c>
       <c r="K48" t="n">
-        <v>-24.18</v>
+        <v>-23.48</v>
       </c>
       <c r="L48" t="n">
-        <v>79.27</v>
+        <v>76.98</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>47.31</v>
+        <v>49.26</v>
       </c>
       <c r="K49" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="L49" t="n">
-        <v>47.38</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>23.06</v>
+        <v>22.21</v>
       </c>
       <c r="K50" t="n">
-        <v>119.66</v>
+        <v>115.25</v>
       </c>
       <c r="L50" t="n">
-        <v>121.86</v>
+        <v>117.37</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>57.1</v>
+        <v>58.42</v>
       </c>
       <c r="K51" t="n">
-        <v>-50.43</v>
+        <v>-51.6</v>
       </c>
       <c r="L51" t="n">
-        <v>76.18000000000001</v>
+        <v>77.95</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-24.85</v>
+        <v>-24.37</v>
       </c>
       <c r="K52" t="n">
-        <v>-98.66</v>
+        <v>-96.73999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>101.74</v>
+        <v>99.76000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>67.36</v>
+        <v>72.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-19.59</v>
+        <v>-21.01</v>
       </c>
       <c r="L53" t="n">
-        <v>70.15000000000001</v>
+        <v>75.23999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>102.33</v>
+        <v>99.38</v>
       </c>
       <c r="K54" t="n">
-        <v>93.84999999999999</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>138.85</v>
+        <v>134.85</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-91.59999999999999</v>
+        <v>-92.55</v>
       </c>
       <c r="K55" t="n">
-        <v>-30.53</v>
+        <v>-30.85</v>
       </c>
       <c r="L55" t="n">
-        <v>96.55</v>
+        <v>97.56</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-116.58</v>
+        <v>-118.93</v>
       </c>
       <c r="K56" t="n">
-        <v>-90.93000000000001</v>
+        <v>-92.76000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>147.85</v>
+        <v>150.82</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-200.82</v>
+        <v>-195.02</v>
       </c>
       <c r="K57" t="n">
-        <v>-33</v>
+        <v>-32.04</v>
       </c>
       <c r="L57" t="n">
-        <v>203.51</v>
+        <v>197.63</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-129.93</v>
+        <v>-134.16</v>
       </c>
       <c r="K58" t="n">
-        <v>-13.36</v>
+        <v>-13.79</v>
       </c>
       <c r="L58" t="n">
-        <v>130.61</v>
+        <v>134.86</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-41.64</v>
+        <v>-40.47</v>
       </c>
       <c r="K59" t="n">
-        <v>25.24</v>
+        <v>24.53</v>
       </c>
       <c r="L59" t="n">
-        <v>48.69</v>
+        <v>47.33</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>36.15</v>
+        <v>36.66</v>
       </c>
       <c r="K60" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="L60" t="n">
-        <v>36.4</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-32.29</v>
+        <v>-30.94</v>
       </c>
       <c r="K61" t="n">
-        <v>-64.56999999999999</v>
+        <v>-61.87</v>
       </c>
       <c r="L61" t="n">
-        <v>72.19</v>
+        <v>69.17</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-57.54</v>
+        <v>-56.77</v>
       </c>
       <c r="K62" t="n">
         <v>0.1</v>
       </c>
       <c r="L62" t="n">
-        <v>57.54</v>
+        <v>56.77</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>63.45</v>
+        <v>62.34</v>
       </c>
       <c r="K63" t="n">
-        <v>7.22</v>
+        <v>7.09</v>
       </c>
       <c r="L63" t="n">
-        <v>63.86</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-30.57</v>
+        <v>-31.11</v>
       </c>
       <c r="K64" t="n">
-        <v>-33.59</v>
+        <v>-34.19</v>
       </c>
       <c r="L64" t="n">
-        <v>45.42</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-17.6</v>
+        <v>-18.93</v>
       </c>
       <c r="K65" t="n">
-        <v>48.08</v>
+        <v>51.71</v>
       </c>
       <c r="L65" t="n">
-        <v>51.2</v>
+        <v>55.07</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-97.41</v>
+        <v>-93.34</v>
       </c>
       <c r="K66" t="n">
-        <v>83.73</v>
+        <v>80.23</v>
       </c>
       <c r="L66" t="n">
-        <v>128.45</v>
+        <v>123.08</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>51.63</v>
+        <v>52.87</v>
       </c>
       <c r="K67" t="n">
-        <v>-47.47</v>
+        <v>-48.61</v>
       </c>
       <c r="L67" t="n">
-        <v>70.14</v>
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-47.56</v>
+        <v>-44.87</v>
       </c>
       <c r="K68" t="n">
-        <v>-198.89</v>
+        <v>-187.65</v>
       </c>
       <c r="L68" t="n">
-        <v>204.5</v>
+        <v>192.94</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>42.35</v>
+        <v>41.92</v>
       </c>
       <c r="K69" t="n">
-        <v>-99.41</v>
+        <v>-98.39</v>
       </c>
       <c r="L69" t="n">
-        <v>108.05</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>48.39</v>
+        <v>49.18</v>
       </c>
       <c r="K70" t="n">
-        <v>74.87</v>
+        <v>76.09</v>
       </c>
       <c r="L70" t="n">
-        <v>89.15000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>140.96</v>
+        <v>141.99</v>
       </c>
       <c r="K71" t="n">
-        <v>38.74</v>
+        <v>39.02</v>
       </c>
       <c r="L71" t="n">
-        <v>146.18</v>
+        <v>147.25</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-108.2</v>
+        <v>-107.23</v>
       </c>
       <c r="K72" t="n">
-        <v>-140.17</v>
+        <v>-138.9</v>
       </c>
       <c r="L72" t="n">
-        <v>177.07</v>
+        <v>175.47</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-176.83</v>
+        <v>-173.57</v>
       </c>
       <c r="K73" t="n">
-        <v>19.05</v>
+        <v>18.7</v>
       </c>
       <c r="L73" t="n">
-        <v>177.85</v>
+        <v>174.58</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>27.11</v>
+        <v>26.75</v>
       </c>
       <c r="K74" t="n">
-        <v>-33.72</v>
+        <v>-33.28</v>
       </c>
       <c r="L74" t="n">
-        <v>43.27</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-38.06</v>
+        <v>-38.37</v>
       </c>
       <c r="K75" t="n">
-        <v>6.79</v>
+        <v>6.85</v>
       </c>
       <c r="L75" t="n">
-        <v>38.66</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>10.16</v>
+        <v>10.93</v>
       </c>
       <c r="K76" t="n">
-        <v>-23.33</v>
+        <v>-25.11</v>
       </c>
       <c r="L76" t="n">
-        <v>25.45</v>
+        <v>27.39</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-36.45</v>
+        <v>-38.08</v>
       </c>
       <c r="K77" t="n">
-        <v>-12.21</v>
+        <v>-12.76</v>
       </c>
       <c r="L77" t="n">
-        <v>38.44</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>35.69</v>
+        <v>35.55</v>
       </c>
       <c r="K78" t="n">
-        <v>41.64</v>
+        <v>41.47</v>
       </c>
       <c r="L78" t="n">
-        <v>54.84</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>19.61</v>
+        <v>19.52</v>
       </c>
       <c r="K79" t="n">
-        <v>-54.62</v>
+        <v>-54.38</v>
       </c>
       <c r="L79" t="n">
-        <v>58.04</v>
+        <v>57.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>40.71</v>
+        <v>41.54</v>
       </c>
       <c r="K80" t="n">
-        <v>-60.39</v>
+        <v>-61.62</v>
       </c>
       <c r="L80" t="n">
-        <v>72.84</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-27.59</v>
+        <v>-27.29</v>
       </c>
       <c r="K81" t="n">
-        <v>-83.94</v>
+        <v>-83.03</v>
       </c>
       <c r="L81" t="n">
-        <v>88.36</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-104.96</v>
+        <v>-101.83</v>
       </c>
       <c r="K82" t="n">
-        <v>-49.11</v>
+        <v>-47.64</v>
       </c>
       <c r="L82" t="n">
-        <v>115.88</v>
+        <v>112.42</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-60.59</v>
+        <v>-59.36</v>
       </c>
       <c r="K83" t="n">
-        <v>104.79</v>
+        <v>102.67</v>
       </c>
       <c r="L83" t="n">
-        <v>121.04</v>
+        <v>118.59</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-66.81999999999999</v>
+        <v>-68.15000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>-66.78</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>94.47</v>
+        <v>96.34</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-96.17</v>
+        <v>-98.20999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-28.98</v>
+        <v>-29.59</v>
       </c>
       <c r="L85" t="n">
-        <v>100.44</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-91.56</v>
+        <v>-90.67</v>
       </c>
       <c r="K86" t="n">
-        <v>161.15</v>
+        <v>159.58</v>
       </c>
       <c r="L86" t="n">
-        <v>185.35</v>
+        <v>183.54</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-83.09</v>
+        <v>-89.19</v>
       </c>
       <c r="K87" t="n">
-        <v>56.15</v>
+        <v>60.26</v>
       </c>
       <c r="L87" t="n">
-        <v>100.28</v>
+        <v>107.64</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>81.26000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="K88" t="n">
-        <v>77.43000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>112.25</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>6.18</v>
+        <v>5.82</v>
       </c>
       <c r="K14" t="n">
-        <v>57.76</v>
+        <v>54.39</v>
       </c>
       <c r="L14" t="n">
-        <v>58.09</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>37.27</v>
+        <v>37.4</v>
       </c>
       <c r="K15" t="n">
         <v>0.55</v>
       </c>
       <c r="L15" t="n">
-        <v>37.28</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.7</v>
+        <v>-24.84</v>
       </c>
       <c r="K16" t="n">
-        <v>19.79</v>
+        <v>20.73</v>
       </c>
       <c r="L16" t="n">
-        <v>30.88</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-49.63</v>
+        <v>-50.18</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.49</v>
+        <v>-3.53</v>
       </c>
       <c r="L17" t="n">
-        <v>49.75</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-35.52</v>
+        <v>-37.54</v>
       </c>
       <c r="K18" t="n">
-        <v>-27.6</v>
+        <v>-29.16</v>
       </c>
       <c r="L18" t="n">
-        <v>44.98</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-21.37</v>
+        <v>-21</v>
       </c>
       <c r="K19" t="n">
-        <v>-62.18</v>
+        <v>-61.09</v>
       </c>
       <c r="L19" t="n">
-        <v>65.75</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-18.84</v>
+        <v>-19.44</v>
       </c>
       <c r="K20" t="n">
-        <v>61.81</v>
+        <v>63.78</v>
       </c>
       <c r="L20" t="n">
-        <v>64.62</v>
+        <v>66.68000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-46.38</v>
+        <v>-50.58</v>
       </c>
       <c r="K21" t="n">
-        <v>-17.67</v>
+        <v>-19.28</v>
       </c>
       <c r="L21" t="n">
-        <v>49.63</v>
+        <v>54.13</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>95.45</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="L22" t="n">
-        <v>95.58</v>
+        <v>93.36</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>90.7</v>
+        <v>93.89</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.91</v>
+        <v>-5.08</v>
       </c>
       <c r="L23" t="n">
-        <v>90.84</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-58.98</v>
+        <v>-60.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-74.34999999999999</v>
+        <v>-75.89</v>
       </c>
       <c r="L24" t="n">
-        <v>94.91</v>
+        <v>96.87</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-36.02</v>
+        <v>-39.41</v>
       </c>
       <c r="K25" t="n">
-        <v>17.89</v>
+        <v>19.57</v>
       </c>
       <c r="L25" t="n">
-        <v>40.22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-152.55</v>
+        <v>-151.95</v>
       </c>
       <c r="K26" t="n">
-        <v>-37.82</v>
+        <v>-37.67</v>
       </c>
       <c r="L26" t="n">
-        <v>157.17</v>
+        <v>156.55</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-161.34</v>
+        <v>-160.9</v>
       </c>
       <c r="K27" t="n">
-        <v>-35.18</v>
+        <v>-35.08</v>
       </c>
       <c r="L27" t="n">
-        <v>165.14</v>
+        <v>164.68</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>123.98</v>
+        <v>121.64</v>
       </c>
       <c r="K28" t="n">
-        <v>136.84</v>
+        <v>134.26</v>
       </c>
       <c r="L28" t="n">
-        <v>184.65</v>
+        <v>181.16</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.09</v>
+        <v>-13.43</v>
       </c>
       <c r="K29" t="n">
-        <v>33.04</v>
+        <v>33.89</v>
       </c>
       <c r="L29" t="n">
-        <v>35.54</v>
+        <v>36.45</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.09</v>
+        <v>-4.76</v>
       </c>
       <c r="K30" t="n">
-        <v>64.77</v>
+        <v>60.63</v>
       </c>
       <c r="L30" t="n">
-        <v>64.97</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-39.83</v>
+        <v>-38.85</v>
       </c>
       <c r="K31" t="n">
-        <v>-30.38</v>
+        <v>-29.63</v>
       </c>
       <c r="L31" t="n">
-        <v>50.1</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.61</v>
+        <v>-3.53</v>
       </c>
       <c r="K32" t="n">
-        <v>61.05</v>
+        <v>59.82</v>
       </c>
       <c r="L32" t="n">
-        <v>61.16</v>
+        <v>59.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>60.63</v>
+        <v>59.16</v>
       </c>
       <c r="K33" t="n">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="L33" t="n">
-        <v>60.7</v>
+        <v>59.23</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-31.77</v>
+        <v>-30.28</v>
       </c>
       <c r="K34" t="n">
-        <v>73.86</v>
+        <v>70.39</v>
       </c>
       <c r="L34" t="n">
-        <v>80.40000000000001</v>
+        <v>76.63</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-71.28</v>
+        <v>-70.97</v>
       </c>
       <c r="K35" t="n">
-        <v>46.37</v>
+        <v>46.17</v>
       </c>
       <c r="L35" t="n">
-        <v>85.04000000000001</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>10.22</v>
+        <v>10.95</v>
       </c>
       <c r="K36" t="n">
-        <v>-7.5</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>12.68</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-71.8</v>
+        <v>-72.98</v>
       </c>
       <c r="K37" t="n">
-        <v>-19.41</v>
+        <v>-19.73</v>
       </c>
       <c r="L37" t="n">
-        <v>74.37</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-48.8</v>
+        <v>-49.05</v>
       </c>
       <c r="K38" t="n">
-        <v>-85.59999999999999</v>
+        <v>-86.03</v>
       </c>
       <c r="L38" t="n">
-        <v>98.53</v>
+        <v>99.02</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-59.02</v>
+        <v>-59.26</v>
       </c>
       <c r="K39" t="n">
-        <v>93.19</v>
+        <v>93.58</v>
       </c>
       <c r="L39" t="n">
-        <v>110.31</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>64.06999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="K40" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="L40" t="n">
-        <v>64.08</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-27.16</v>
+        <v>-27.56</v>
       </c>
       <c r="K41" t="n">
-        <v>-142.29</v>
+        <v>-144.37</v>
       </c>
       <c r="L41" t="n">
-        <v>144.86</v>
+        <v>146.97</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-60.16</v>
+        <v>-60.87</v>
       </c>
       <c r="K42" t="n">
-        <v>136.15</v>
+        <v>137.75</v>
       </c>
       <c r="L42" t="n">
-        <v>148.85</v>
+        <v>150.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>8.17</v>
+        <v>7.73</v>
       </c>
       <c r="K43" t="n">
-        <v>248.5</v>
+        <v>234.94</v>
       </c>
       <c r="L43" t="n">
-        <v>248.63</v>
+        <v>235.07</v>
       </c>
     </row>
     <row r="44">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="K45" t="n">
-        <v>52.62</v>
+        <v>50.98</v>
       </c>
       <c r="L45" t="n">
-        <v>52.65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-44.88</v>
+        <v>-42.78</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.6</v>
+        <v>-49.18</v>
       </c>
       <c r="L46" t="n">
-        <v>68.38</v>
+        <v>65.18000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>51.48</v>
+        <v>49.82</v>
       </c>
       <c r="K47" t="n">
-        <v>57.15</v>
+        <v>55.31</v>
       </c>
       <c r="L47" t="n">
-        <v>76.91</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.31</v>
+        <v>-70.81999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-23.48</v>
+        <v>-22.68</v>
       </c>
       <c r="L48" t="n">
-        <v>76.98</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>49.26</v>
+        <v>51.49</v>
       </c>
       <c r="K49" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="L49" t="n">
-        <v>49.33</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>22.21</v>
+        <v>21.24</v>
       </c>
       <c r="K50" t="n">
-        <v>115.25</v>
+        <v>110.21</v>
       </c>
       <c r="L50" t="n">
-        <v>117.37</v>
+        <v>112.24</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>58.42</v>
+        <v>59.94</v>
       </c>
       <c r="K51" t="n">
-        <v>-51.6</v>
+        <v>-52.94</v>
       </c>
       <c r="L51" t="n">
-        <v>77.95</v>
+        <v>79.97</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-24.37</v>
+        <v>-23.81</v>
       </c>
       <c r="K52" t="n">
-        <v>-96.73999999999999</v>
+        <v>-94.54000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>99.76000000000001</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>72.25</v>
+        <v>77.83</v>
       </c>
       <c r="K53" t="n">
-        <v>-21.01</v>
+        <v>-22.64</v>
       </c>
       <c r="L53" t="n">
-        <v>75.23999999999999</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>99.38</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>91.15000000000001</v>
+        <v>88.06</v>
       </c>
       <c r="L54" t="n">
-        <v>134.85</v>
+        <v>130.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-92.55</v>
+        <v>-93.64</v>
       </c>
       <c r="K55" t="n">
-        <v>-30.85</v>
+        <v>-31.21</v>
       </c>
       <c r="L55" t="n">
-        <v>97.56</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-118.93</v>
+        <v>-121.61</v>
       </c>
       <c r="K56" t="n">
-        <v>-92.76000000000001</v>
+        <v>-94.84999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>150.82</v>
+        <v>154.22</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-195.02</v>
+        <v>-188.39</v>
       </c>
       <c r="K57" t="n">
-        <v>-32.04</v>
+        <v>-30.95</v>
       </c>
       <c r="L57" t="n">
-        <v>197.63</v>
+        <v>190.91</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-134.16</v>
+        <v>-138.99</v>
       </c>
       <c r="K58" t="n">
-        <v>-13.79</v>
+        <v>-14.29</v>
       </c>
       <c r="L58" t="n">
-        <v>134.86</v>
+        <v>139.72</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-40.47</v>
+        <v>-39.14</v>
       </c>
       <c r="K59" t="n">
-        <v>24.53</v>
+        <v>23.72</v>
       </c>
       <c r="L59" t="n">
-        <v>47.33</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>36.66</v>
+        <v>37.24</v>
       </c>
       <c r="K60" t="n">
-        <v>4.26</v>
+        <v>4.32</v>
       </c>
       <c r="L60" t="n">
-        <v>36.9</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-30.94</v>
+        <v>-29.39</v>
       </c>
       <c r="K61" t="n">
-        <v>-61.87</v>
+        <v>-58.78</v>
       </c>
       <c r="L61" t="n">
-        <v>69.17</v>
+        <v>65.72</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-56.77</v>
+        <v>-55.9</v>
       </c>
       <c r="K62" t="n">
         <v>0.1</v>
       </c>
       <c r="L62" t="n">
-        <v>56.77</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>62.34</v>
+        <v>61.07</v>
       </c>
       <c r="K63" t="n">
-        <v>7.09</v>
+        <v>6.95</v>
       </c>
       <c r="L63" t="n">
-        <v>62.74</v>
+        <v>61.46</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-31.11</v>
+        <v>-31.73</v>
       </c>
       <c r="K64" t="n">
-        <v>-34.19</v>
+        <v>-34.87</v>
       </c>
       <c r="L64" t="n">
-        <v>46.22</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-18.93</v>
+        <v>-20.45</v>
       </c>
       <c r="K65" t="n">
-        <v>51.71</v>
+        <v>55.86</v>
       </c>
       <c r="L65" t="n">
-        <v>55.07</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-93.34</v>
+        <v>-88.68000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>80.23</v>
+        <v>76.23</v>
       </c>
       <c r="L66" t="n">
-        <v>123.08</v>
+        <v>116.95</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>52.87</v>
+        <v>54.28</v>
       </c>
       <c r="K67" t="n">
-        <v>-48.61</v>
+        <v>-49.91</v>
       </c>
       <c r="L67" t="n">
-        <v>71.81999999999999</v>
+        <v>73.73</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-44.87</v>
+        <v>-41.8</v>
       </c>
       <c r="K68" t="n">
-        <v>-187.65</v>
+        <v>-174.8</v>
       </c>
       <c r="L68" t="n">
-        <v>192.94</v>
+        <v>179.72</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>41.92</v>
+        <v>41.42</v>
       </c>
       <c r="K69" t="n">
-        <v>-98.39</v>
+        <v>-97.23</v>
       </c>
       <c r="L69" t="n">
-        <v>106.95</v>
+        <v>105.68</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>49.18</v>
+        <v>50.08</v>
       </c>
       <c r="K70" t="n">
-        <v>76.09</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>90.59999999999999</v>
+        <v>92.26000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>141.99</v>
+        <v>143.17</v>
       </c>
       <c r="K71" t="n">
-        <v>39.02</v>
+        <v>39.34</v>
       </c>
       <c r="L71" t="n">
-        <v>147.25</v>
+        <v>148.47</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-107.23</v>
+        <v>-106.11</v>
       </c>
       <c r="K72" t="n">
-        <v>-138.9</v>
+        <v>-137.46</v>
       </c>
       <c r="L72" t="n">
-        <v>175.47</v>
+        <v>173.65</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-173.57</v>
+        <v>-169.85</v>
       </c>
       <c r="K73" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="L73" t="n">
-        <v>174.58</v>
+        <v>170.83</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>26.75</v>
+        <v>26.35</v>
       </c>
       <c r="K74" t="n">
-        <v>-33.28</v>
+        <v>-32.78</v>
       </c>
       <c r="L74" t="n">
-        <v>42.7</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-38.37</v>
+        <v>-38.73</v>
       </c>
       <c r="K75" t="n">
-        <v>6.85</v>
+        <v>6.91</v>
       </c>
       <c r="L75" t="n">
-        <v>38.98</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>10.93</v>
+        <v>11.81</v>
       </c>
       <c r="K76" t="n">
-        <v>-25.11</v>
+        <v>-27.14</v>
       </c>
       <c r="L76" t="n">
-        <v>27.39</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-38.08</v>
+        <v>-39.94</v>
       </c>
       <c r="K77" t="n">
-        <v>-12.76</v>
+        <v>-13.38</v>
       </c>
       <c r="L77" t="n">
-        <v>40.16</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>35.55</v>
+        <v>35.38</v>
       </c>
       <c r="K78" t="n">
-        <v>41.47</v>
+        <v>41.28</v>
       </c>
       <c r="L78" t="n">
-        <v>54.62</v>
+        <v>54.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>19.52</v>
+        <v>19.42</v>
       </c>
       <c r="K79" t="n">
-        <v>-54.38</v>
+        <v>-54.1</v>
       </c>
       <c r="L79" t="n">
-        <v>57.78</v>
+        <v>57.49</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>41.54</v>
+        <v>42.49</v>
       </c>
       <c r="K80" t="n">
-        <v>-61.62</v>
+        <v>-63.03</v>
       </c>
       <c r="L80" t="n">
-        <v>74.31999999999999</v>
+        <v>76.01000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-27.29</v>
+        <v>-26.95</v>
       </c>
       <c r="K81" t="n">
-        <v>-83.03</v>
+        <v>-81.98999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>87.40000000000001</v>
+        <v>86.31</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-101.83</v>
+        <v>-98.25</v>
       </c>
       <c r="K82" t="n">
-        <v>-47.64</v>
+        <v>-45.97</v>
       </c>
       <c r="L82" t="n">
-        <v>112.42</v>
+        <v>108.47</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-59.36</v>
+        <v>-57.96</v>
       </c>
       <c r="K83" t="n">
-        <v>102.67</v>
+        <v>100.24</v>
       </c>
       <c r="L83" t="n">
-        <v>118.59</v>
+        <v>115.79</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-68.15000000000001</v>
+        <v>-69.66</v>
       </c>
       <c r="K84" t="n">
-        <v>-68.09999999999999</v>
+        <v>-69.61</v>
       </c>
       <c r="L84" t="n">
-        <v>96.34</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-98.20999999999999</v>
+        <v>-100.53</v>
       </c>
       <c r="K85" t="n">
-        <v>-29.59</v>
+        <v>-30.29</v>
       </c>
       <c r="L85" t="n">
-        <v>102.57</v>
+        <v>104.99</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-90.67</v>
+        <v>-89.65000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>159.58</v>
+        <v>157.79</v>
       </c>
       <c r="L86" t="n">
-        <v>183.54</v>
+        <v>181.48</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-89.19</v>
+        <v>-96.15000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>60.26</v>
+        <v>64.97</v>
       </c>
       <c r="L87" t="n">
-        <v>107.64</v>
+        <v>116.04</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>84.7</v>
+        <v>88.64</v>
       </c>
       <c r="K88" t="n">
-        <v>80.70999999999999</v>
+        <v>84.47</v>
       </c>
       <c r="L88" t="n">
-        <v>117</v>
+        <v>122.44</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="F14" t="n">
-        <v>5.15</v>
+        <v>4.37</v>
       </c>
       <c r="G14" t="n">
-        <v>241.6</v>
+        <v>247.6</v>
       </c>
       <c r="H14" t="n">
-        <v>23</v>
+        <v>19.4</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>5.82</v>
+        <v>-29.41</v>
       </c>
       <c r="K14" t="n">
-        <v>54.39</v>
+        <v>23.99</v>
       </c>
       <c r="L14" t="n">
-        <v>54.7</v>
+        <v>37.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:34:12</t>
+          <t>04:32:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="F15" t="n">
-        <v>5.57</v>
+        <v>4.39</v>
       </c>
       <c r="G15" t="n">
-        <v>254.7</v>
+        <v>256.3</v>
       </c>
       <c r="H15" t="n">
-        <v>17.8</v>
+        <v>22.3</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>37.4</v>
+        <v>-47.42</v>
       </c>
       <c r="K15" t="n">
-        <v>0.55</v>
+        <v>-3.22</v>
       </c>
       <c r="L15" t="n">
-        <v>37.4</v>
+        <v>47.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:23</t>
+          <t>04:35:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="F16" t="n">
-        <v>5.24</v>
+        <v>6.09</v>
       </c>
       <c r="G16" t="n">
-        <v>241.2</v>
+        <v>244.1</v>
       </c>
       <c r="H16" t="n">
-        <v>22.5</v>
+        <v>24.2</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-24.84</v>
+        <v>-33.67</v>
       </c>
       <c r="K16" t="n">
-        <v>20.73</v>
+        <v>-26.39</v>
       </c>
       <c r="L16" t="n">
-        <v>32.35</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:49</t>
+          <t>04:39:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="F17" t="n">
-        <v>5.67</v>
+        <v>4.99</v>
       </c>
       <c r="G17" t="n">
-        <v>247</v>
+        <v>253.4</v>
       </c>
       <c r="H17" t="n">
-        <v>18.4</v>
+        <v>26.8</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-50.18</v>
+        <v>-47.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.53</v>
+        <v>-35.08</v>
       </c>
       <c r="L17" t="n">
-        <v>50.31</v>
+        <v>58.78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:43:00</t>
+          <t>04:41:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.98</v>
+        <v>1.37</v>
       </c>
       <c r="F18" t="n">
-        <v>5.06</v>
+        <v>3.98</v>
       </c>
       <c r="G18" t="n">
-        <v>250.9</v>
+        <v>253</v>
       </c>
       <c r="H18" t="n">
-        <v>25.2</v>
+        <v>30.1</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-37.54</v>
+        <v>-65.79000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-29.16</v>
+        <v>-9.68</v>
       </c>
       <c r="L18" t="n">
-        <v>47.54</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:44:33</t>
+          <t>04:43:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="F19" t="n">
-        <v>5.28</v>
+        <v>5.75</v>
       </c>
       <c r="G19" t="n">
-        <v>253.4</v>
+        <v>236</v>
       </c>
       <c r="H19" t="n">
-        <v>27.6</v>
+        <v>26.1</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-21</v>
+        <v>-58.72</v>
       </c>
       <c r="K19" t="n">
-        <v>-61.09</v>
+        <v>39.31</v>
       </c>
       <c r="L19" t="n">
-        <v>64.59999999999999</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:49:17</t>
+          <t>04:49:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="F20" t="n">
-        <v>4.95</v>
+        <v>3.38</v>
       </c>
       <c r="G20" t="n">
-        <v>253</v>
+        <v>250.8</v>
       </c>
       <c r="H20" t="n">
-        <v>30.1</v>
+        <v>22.2</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-19.44</v>
+        <v>61.52</v>
       </c>
       <c r="K20" t="n">
-        <v>63.78</v>
+        <v>87.59</v>
       </c>
       <c r="L20" t="n">
-        <v>66.68000000000001</v>
+        <v>107.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:51:41</t>
+          <t>04:51:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.13</v>
+        <v>1.69</v>
       </c>
       <c r="F21" t="n">
-        <v>4.86</v>
+        <v>4.79</v>
       </c>
       <c r="G21" t="n">
-        <v>261.6</v>
+        <v>244.4</v>
       </c>
       <c r="H21" t="n">
-        <v>16.8</v>
+        <v>24.9</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-50.58</v>
+        <v>73.45</v>
       </c>
       <c r="K21" t="n">
-        <v>-19.28</v>
+        <v>-13.84</v>
       </c>
       <c r="L21" t="n">
-        <v>54.13</v>
+        <v>74.73999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:53:14</t>
+          <t>04:53:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="F22" t="n">
-        <v>5.86</v>
+        <v>4.65</v>
       </c>
       <c r="G22" t="n">
-        <v>257.3</v>
+        <v>262.2</v>
       </c>
       <c r="H22" t="n">
-        <v>25</v>
+        <v>11.4</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>93.23999999999999</v>
+        <v>-66.13</v>
       </c>
       <c r="K22" t="n">
-        <v>4.69</v>
+        <v>-81.16</v>
       </c>
       <c r="L22" t="n">
-        <v>93.36</v>
+        <v>104.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:57:52</t>
+          <t>04:58:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="F23" t="n">
-        <v>5.29</v>
+        <v>3.08</v>
       </c>
       <c r="G23" t="n">
-        <v>252.8</v>
+        <v>265</v>
       </c>
       <c r="H23" t="n">
-        <v>23.9</v>
+        <v>25.3</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>93.89</v>
+        <v>103.13</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.08</v>
+        <v>-42.21</v>
       </c>
       <c r="L23" t="n">
-        <v>94.03</v>
+        <v>111.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:59:33</t>
+          <t>05:00:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.15</v>
+        <v>2.03</v>
       </c>
       <c r="F24" t="n">
-        <v>4.85</v>
+        <v>4.84</v>
       </c>
       <c r="G24" t="n">
-        <v>242.2</v>
+        <v>257.5</v>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>26.6</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-60.2</v>
+        <v>-128.35</v>
       </c>
       <c r="K24" t="n">
-        <v>-75.89</v>
+        <v>-31.26</v>
       </c>
       <c r="L24" t="n">
-        <v>96.87</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:00:33</t>
+          <t>05:01:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="F25" t="n">
-        <v>5.15</v>
+        <v>4.33</v>
       </c>
       <c r="G25" t="n">
-        <v>257.8</v>
+        <v>252.1</v>
       </c>
       <c r="H25" t="n">
-        <v>26.5</v>
+        <v>24.2</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-39.41</v>
+        <v>-127.16</v>
       </c>
       <c r="K25" t="n">
-        <v>19.57</v>
+        <v>-28.29</v>
       </c>
       <c r="L25" t="n">
-        <v>44</v>
+        <v>130.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:05:51</t>
+          <t>05:07:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1132,31 +1132,31 @@
         <v>1.73</v>
       </c>
       <c r="F26" t="n">
-        <v>5.74</v>
+        <v>4.31</v>
       </c>
       <c r="G26" t="n">
-        <v>255.6</v>
+        <v>255.8</v>
       </c>
       <c r="H26" t="n">
-        <v>21.5</v>
+        <v>25.4</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-151.95</v>
+        <v>122.05</v>
       </c>
       <c r="K26" t="n">
-        <v>-37.67</v>
+        <v>155.29</v>
       </c>
       <c r="L26" t="n">
-        <v>156.55</v>
+        <v>197.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:08:13</t>
+          <t>05:08:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="F27" t="n">
-        <v>5.47</v>
+        <v>6.09</v>
       </c>
       <c r="G27" t="n">
-        <v>250.7</v>
+        <v>254.9</v>
       </c>
       <c r="H27" t="n">
-        <v>22.1</v>
+        <v>31.7</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-160.9</v>
+        <v>-114.44</v>
       </c>
       <c r="K27" t="n">
-        <v>-35.08</v>
+        <v>147.26</v>
       </c>
       <c r="L27" t="n">
-        <v>164.68</v>
+        <v>186.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:09:35</t>
+          <t>05:10:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="F28" t="n">
-        <v>5.65</v>
+        <v>5.01</v>
       </c>
       <c r="G28" t="n">
-        <v>253.2</v>
+        <v>247.4</v>
       </c>
       <c r="H28" t="n">
-        <v>22.1</v>
+        <v>14.6</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>121.64</v>
+        <v>-45.32</v>
       </c>
       <c r="K28" t="n">
-        <v>134.26</v>
+        <v>262.85</v>
       </c>
       <c r="L28" t="n">
-        <v>181.16</v>
+        <v>266.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:20:53</t>
+          <t>05:18:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="F29" t="n">
-        <v>5.61</v>
+        <v>6.09</v>
       </c>
       <c r="G29" t="n">
-        <v>265.8</v>
+        <v>250.2</v>
       </c>
       <c r="H29" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.43</v>
+        <v>-47.86</v>
       </c>
       <c r="K29" t="n">
-        <v>33.89</v>
+        <v>-36.32</v>
       </c>
       <c r="L29" t="n">
-        <v>36.45</v>
+        <v>60.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:22:25</t>
+          <t>05:20:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="F30" t="n">
-        <v>5.23</v>
+        <v>3.52</v>
       </c>
       <c r="G30" t="n">
-        <v>231.7</v>
+        <v>248.1</v>
       </c>
       <c r="H30" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.76</v>
+        <v>-2.83</v>
       </c>
       <c r="K30" t="n">
-        <v>60.63</v>
+        <v>47.22</v>
       </c>
       <c r="L30" t="n">
-        <v>60.81</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:24:52</t>
+          <t>05:22:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.98</v>
+        <v>1.56</v>
       </c>
       <c r="F31" t="n">
-        <v>5.37</v>
+        <v>3.73</v>
       </c>
       <c r="G31" t="n">
-        <v>246.1</v>
+        <v>264.2</v>
       </c>
       <c r="H31" t="n">
-        <v>26.4</v>
+        <v>20.1</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-38.85</v>
+        <v>54.77</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.63</v>
+        <v>2.84</v>
       </c>
       <c r="L31" t="n">
-        <v>48.86</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:28:17</t>
+          <t>05:27:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="F32" t="n">
-        <v>5.26</v>
+        <v>6.09</v>
       </c>
       <c r="G32" t="n">
-        <v>242.4</v>
+        <v>253.6</v>
       </c>
       <c r="H32" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.53</v>
+        <v>-36.26</v>
       </c>
       <c r="K32" t="n">
-        <v>59.82</v>
+        <v>82.09</v>
       </c>
       <c r="L32" t="n">
-        <v>59.92</v>
+        <v>89.73999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:30:15</t>
+          <t>05:29:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="F33" t="n">
-        <v>6.07</v>
+        <v>3.36</v>
       </c>
       <c r="G33" t="n">
-        <v>242.5</v>
+        <v>245.5</v>
       </c>
       <c r="H33" t="n">
-        <v>25.6</v>
+        <v>15.4</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>59.16</v>
+        <v>-53.8</v>
       </c>
       <c r="K33" t="n">
-        <v>2.82</v>
+        <v>35.22</v>
       </c>
       <c r="L33" t="n">
-        <v>59.23</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:31:34</t>
+          <t>05:31:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="F34" t="n">
-        <v>5.54</v>
+        <v>4.09</v>
       </c>
       <c r="G34" t="n">
-        <v>243</v>
+        <v>249.4</v>
       </c>
       <c r="H34" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="I34" t="n">
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-30.28</v>
+        <v>8.93</v>
       </c>
       <c r="K34" t="n">
-        <v>70.39</v>
+        <v>-6.71</v>
       </c>
       <c r="L34" t="n">
-        <v>76.63</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:35:34</t>
+          <t>05:34:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="F35" t="n">
-        <v>5.13</v>
+        <v>5.26</v>
       </c>
       <c r="G35" t="n">
-        <v>233.2</v>
+        <v>254.2</v>
       </c>
       <c r="H35" t="n">
         <v>22.3</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-70.97</v>
+        <v>-89.8</v>
       </c>
       <c r="K35" t="n">
-        <v>46.17</v>
+        <v>-23.92</v>
       </c>
       <c r="L35" t="n">
-        <v>84.66</v>
+        <v>92.93000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:37:36</t>
+          <t>05:36:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="F36" t="n">
-        <v>5.33</v>
+        <v>5.03</v>
       </c>
       <c r="G36" t="n">
-        <v>251.6</v>
+        <v>246.5</v>
       </c>
       <c r="H36" t="n">
-        <v>21.9</v>
+        <v>29.4</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>10.95</v>
+        <v>-51.55</v>
       </c>
       <c r="K36" t="n">
-        <v>-8.039999999999999</v>
+        <v>-87.84999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>13.58</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:39:57</t>
+          <t>05:38:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="F37" t="n">
-        <v>5.57</v>
+        <v>3.32</v>
       </c>
       <c r="G37" t="n">
-        <v>247</v>
+        <v>252.5</v>
       </c>
       <c r="H37" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-72.98</v>
+        <v>-49.69</v>
       </c>
       <c r="K37" t="n">
-        <v>-19.73</v>
+        <v>73.08</v>
       </c>
       <c r="L37" t="n">
-        <v>75.59999999999999</v>
+        <v>88.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:44:21</t>
+          <t>05:42:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.97</v>
+        <v>1.43</v>
       </c>
       <c r="F38" t="n">
-        <v>5.19</v>
+        <v>1.79</v>
       </c>
       <c r="G38" t="n">
-        <v>261.2</v>
+        <v>259.6</v>
       </c>
       <c r="H38" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="I38" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-49.05</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-86.03</v>
+        <v>0.23</v>
       </c>
       <c r="L38" t="n">
-        <v>99.02</v>
+        <v>74.51000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:46:17</t>
+          <t>05:45:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="F39" t="n">
-        <v>5.49</v>
+        <v>6.09</v>
       </c>
       <c r="G39" t="n">
-        <v>251.3</v>
+        <v>242.2</v>
       </c>
       <c r="H39" t="n">
-        <v>33.6</v>
+        <v>26.9</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-59.26</v>
+        <v>-32.78</v>
       </c>
       <c r="K39" t="n">
-        <v>93.58</v>
+        <v>-127.76</v>
       </c>
       <c r="L39" t="n">
-        <v>110.77</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:48:18</t>
+          <t>05:46:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="F40" t="n">
-        <v>5.84</v>
+        <v>4.48</v>
       </c>
       <c r="G40" t="n">
-        <v>246.8</v>
+        <v>246.2</v>
       </c>
       <c r="H40" t="n">
-        <v>18.1</v>
+        <v>20.2</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>69.67</v>
+        <v>-59.23</v>
       </c>
       <c r="K40" t="n">
-        <v>1.29</v>
+        <v>110.73</v>
       </c>
       <c r="L40" t="n">
-        <v>69.68000000000001</v>
+        <v>125.58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:53:50</t>
+          <t>05:51:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="F41" t="n">
-        <v>4.97</v>
+        <v>5.35</v>
       </c>
       <c r="G41" t="n">
-        <v>256.2</v>
+        <v>261.8</v>
       </c>
       <c r="H41" t="n">
-        <v>22.4</v>
+        <v>19.9</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-27.56</v>
+        <v>-11.81</v>
       </c>
       <c r="K41" t="n">
-        <v>-144.37</v>
+        <v>267.55</v>
       </c>
       <c r="L41" t="n">
-        <v>146.97</v>
+        <v>267.81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:55:00</t>
+          <t>05:52:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="F42" t="n">
-        <v>5.17</v>
+        <v>3.33</v>
       </c>
       <c r="G42" t="n">
-        <v>242.7</v>
+        <v>267.3</v>
       </c>
       <c r="H42" t="n">
-        <v>23.7</v>
+        <v>22.3</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-60.87</v>
+        <v>-149.39</v>
       </c>
       <c r="K42" t="n">
-        <v>137.75</v>
+        <v>-123.2</v>
       </c>
       <c r="L42" t="n">
-        <v>150.6</v>
+        <v>193.64</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:57:05</t>
+          <t>05:53:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="F43" t="n">
-        <v>5.95</v>
+        <v>4.61</v>
       </c>
       <c r="G43" t="n">
-        <v>242.2</v>
+        <v>262.6</v>
       </c>
       <c r="H43" t="n">
-        <v>24.2</v>
+        <v>18.7</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>7.73</v>
+        <v>-26.9</v>
       </c>
       <c r="K43" t="n">
-        <v>234.94</v>
+        <v>220.9</v>
       </c>
       <c r="L43" t="n">
-        <v>235.07</v>
+        <v>222.53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:08:18</t>
+          <t>06:01:49</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="F44" t="n">
-        <v>6.22</v>
+        <v>5.91</v>
       </c>
       <c r="G44" t="n">
-        <v>247</v>
+        <v>246.5</v>
       </c>
       <c r="H44" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-27.33</v>
+        <v>-45.79</v>
       </c>
       <c r="K44" t="n">
-        <v>-28.35</v>
+        <v>-52.39</v>
       </c>
       <c r="L44" t="n">
-        <v>39.38</v>
+        <v>69.58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:10:12</t>
+          <t>06:02:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="F45" t="n">
-        <v>5.99</v>
+        <v>6.09</v>
       </c>
       <c r="G45" t="n">
-        <v>239.8</v>
+        <v>245.9</v>
       </c>
       <c r="H45" t="n">
-        <v>15.7</v>
+        <v>30.1</v>
       </c>
       <c r="I45" t="n">
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>1.45</v>
+        <v>38.84</v>
       </c>
       <c r="K45" t="n">
-        <v>50.98</v>
+        <v>42.87</v>
       </c>
       <c r="L45" t="n">
-        <v>51</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:12:37</t>
+          <t>06:03:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.09</v>
+        <v>1.59</v>
       </c>
       <c r="F46" t="n">
-        <v>5.19</v>
+        <v>2.96</v>
       </c>
       <c r="G46" t="n">
-        <v>244.1</v>
+        <v>249.7</v>
       </c>
       <c r="H46" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-42.78</v>
+        <v>-47.17</v>
       </c>
       <c r="K46" t="n">
-        <v>-49.18</v>
+        <v>-15.09</v>
       </c>
       <c r="L46" t="n">
-        <v>65.18000000000001</v>
+        <v>49.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:17:24</t>
+          <t>06:08:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="F47" t="n">
-        <v>5.15</v>
+        <v>4.79</v>
       </c>
       <c r="G47" t="n">
-        <v>262.7</v>
+        <v>260.1</v>
       </c>
       <c r="H47" t="n">
-        <v>20.3</v>
+        <v>20.8</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>49.82</v>
+        <v>57.53</v>
       </c>
       <c r="K47" t="n">
-        <v>55.31</v>
+        <v>3.33</v>
       </c>
       <c r="L47" t="n">
-        <v>74.44</v>
+        <v>57.62</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:18:39</t>
+          <t>06:10:02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="F48" t="n">
-        <v>5.34</v>
+        <v>4.55</v>
       </c>
       <c r="G48" t="n">
-        <v>247.8</v>
+        <v>244.6</v>
       </c>
       <c r="H48" t="n">
-        <v>19.6</v>
+        <v>23.2</v>
       </c>
       <c r="I48" t="n">
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-70.81999999999999</v>
+        <v>16.38</v>
       </c>
       <c r="K48" t="n">
-        <v>-22.68</v>
+        <v>84.62</v>
       </c>
       <c r="L48" t="n">
-        <v>74.36</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:20:29</t>
+          <t>06:11:13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="F49" t="n">
-        <v>5.86</v>
+        <v>6.09</v>
       </c>
       <c r="G49" t="n">
-        <v>243.9</v>
+        <v>260.6</v>
       </c>
       <c r="H49" t="n">
-        <v>19.5</v>
+        <v>31.2</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>51.49</v>
+        <v>46.57</v>
       </c>
       <c r="K49" t="n">
-        <v>2.71</v>
+        <v>-41.33</v>
       </c>
       <c r="L49" t="n">
-        <v>51.56</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:23:50</t>
+          <t>06:15:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="F50" t="n">
-        <v>5.09</v>
+        <v>6.09</v>
       </c>
       <c r="G50" t="n">
-        <v>248.8</v>
+        <v>249.4</v>
       </c>
       <c r="H50" t="n">
-        <v>21.8</v>
+        <v>26.8</v>
       </c>
       <c r="I50" t="n">
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>21.24</v>
+        <v>-30.77</v>
       </c>
       <c r="K50" t="n">
-        <v>110.21</v>
+        <v>-108.55</v>
       </c>
       <c r="L50" t="n">
-        <v>112.24</v>
+        <v>112.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:25:21</t>
+          <t>06:16:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="F51" t="n">
-        <v>5.89</v>
+        <v>4.27</v>
       </c>
       <c r="G51" t="n">
-        <v>264.9</v>
+        <v>245.2</v>
       </c>
       <c r="H51" t="n">
-        <v>22.4</v>
+        <v>21</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>59.94</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-52.94</v>
+        <v>-23.6</v>
       </c>
       <c r="L51" t="n">
-        <v>79.97</v>
+        <v>70.56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:27:26</t>
+          <t>06:18:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="F52" t="n">
-        <v>5.33</v>
+        <v>4.56</v>
       </c>
       <c r="G52" t="n">
-        <v>256</v>
+        <v>236.4</v>
       </c>
       <c r="H52" t="n">
-        <v>27.7</v>
+        <v>17.4</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-23.81</v>
+        <v>84</v>
       </c>
       <c r="K52" t="n">
-        <v>-94.54000000000001</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>97.48999999999999</v>
+        <v>114.32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:32:06</t>
+          <t>06:23:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="F53" t="n">
-        <v>5.12</v>
+        <v>3.37</v>
       </c>
       <c r="G53" t="n">
-        <v>244.5</v>
+        <v>259.4</v>
       </c>
       <c r="H53" t="n">
-        <v>23.8</v>
+        <v>20.8</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>77.83</v>
+        <v>-111.89</v>
       </c>
       <c r="K53" t="n">
-        <v>-22.64</v>
+        <v>-34.02</v>
       </c>
       <c r="L53" t="n">
-        <v>81.06</v>
+        <v>116.95</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:33:24</t>
+          <t>06:24:57</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="F54" t="n">
-        <v>4.68</v>
+        <v>5.67</v>
       </c>
       <c r="G54" t="n">
-        <v>237.1</v>
+        <v>251.9</v>
       </c>
       <c r="H54" t="n">
-        <v>21.5</v>
+        <v>24.8</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>96.01000000000001</v>
+        <v>-104.71</v>
       </c>
       <c r="K54" t="n">
-        <v>88.06</v>
+        <v>-76.13</v>
       </c>
       <c r="L54" t="n">
-        <v>130.28</v>
+        <v>129.46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:35:33</t>
+          <t>06:25:58</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="F55" t="n">
-        <v>5.83</v>
+        <v>4.4</v>
       </c>
       <c r="G55" t="n">
-        <v>244.1</v>
+        <v>251</v>
       </c>
       <c r="H55" t="n">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-93.64</v>
+        <v>-158.87</v>
       </c>
       <c r="K55" t="n">
-        <v>-31.21</v>
+        <v>-25.86</v>
       </c>
       <c r="L55" t="n">
-        <v>98.70999999999999</v>
+        <v>160.96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:40:48</t>
+          <t>06:30:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="F56" t="n">
-        <v>5.46</v>
+        <v>2.72</v>
       </c>
       <c r="G56" t="n">
-        <v>252</v>
+        <v>242.8</v>
       </c>
       <c r="H56" t="n">
-        <v>23.5</v>
+        <v>25.8</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-121.61</v>
+        <v>-156.63</v>
       </c>
       <c r="K56" t="n">
-        <v>-94.84999999999999</v>
+        <v>-31.75</v>
       </c>
       <c r="L56" t="n">
-        <v>154.22</v>
+        <v>159.82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:42:37</t>
+          <t>06:32:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="F57" t="n">
-        <v>5.41</v>
+        <v>3.94</v>
       </c>
       <c r="G57" t="n">
-        <v>237.8</v>
+        <v>252.7</v>
       </c>
       <c r="H57" t="n">
-        <v>26.5</v>
+        <v>18.5</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-188.39</v>
+        <v>-197.63</v>
       </c>
       <c r="K57" t="n">
-        <v>-30.95</v>
+        <v>97.23</v>
       </c>
       <c r="L57" t="n">
-        <v>190.91</v>
+        <v>220.26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:44:08</t>
+          <t>06:33:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>6.09</v>
       </c>
       <c r="G58" t="n">
-        <v>254.1</v>
+        <v>258.1</v>
       </c>
       <c r="H58" t="n">
-        <v>15.7</v>
+        <v>24.5</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-138.99</v>
+        <v>183.25</v>
       </c>
       <c r="K58" t="n">
-        <v>-14.29</v>
+        <v>16.09</v>
       </c>
       <c r="L58" t="n">
-        <v>139.72</v>
+        <v>183.95</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:56:33</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.73</v>
+        <v>2.37</v>
       </c>
       <c r="F59" t="n">
-        <v>5.5</v>
+        <v>6.09</v>
       </c>
       <c r="G59" t="n">
-        <v>239.4</v>
+        <v>248.4</v>
       </c>
       <c r="H59" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-39.14</v>
+        <v>-36.51</v>
       </c>
       <c r="K59" t="n">
-        <v>23.72</v>
+        <v>-72.28</v>
       </c>
       <c r="L59" t="n">
-        <v>45.77</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:58:52</t>
+          <t>06:45:50</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="F60" t="n">
-        <v>5.77</v>
+        <v>3.38</v>
       </c>
       <c r="G60" t="n">
-        <v>251.4</v>
+        <v>252</v>
       </c>
       <c r="H60" t="n">
-        <v>26.3</v>
+        <v>30.8</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>37.24</v>
+        <v>-51.62</v>
       </c>
       <c r="K60" t="n">
-        <v>4.32</v>
+        <v>-0.05</v>
       </c>
       <c r="L60" t="n">
-        <v>37.49</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:00:47</t>
+          <t>06:47:09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="F61" t="n">
-        <v>5.28</v>
+        <v>6.09</v>
       </c>
       <c r="G61" t="n">
-        <v>243.7</v>
+        <v>242</v>
       </c>
       <c r="H61" t="n">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="I61" t="n">
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-29.39</v>
+        <v>59.07</v>
       </c>
       <c r="K61" t="n">
-        <v>-58.78</v>
+        <v>6.73</v>
       </c>
       <c r="L61" t="n">
-        <v>65.72</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:04:17</t>
+          <t>06:52:05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="F62" t="n">
-        <v>5.46</v>
+        <v>3.48</v>
       </c>
       <c r="G62" t="n">
-        <v>264</v>
+        <v>252.5</v>
       </c>
       <c r="H62" t="n">
-        <v>20.6</v>
+        <v>23.4</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-55.9</v>
+        <v>-40.77</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1</v>
+        <v>-43.71</v>
       </c>
       <c r="L62" t="n">
-        <v>55.9</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:05:28</t>
+          <t>06:54:21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="F63" t="n">
-        <v>4.96</v>
+        <v>6.09</v>
       </c>
       <c r="G63" t="n">
-        <v>241.1</v>
+        <v>248.8</v>
       </c>
       <c r="H63" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>61.07</v>
+        <v>-19.52</v>
       </c>
       <c r="K63" t="n">
-        <v>6.95</v>
+        <v>53.12</v>
       </c>
       <c r="L63" t="n">
-        <v>61.46</v>
+        <v>56.59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:07:48</t>
+          <t>06:56:29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="F64" t="n">
-        <v>5.49</v>
+        <v>4.82</v>
       </c>
       <c r="G64" t="n">
-        <v>249.2</v>
+        <v>245.3</v>
       </c>
       <c r="H64" t="n">
-        <v>19.3</v>
+        <v>21.9</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-31.73</v>
+        <v>-71.42</v>
       </c>
       <c r="K64" t="n">
-        <v>-34.87</v>
+        <v>61.38</v>
       </c>
       <c r="L64" t="n">
-        <v>47.15</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:10:53</t>
+          <t>07:01:15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="F65" t="n">
-        <v>5.3</v>
+        <v>6.09</v>
       </c>
       <c r="G65" t="n">
-        <v>244</v>
+        <v>240.5</v>
       </c>
       <c r="H65" t="n">
-        <v>22.1</v>
+        <v>19.5</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-20.45</v>
+        <v>60.5</v>
       </c>
       <c r="K65" t="n">
-        <v>55.86</v>
+        <v>-64.5</v>
       </c>
       <c r="L65" t="n">
-        <v>59.49</v>
+        <v>88.44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:12:48</t>
+          <t>07:03:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="F66" t="n">
-        <v>5.12</v>
+        <v>5.05</v>
       </c>
       <c r="G66" t="n">
-        <v>246.3</v>
+        <v>247.4</v>
       </c>
       <c r="H66" t="n">
-        <v>22.5</v>
+        <v>27.9</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-88.68000000000001</v>
+        <v>-36.3</v>
       </c>
       <c r="K66" t="n">
-        <v>76.23</v>
+        <v>-145.47</v>
       </c>
       <c r="L66" t="n">
-        <v>116.95</v>
+        <v>149.93</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:13:50</t>
+          <t>07:04:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="F67" t="n">
-        <v>4.89</v>
+        <v>3.88</v>
       </c>
       <c r="G67" t="n">
-        <v>241.5</v>
+        <v>235.8</v>
       </c>
       <c r="H67" t="n">
-        <v>20.4</v>
+        <v>13.9</v>
       </c>
       <c r="I67" t="n">
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>54.28</v>
+        <v>36.44</v>
       </c>
       <c r="K67" t="n">
-        <v>-49.91</v>
+        <v>-92.66</v>
       </c>
       <c r="L67" t="n">
-        <v>73.73</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:18:33</t>
+          <t>07:08:04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="F68" t="n">
-        <v>5.23</v>
+        <v>3.02</v>
       </c>
       <c r="G68" t="n">
-        <v>258.1</v>
+        <v>247.5</v>
       </c>
       <c r="H68" t="n">
-        <v>21.7</v>
+        <v>15.2</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-41.8</v>
+        <v>48.16</v>
       </c>
       <c r="K68" t="n">
-        <v>-174.8</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>179.72</v>
+        <v>103.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:20:48</t>
+          <t>07:09:29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="F69" t="n">
-        <v>4.65</v>
+        <v>4.21</v>
       </c>
       <c r="G69" t="n">
-        <v>230.1</v>
+        <v>243.5</v>
       </c>
       <c r="H69" t="n">
-        <v>21.3</v>
+        <v>22.4</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>41.42</v>
+        <v>121.06</v>
       </c>
       <c r="K69" t="n">
-        <v>-97.23</v>
+        <v>30.61</v>
       </c>
       <c r="L69" t="n">
-        <v>105.68</v>
+        <v>124.87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:22:45</t>
+          <t>07:10:42</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="F70" t="n">
-        <v>5.24</v>
+        <v>3.93</v>
       </c>
       <c r="G70" t="n">
-        <v>232.8</v>
+        <v>242.7</v>
       </c>
       <c r="H70" t="n">
-        <v>18.4</v>
+        <v>21.5</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>50.08</v>
+        <v>-81.67</v>
       </c>
       <c r="K70" t="n">
-        <v>77.48999999999999</v>
+        <v>-101.13</v>
       </c>
       <c r="L70" t="n">
-        <v>92.26000000000001</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:28:13</t>
+          <t>07:14:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="F71" t="n">
-        <v>5.04</v>
+        <v>5.8</v>
       </c>
       <c r="G71" t="n">
-        <v>247.1</v>
+        <v>245.1</v>
       </c>
       <c r="H71" t="n">
-        <v>22.9</v>
+        <v>20.5</v>
       </c>
       <c r="I71" t="n">
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>143.17</v>
+        <v>-226.12</v>
       </c>
       <c r="K71" t="n">
-        <v>39.34</v>
+        <v>11.29</v>
       </c>
       <c r="L71" t="n">
-        <v>148.47</v>
+        <v>226.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:29:50</t>
+          <t>07:16:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="F72" t="n">
-        <v>4.99</v>
+        <v>6.07</v>
       </c>
       <c r="G72" t="n">
-        <v>245.4</v>
+        <v>235.9</v>
       </c>
       <c r="H72" t="n">
-        <v>21.4</v>
+        <v>24.9</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-106.11</v>
+        <v>111.32</v>
       </c>
       <c r="K72" t="n">
-        <v>-137.46</v>
+        <v>-197.47</v>
       </c>
       <c r="L72" t="n">
-        <v>173.65</v>
+        <v>226.69</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:31:56</t>
+          <t>07:17:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="F73" t="n">
-        <v>5.11</v>
+        <v>2.79</v>
       </c>
       <c r="G73" t="n">
-        <v>243.5</v>
+        <v>246</v>
       </c>
       <c r="H73" t="n">
-        <v>26</v>
+        <v>24.7</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-169.85</v>
+        <v>-187.72</v>
       </c>
       <c r="K73" t="n">
-        <v>18.3</v>
+        <v>12.06</v>
       </c>
       <c r="L73" t="n">
-        <v>170.83</v>
+        <v>188.11</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:43:37</t>
+          <t>07:25:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="F74" t="n">
-        <v>4.66</v>
+        <v>5.05</v>
       </c>
       <c r="G74" t="n">
-        <v>252.1</v>
+        <v>237.7</v>
       </c>
       <c r="H74" t="n">
-        <v>25.4</v>
+        <v>23.4</v>
       </c>
       <c r="I74" t="n">
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>26.35</v>
+        <v>13.07</v>
       </c>
       <c r="K74" t="n">
-        <v>-32.78</v>
+        <v>-31.98</v>
       </c>
       <c r="L74" t="n">
-        <v>42.05</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:44:46</t>
+          <t>07:25:36</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="F75" t="n">
-        <v>5.16</v>
+        <v>6.09</v>
       </c>
       <c r="G75" t="n">
-        <v>251.8</v>
+        <v>253.8</v>
       </c>
       <c r="H75" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-38.73</v>
+        <v>-42.71</v>
       </c>
       <c r="K75" t="n">
-        <v>6.91</v>
+        <v>-14.42</v>
       </c>
       <c r="L75" t="n">
-        <v>39.35</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:46:11</t>
+          <t>07:28:09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3232,31 +3232,31 @@
         <v>1.83</v>
       </c>
       <c r="F76" t="n">
-        <v>4.74</v>
+        <v>6.09</v>
       </c>
       <c r="G76" t="n">
-        <v>249.3</v>
+        <v>255.8</v>
       </c>
       <c r="H76" t="n">
-        <v>22.5</v>
+        <v>23.7</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>11.81</v>
+        <v>32.01</v>
       </c>
       <c r="K76" t="n">
-        <v>-27.14</v>
+        <v>37.48</v>
       </c>
       <c r="L76" t="n">
-        <v>29.6</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:50:39</t>
+          <t>07:33:08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="F77" t="n">
-        <v>5.55</v>
+        <v>6.09</v>
       </c>
       <c r="G77" t="n">
-        <v>258</v>
+        <v>251.2</v>
       </c>
       <c r="H77" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-39.94</v>
+        <v>25.03</v>
       </c>
       <c r="K77" t="n">
-        <v>-13.38</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>42.12</v>
+        <v>78.16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:51:36</t>
+          <t>07:33:48</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="F78" t="n">
-        <v>5.65</v>
+        <v>4.11</v>
       </c>
       <c r="G78" t="n">
-        <v>249.8</v>
+        <v>249.3</v>
       </c>
       <c r="H78" t="n">
-        <v>26.4</v>
+        <v>23.5</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>35.38</v>
+        <v>34.47</v>
       </c>
       <c r="K78" t="n">
-        <v>41.28</v>
+        <v>-51.13</v>
       </c>
       <c r="L78" t="n">
-        <v>54.37</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:53:33</t>
+          <t>07:36:20</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="F79" t="n">
-        <v>5.42</v>
+        <v>4.72</v>
       </c>
       <c r="G79" t="n">
-        <v>250.4</v>
+        <v>245.5</v>
       </c>
       <c r="H79" t="n">
-        <v>19.6</v>
+        <v>27.8</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>19.42</v>
+        <v>56.54</v>
       </c>
       <c r="K79" t="n">
-        <v>-54.1</v>
+        <v>-30.94</v>
       </c>
       <c r="L79" t="n">
-        <v>57.49</v>
+        <v>64.45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:57:17</t>
+          <t>07:41:32</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="F80" t="n">
-        <v>5.33</v>
+        <v>6.09</v>
       </c>
       <c r="G80" t="n">
-        <v>249.5</v>
+        <v>235</v>
       </c>
       <c r="H80" t="n">
-        <v>20.3</v>
+        <v>32.8</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>42.49</v>
+        <v>-22.83</v>
       </c>
       <c r="K80" t="n">
-        <v>-63.03</v>
+        <v>140.37</v>
       </c>
       <c r="L80" t="n">
-        <v>76.01000000000001</v>
+        <v>142.21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:58:09</t>
+          <t>07:42:49</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="F81" t="n">
-        <v>4.91</v>
+        <v>5.19</v>
       </c>
       <c r="G81" t="n">
-        <v>239.4</v>
+        <v>242.5</v>
       </c>
       <c r="H81" t="n">
-        <v>31.9</v>
+        <v>19.9</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-26.95</v>
+        <v>-67.95999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-81.98999999999999</v>
+        <v>-32.5</v>
       </c>
       <c r="L81" t="n">
-        <v>86.31</v>
+        <v>75.33</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:00:38</t>
+          <t>07:44:51</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="F82" t="n">
-        <v>5.41</v>
+        <v>6.09</v>
       </c>
       <c r="G82" t="n">
-        <v>256.3</v>
+        <v>246.4</v>
       </c>
       <c r="H82" t="n">
-        <v>25.8</v>
+        <v>18.8</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-98.25</v>
+        <v>-88.88</v>
       </c>
       <c r="K82" t="n">
-        <v>-45.97</v>
+        <v>20.78</v>
       </c>
       <c r="L82" t="n">
-        <v>108.47</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:05:42</t>
+          <t>07:49:32</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="F83" t="n">
-        <v>5.03</v>
+        <v>6.09</v>
       </c>
       <c r="G83" t="n">
-        <v>242.4</v>
+        <v>247.2</v>
       </c>
       <c r="H83" t="n">
-        <v>28.4</v>
+        <v>25.9</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-57.96</v>
+        <v>-115.07</v>
       </c>
       <c r="K83" t="n">
-        <v>100.24</v>
+        <v>-37.49</v>
       </c>
       <c r="L83" t="n">
-        <v>115.79</v>
+        <v>121.03</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:07:15</t>
+          <t>07:50:30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="F84" t="n">
-        <v>4.86</v>
+        <v>4.66</v>
       </c>
       <c r="G84" t="n">
-        <v>249.2</v>
+        <v>245</v>
       </c>
       <c r="H84" t="n">
-        <v>16.5</v>
+        <v>26.9</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-69.66</v>
+        <v>-75.67</v>
       </c>
       <c r="K84" t="n">
-        <v>-69.61</v>
+        <v>109.95</v>
       </c>
       <c r="L84" t="n">
-        <v>98.48</v>
+        <v>133.47</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:09:22</t>
+          <t>07:51:41</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="F85" t="n">
-        <v>5.22</v>
+        <v>3.56</v>
       </c>
       <c r="G85" t="n">
-        <v>254.3</v>
+        <v>250.1</v>
       </c>
       <c r="H85" t="n">
-        <v>19.7</v>
+        <v>28.8</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-100.53</v>
+        <v>-81.55</v>
       </c>
       <c r="K85" t="n">
-        <v>-30.29</v>
+        <v>35.5</v>
       </c>
       <c r="L85" t="n">
-        <v>104.99</v>
+        <v>88.94</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:14:40</t>
+          <t>07:56:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="F86" t="n">
-        <v>5.11</v>
+        <v>3.84</v>
       </c>
       <c r="G86" t="n">
-        <v>256.2</v>
+        <v>255.3</v>
       </c>
       <c r="H86" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-89.65000000000001</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>157.79</v>
+        <v>115.11</v>
       </c>
       <c r="L86" t="n">
-        <v>181.48</v>
+        <v>135.16</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:16:56</t>
+          <t>07:58:34</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="F87" t="n">
-        <v>5.37</v>
+        <v>6.09</v>
       </c>
       <c r="G87" t="n">
-        <v>260</v>
+        <v>245.1</v>
       </c>
       <c r="H87" t="n">
-        <v>22</v>
+        <v>25.4</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-96.15000000000001</v>
+        <v>-177.36</v>
       </c>
       <c r="K87" t="n">
-        <v>64.97</v>
+        <v>-37</v>
       </c>
       <c r="L87" t="n">
-        <v>116.04</v>
+        <v>181.18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:19:21</t>
+          <t>08:01:16</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="F88" t="n">
-        <v>5.63</v>
+        <v>5.5</v>
       </c>
       <c r="G88" t="n">
-        <v>242.4</v>
+        <v>253.2</v>
       </c>
       <c r="H88" t="n">
-        <v>16.6</v>
+        <v>23.3</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>88.64</v>
+        <v>-18.04</v>
       </c>
       <c r="K88" t="n">
-        <v>84.47</v>
+        <v>-187.35</v>
       </c>
       <c r="L88" t="n">
-        <v>122.44</v>
+        <v>188.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-47.42</v>
+        <v>-50.93</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.22</v>
+        <v>-3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>47.53</v>
+        <v>51.05</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-33.67</v>
+        <v>-34.96</v>
       </c>
       <c r="K16" t="n">
-        <v>-26.39</v>
+        <v>-27.41</v>
       </c>
       <c r="L16" t="n">
-        <v>42.78</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="17">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-65.79000000000001</v>
+        <v>-64.44</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.68</v>
+        <v>-9.48</v>
       </c>
       <c r="L18" t="n">
-        <v>66.48999999999999</v>
+        <v>65.14</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-58.72</v>
+        <v>-57.52</v>
       </c>
       <c r="K19" t="n">
-        <v>39.31</v>
+        <v>38.51</v>
       </c>
       <c r="L19" t="n">
-        <v>70.66</v>
+        <v>69.22</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>61.52</v>
+        <v>66.08</v>
       </c>
       <c r="K20" t="n">
-        <v>87.59</v>
+        <v>94.08</v>
       </c>
       <c r="L20" t="n">
-        <v>107.04</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>73.45</v>
+        <v>76.27</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.84</v>
+        <v>-14.37</v>
       </c>
       <c r="L21" t="n">
-        <v>74.73999999999999</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-66.13</v>
+        <v>-69.87</v>
       </c>
       <c r="K22" t="n">
-        <v>-81.16</v>
+        <v>-85.76000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>104.69</v>
+        <v>110.62</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>103.13</v>
+        <v>107.1</v>
       </c>
       <c r="K23" t="n">
-        <v>-42.21</v>
+        <v>-43.83</v>
       </c>
       <c r="L23" t="n">
-        <v>111.43</v>
+        <v>115.72</v>
       </c>
     </row>
     <row r="24">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>122.05</v>
+        <v>124.44</v>
       </c>
       <c r="K26" t="n">
-        <v>155.29</v>
+        <v>158.34</v>
       </c>
       <c r="L26" t="n">
-        <v>197.51</v>
+        <v>201.39</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-114.44</v>
+        <v>-116.69</v>
       </c>
       <c r="K27" t="n">
-        <v>147.26</v>
+        <v>150.15</v>
       </c>
       <c r="L27" t="n">
-        <v>186.5</v>
+        <v>190.16</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-45.32</v>
+        <v>-44.4</v>
       </c>
       <c r="K28" t="n">
-        <v>262.85</v>
+        <v>257.48</v>
       </c>
       <c r="L28" t="n">
-        <v>266.73</v>
+        <v>261.28</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-47.86</v>
+        <v>-49.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.32</v>
+        <v>-37.71</v>
       </c>
       <c r="L29" t="n">
-        <v>60.08</v>
+        <v>62.39</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.83</v>
+        <v>-2.78</v>
       </c>
       <c r="K30" t="n">
-        <v>47.22</v>
+        <v>46.26</v>
       </c>
       <c r="L30" t="n">
-        <v>47.31</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>54.77</v>
+        <v>59.75</v>
       </c>
       <c r="K31" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="L31" t="n">
-        <v>54.84</v>
+        <v>59.83</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-36.26</v>
+        <v>-35.52</v>
       </c>
       <c r="K32" t="n">
-        <v>82.09</v>
+        <v>80.41</v>
       </c>
       <c r="L32" t="n">
-        <v>89.73999999999999</v>
+        <v>87.91</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-53.8</v>
+        <v>-55.87</v>
       </c>
       <c r="K33" t="n">
-        <v>35.22</v>
+        <v>36.57</v>
       </c>
       <c r="L33" t="n">
-        <v>64.3</v>
+        <v>66.77</v>
       </c>
     </row>
     <row r="34">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-51.55</v>
+        <v>-54.47</v>
       </c>
       <c r="K36" t="n">
-        <v>-87.84999999999999</v>
+        <v>-92.81999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>101.86</v>
+        <v>107.62</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-49.69</v>
+        <v>-50.67</v>
       </c>
       <c r="K37" t="n">
-        <v>73.08</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>88.37</v>
+        <v>90.11</v>
       </c>
     </row>
     <row r="38">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-32.78</v>
+        <v>-34.04</v>
       </c>
       <c r="K39" t="n">
-        <v>-127.76</v>
+        <v>-132.68</v>
       </c>
       <c r="L39" t="n">
-        <v>131.9</v>
+        <v>136.97</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-59.23</v>
+        <v>-62.58</v>
       </c>
       <c r="K40" t="n">
-        <v>110.73</v>
+        <v>117</v>
       </c>
       <c r="L40" t="n">
-        <v>125.58</v>
+        <v>132.69</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.81</v>
+        <v>-12.05</v>
       </c>
       <c r="K41" t="n">
-        <v>267.55</v>
+        <v>272.79</v>
       </c>
       <c r="L41" t="n">
-        <v>267.81</v>
+        <v>273.06</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-149.39</v>
+        <v>-157.84</v>
       </c>
       <c r="K42" t="n">
-        <v>-123.2</v>
+        <v>-130.18</v>
       </c>
       <c r="L42" t="n">
-        <v>193.64</v>
+        <v>204.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-26.9</v>
+        <v>-27.94</v>
       </c>
       <c r="K43" t="n">
-        <v>220.9</v>
+        <v>229.4</v>
       </c>
       <c r="L43" t="n">
-        <v>222.53</v>
+        <v>231.09</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-45.79</v>
+        <v>-48.38</v>
       </c>
       <c r="K44" t="n">
-        <v>-52.39</v>
+        <v>-55.36</v>
       </c>
       <c r="L44" t="n">
-        <v>69.58</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>38.84</v>
+        <v>38.05</v>
       </c>
       <c r="K45" t="n">
-        <v>42.87</v>
+        <v>41.99</v>
       </c>
       <c r="L45" t="n">
-        <v>57.85</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="46">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>57.53</v>
+        <v>61.79</v>
       </c>
       <c r="K47" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="L47" t="n">
-        <v>57.62</v>
+        <v>61.89</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>16.38</v>
+        <v>17.31</v>
       </c>
       <c r="K48" t="n">
-        <v>84.62</v>
+        <v>89.42</v>
       </c>
       <c r="L48" t="n">
-        <v>86.2</v>
+        <v>91.06999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>66.48999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-23.6</v>
+        <v>-24.51</v>
       </c>
       <c r="L51" t="n">
-        <v>70.56</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>84</v>
+        <v>88.75</v>
       </c>
       <c r="K52" t="n">
-        <v>77.54000000000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>114.32</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-111.89</v>
+        <v>-118.23</v>
       </c>
       <c r="K53" t="n">
-        <v>-34.02</v>
+        <v>-35.95</v>
       </c>
       <c r="L53" t="n">
-        <v>116.95</v>
+        <v>123.57</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>-104.71</v>
+        <v>-114.23</v>
       </c>
       <c r="K54" t="n">
-        <v>-76.13</v>
+        <v>-83.05</v>
       </c>
       <c r="L54" t="n">
-        <v>129.46</v>
+        <v>141.23</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-158.87</v>
+        <v>-173.31</v>
       </c>
       <c r="K55" t="n">
-        <v>-25.86</v>
+        <v>-28.22</v>
       </c>
       <c r="L55" t="n">
-        <v>160.96</v>
+        <v>175.59</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-156.63</v>
+        <v>-162.66</v>
       </c>
       <c r="K56" t="n">
-        <v>-31.75</v>
+        <v>-32.97</v>
       </c>
       <c r="L56" t="n">
-        <v>159.82</v>
+        <v>165.96</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-197.63</v>
+        <v>-201.51</v>
       </c>
       <c r="K57" t="n">
-        <v>97.23</v>
+        <v>99.14</v>
       </c>
       <c r="L57" t="n">
-        <v>220.26</v>
+        <v>224.58</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>183.25</v>
+        <v>199.91</v>
       </c>
       <c r="K58" t="n">
-        <v>16.09</v>
+        <v>17.56</v>
       </c>
       <c r="L58" t="n">
-        <v>183.95</v>
+        <v>200.68</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-36.51</v>
+        <v>-39.83</v>
       </c>
       <c r="K59" t="n">
-        <v>-72.28</v>
+        <v>-78.84999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>80.98</v>
+        <v>88.34</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-51.62</v>
+        <v>-55.44</v>
       </c>
       <c r="K60" t="n">
         <v>-0.05</v>
       </c>
       <c r="L60" t="n">
-        <v>51.62</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>59.07</v>
+        <v>60.23</v>
       </c>
       <c r="K61" t="n">
-        <v>6.73</v>
+        <v>6.86</v>
       </c>
       <c r="L61" t="n">
-        <v>59.45</v>
+        <v>60.62</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-40.77</v>
+        <v>-42.34</v>
       </c>
       <c r="K62" t="n">
-        <v>-43.71</v>
+        <v>-45.39</v>
       </c>
       <c r="L62" t="n">
-        <v>59.77</v>
+        <v>62.07</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-19.52</v>
+        <v>-20.63</v>
       </c>
       <c r="K63" t="n">
-        <v>53.12</v>
+        <v>56.13</v>
       </c>
       <c r="L63" t="n">
-        <v>56.59</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-71.42</v>
+        <v>-75.45999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>61.38</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>94.17</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>60.5</v>
+        <v>59.27</v>
       </c>
       <c r="K65" t="n">
-        <v>-64.5</v>
+        <v>-63.19</v>
       </c>
       <c r="L65" t="n">
-        <v>88.44</v>
+        <v>86.63</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-36.3</v>
+        <v>-35.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-145.47</v>
+        <v>-142.5</v>
       </c>
       <c r="L66" t="n">
-        <v>149.93</v>
+        <v>146.87</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>36.44</v>
+        <v>37.84</v>
       </c>
       <c r="K67" t="n">
-        <v>-92.66</v>
+        <v>-96.22</v>
       </c>
       <c r="L67" t="n">
-        <v>99.56</v>
+        <v>103.39</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>48.16</v>
+        <v>49.11</v>
       </c>
       <c r="K68" t="n">
-        <v>91.31999999999999</v>
+        <v>93.11</v>
       </c>
       <c r="L68" t="n">
-        <v>103.24</v>
+        <v>105.26</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>121.06</v>
+        <v>130.03</v>
       </c>
       <c r="K69" t="n">
-        <v>30.61</v>
+        <v>32.88</v>
       </c>
       <c r="L69" t="n">
-        <v>124.87</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="70">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>111.32</v>
+        <v>115.6</v>
       </c>
       <c r="K72" t="n">
-        <v>-197.47</v>
+        <v>-205.06</v>
       </c>
       <c r="L72" t="n">
-        <v>226.69</v>
+        <v>235.4</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-187.72</v>
+        <v>-201.63</v>
       </c>
       <c r="K73" t="n">
-        <v>12.06</v>
+        <v>12.96</v>
       </c>
       <c r="L73" t="n">
-        <v>188.11</v>
+        <v>202.04</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>13.07</v>
+        <v>12.8</v>
       </c>
       <c r="K74" t="n">
-        <v>-31.98</v>
+        <v>-31.33</v>
       </c>
       <c r="L74" t="n">
-        <v>34.55</v>
+        <v>33.84</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-42.71</v>
+        <v>-46.59</v>
       </c>
       <c r="K75" t="n">
-        <v>-14.42</v>
+        <v>-15.73</v>
       </c>
       <c r="L75" t="n">
-        <v>45.08</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>32.01</v>
+        <v>31.35</v>
       </c>
       <c r="K76" t="n">
-        <v>37.48</v>
+        <v>36.71</v>
       </c>
       <c r="L76" t="n">
-        <v>49.29</v>
+        <v>48.28</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>25.03</v>
+        <v>27.3</v>
       </c>
       <c r="K77" t="n">
-        <v>-74.04000000000001</v>
+        <v>-80.78</v>
       </c>
       <c r="L77" t="n">
-        <v>78.16</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>34.47</v>
+        <v>37.02</v>
       </c>
       <c r="K78" t="n">
-        <v>-51.13</v>
+        <v>-54.91</v>
       </c>
       <c r="L78" t="n">
-        <v>61.66</v>
+        <v>66.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>56.54</v>
+        <v>60.73</v>
       </c>
       <c r="K79" t="n">
-        <v>-30.94</v>
+        <v>-33.23</v>
       </c>
       <c r="L79" t="n">
-        <v>64.45</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-22.83</v>
+        <v>-24.9</v>
       </c>
       <c r="K80" t="n">
-        <v>140.37</v>
+        <v>153.13</v>
       </c>
       <c r="L80" t="n">
-        <v>142.21</v>
+        <v>155.14</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-67.95999999999999</v>
+        <v>-71.81</v>
       </c>
       <c r="K81" t="n">
-        <v>-32.5</v>
+        <v>-34.34</v>
       </c>
       <c r="L81" t="n">
-        <v>75.33</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-88.88</v>
+        <v>-95.47</v>
       </c>
       <c r="K82" t="n">
-        <v>20.78</v>
+        <v>22.32</v>
       </c>
       <c r="L82" t="n">
-        <v>91.28</v>
+        <v>98.04000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-75.67</v>
+        <v>-77.15000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>109.95</v>
+        <v>112.1</v>
       </c>
       <c r="L84" t="n">
-        <v>133.47</v>
+        <v>136.09</v>
       </c>
     </row>
     <row r="85">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-177.36</v>
+        <v>-187.4</v>
       </c>
       <c r="K87" t="n">
-        <v>-37</v>
+        <v>-39.09</v>
       </c>
       <c r="L87" t="n">
-        <v>181.18</v>
+        <v>191.43</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-18.04</v>
+        <v>-19.38</v>
       </c>
       <c r="K88" t="n">
-        <v>-187.35</v>
+        <v>-201.23</v>
       </c>
       <c r="L88" t="n">
-        <v>188.21</v>
+        <v>202.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="F14" t="n">
-        <v>4.37</v>
+        <v>5.2</v>
       </c>
       <c r="G14" t="n">
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="H14" t="n">
-        <v>19.4</v>
+        <v>47.1</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-29.41</v>
+        <v>-11.84</v>
       </c>
       <c r="K14" t="n">
-        <v>23.99</v>
+        <v>-28.44</v>
       </c>
       <c r="L14" t="n">
-        <v>37.95</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:32:57</t>
+          <t>04:34:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="F15" t="n">
-        <v>4.39</v>
+        <v>3.61</v>
       </c>
       <c r="G15" t="n">
-        <v>256.3</v>
+        <v>261.2</v>
       </c>
       <c r="H15" t="n">
-        <v>22.3</v>
+        <v>51.4</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-50.93</v>
+        <v>33.41</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.45</v>
+        <v>-2.26</v>
       </c>
       <c r="L15" t="n">
-        <v>51.05</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:04</t>
+          <t>04:35:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="F16" t="n">
         <v>6.09</v>
       </c>
       <c r="G16" t="n">
-        <v>244.1</v>
+        <v>252.3</v>
       </c>
       <c r="H16" t="n">
-        <v>24.2</v>
+        <v>18.3</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-34.96</v>
+        <v>-22.84</v>
       </c>
       <c r="K16" t="n">
-        <v>-27.41</v>
+        <v>-28.49</v>
       </c>
       <c r="L16" t="n">
-        <v>44.43</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:39:17</t>
+          <t>04:40:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>4.99</v>
+        <v>3.86</v>
       </c>
       <c r="G17" t="n">
-        <v>253.4</v>
+        <v>246.8</v>
       </c>
       <c r="H17" t="n">
-        <v>26.8</v>
+        <v>40.2</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-47.16</v>
+        <v>21.69</v>
       </c>
       <c r="K17" t="n">
-        <v>-35.08</v>
+        <v>-38.51</v>
       </c>
       <c r="L17" t="n">
-        <v>58.78</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:41:07</t>
+          <t>04:42:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="F18" t="n">
-        <v>3.98</v>
+        <v>2.51</v>
       </c>
       <c r="G18" t="n">
-        <v>253</v>
+        <v>243.7</v>
       </c>
       <c r="H18" t="n">
-        <v>30.1</v>
+        <v>39.8</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-64.44</v>
+        <v>11.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.48</v>
+        <v>34.03</v>
       </c>
       <c r="L18" t="n">
-        <v>65.14</v>
+        <v>35.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:43:18</t>
+          <t>04:43:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="F19" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="G19" t="n">
-        <v>236</v>
+        <v>242.5</v>
       </c>
       <c r="H19" t="n">
-        <v>26.1</v>
+        <v>34.6</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>-57.52</v>
+        <v>-36.14</v>
       </c>
       <c r="K19" t="n">
-        <v>38.51</v>
+        <v>-24.38</v>
       </c>
       <c r="L19" t="n">
-        <v>69.22</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:49:01</t>
+          <t>04:46:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="F20" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>250.8</v>
+        <v>242.4</v>
       </c>
       <c r="H20" t="n">
-        <v>22.2</v>
+        <v>53.8</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>66.08</v>
+        <v>-59.17</v>
       </c>
       <c r="K20" t="n">
-        <v>94.08</v>
+        <v>57.33</v>
       </c>
       <c r="L20" t="n">
-        <v>114.97</v>
+        <v>82.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:51:06</t>
+          <t>04:48:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="F21" t="n">
-        <v>4.79</v>
+        <v>2.86</v>
       </c>
       <c r="G21" t="n">
-        <v>244.4</v>
+        <v>252.2</v>
       </c>
       <c r="H21" t="n">
-        <v>24.9</v>
+        <v>37</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>76.27</v>
+        <v>60.51</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.37</v>
+        <v>33.45</v>
       </c>
       <c r="L21" t="n">
-        <v>77.62</v>
+        <v>69.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:53:22</t>
+          <t>04:50:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="F22" t="n">
-        <v>4.65</v>
+        <v>4.49</v>
       </c>
       <c r="G22" t="n">
-        <v>262.2</v>
+        <v>248.9</v>
       </c>
       <c r="H22" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-69.87</v>
+        <v>-54.76</v>
       </c>
       <c r="K22" t="n">
-        <v>-85.76000000000001</v>
+        <v>53.84</v>
       </c>
       <c r="L22" t="n">
-        <v>110.62</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:58:13</t>
+          <t>04:54:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="F23" t="n">
-        <v>3.08</v>
+        <v>5.1</v>
       </c>
       <c r="G23" t="n">
-        <v>265</v>
+        <v>254.5</v>
       </c>
       <c r="H23" t="n">
-        <v>25.3</v>
+        <v>28.6</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>107.1</v>
+        <v>116.25</v>
       </c>
       <c r="K23" t="n">
-        <v>-43.83</v>
+        <v>85.14</v>
       </c>
       <c r="L23" t="n">
-        <v>115.72</v>
+        <v>144.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:00:40</t>
+          <t>04:56:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="F24" t="n">
-        <v>4.84</v>
+        <v>6.09</v>
       </c>
       <c r="G24" t="n">
-        <v>257.5</v>
+        <v>238.5</v>
       </c>
       <c r="H24" t="n">
-        <v>26.6</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-128.35</v>
+        <v>-86.31999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-31.26</v>
+        <v>108.81</v>
       </c>
       <c r="L24" t="n">
-        <v>132.1</v>
+        <v>138.89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:01:24</t>
+          <t>04:58:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="F25" t="n">
-        <v>4.33</v>
+        <v>5.86</v>
       </c>
       <c r="G25" t="n">
-        <v>252.1</v>
+        <v>247.8</v>
       </c>
       <c r="H25" t="n">
-        <v>24.2</v>
+        <v>56.6</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-127.16</v>
+        <v>2.77</v>
       </c>
       <c r="K25" t="n">
-        <v>-28.29</v>
+        <v>-95.09</v>
       </c>
       <c r="L25" t="n">
-        <v>130.27</v>
+        <v>95.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:07:06</t>
+          <t>05:02:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="F26" t="n">
-        <v>4.31</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>255.8</v>
+        <v>245</v>
       </c>
       <c r="H26" t="n">
-        <v>25.4</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>124.44</v>
+        <v>-111.02</v>
       </c>
       <c r="K26" t="n">
-        <v>158.34</v>
+        <v>-66.95</v>
       </c>
       <c r="L26" t="n">
-        <v>201.39</v>
+        <v>129.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:08:26</t>
+          <t>05:03:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="F27" t="n">
-        <v>6.09</v>
+        <v>5.41</v>
       </c>
       <c r="G27" t="n">
-        <v>254.9</v>
+        <v>271.2</v>
       </c>
       <c r="H27" t="n">
-        <v>31.7</v>
+        <v>0.5</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>-116.69</v>
+        <v>-136.74</v>
       </c>
       <c r="K27" t="n">
-        <v>150.15</v>
+        <v>47.73</v>
       </c>
       <c r="L27" t="n">
-        <v>190.16</v>
+        <v>144.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:10:05</t>
+          <t>05:06:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="F28" t="n">
-        <v>5.01</v>
+        <v>1.82</v>
       </c>
       <c r="G28" t="n">
-        <v>247.4</v>
+        <v>245.8</v>
       </c>
       <c r="H28" t="n">
-        <v>14.6</v>
+        <v>52.1</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-44.4</v>
+        <v>11.41</v>
       </c>
       <c r="K28" t="n">
-        <v>257.48</v>
+        <v>-131.54</v>
       </c>
       <c r="L28" t="n">
-        <v>261.28</v>
+        <v>132.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:18:54</t>
+          <t>05:15:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="F29" t="n">
-        <v>6.09</v>
+        <v>5.62</v>
       </c>
       <c r="G29" t="n">
-        <v>250.2</v>
+        <v>243.2</v>
       </c>
       <c r="H29" t="n">
-        <v>21.8</v>
+        <v>40.8</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-49.7</v>
+        <v>-15.4</v>
       </c>
       <c r="K29" t="n">
-        <v>-37.71</v>
+        <v>-25.43</v>
       </c>
       <c r="L29" t="n">
-        <v>62.39</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:20:30</t>
+          <t>05:17:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="F30" t="n">
-        <v>3.52</v>
+        <v>6.09</v>
       </c>
       <c r="G30" t="n">
-        <v>248.1</v>
+        <v>248.3</v>
       </c>
       <c r="H30" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I30" t="n">
         <v>20</v>
       </c>
-      <c r="I30" t="n">
-        <v>25</v>
-      </c>
       <c r="J30" t="n">
-        <v>-2.78</v>
+        <v>32.08</v>
       </c>
       <c r="K30" t="n">
-        <v>46.26</v>
+        <v>20.05</v>
       </c>
       <c r="L30" t="n">
-        <v>46.34</v>
+        <v>37.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:22:03</t>
+          <t>05:19:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="F31" t="n">
-        <v>3.73</v>
+        <v>2.93</v>
       </c>
       <c r="G31" t="n">
-        <v>264.2</v>
+        <v>242.6</v>
       </c>
       <c r="H31" t="n">
-        <v>20.1</v>
+        <v>40.6</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>59.75</v>
+        <v>-17.62</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>-25.69</v>
       </c>
       <c r="L31" t="n">
-        <v>59.83</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:27:32</t>
+          <t>05:24:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="F32" t="n">
-        <v>6.09</v>
+        <v>3.89</v>
       </c>
       <c r="G32" t="n">
-        <v>253.6</v>
+        <v>259.2</v>
       </c>
       <c r="H32" t="n">
-        <v>20.3</v>
+        <v>39.8</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-35.52</v>
+        <v>33.75</v>
       </c>
       <c r="K32" t="n">
-        <v>80.41</v>
+        <v>-26.22</v>
       </c>
       <c r="L32" t="n">
-        <v>87.91</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:29:26</t>
+          <t>05:26:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="F33" t="n">
-        <v>3.36</v>
+        <v>5.33</v>
       </c>
       <c r="G33" t="n">
-        <v>245.5</v>
+        <v>257.5</v>
       </c>
       <c r="H33" t="n">
-        <v>15.4</v>
+        <v>39.4</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-55.87</v>
+        <v>60.44</v>
       </c>
       <c r="K33" t="n">
-        <v>36.57</v>
+        <v>-19.16</v>
       </c>
       <c r="L33" t="n">
-        <v>66.77</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:31:01</t>
+          <t>05:27:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="F34" t="n">
-        <v>4.09</v>
+        <v>2.42</v>
       </c>
       <c r="G34" t="n">
-        <v>249.4</v>
+        <v>251.1</v>
       </c>
       <c r="H34" t="n">
-        <v>24.6</v>
+        <v>55.7</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>8.93</v>
+        <v>6.44</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.71</v>
+        <v>46.2</v>
       </c>
       <c r="L34" t="n">
-        <v>11.17</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:34:59</t>
+          <t>05:30:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1510,31 +1510,31 @@
         <v>1.51</v>
       </c>
       <c r="F35" t="n">
-        <v>5.26</v>
+        <v>3.78</v>
       </c>
       <c r="G35" t="n">
-        <v>254.2</v>
+        <v>251.5</v>
       </c>
       <c r="H35" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="I35" t="n">
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-89.8</v>
+        <v>-10.48</v>
       </c>
       <c r="K35" t="n">
-        <v>-23.92</v>
+        <v>-73.56</v>
       </c>
       <c r="L35" t="n">
-        <v>92.93000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:36:22</t>
+          <t>05:31:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="F36" t="n">
-        <v>5.03</v>
+        <v>3.98</v>
       </c>
       <c r="G36" t="n">
-        <v>246.5</v>
+        <v>251.7</v>
       </c>
       <c r="H36" t="n">
-        <v>29.4</v>
+        <v>41.3</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-54.47</v>
+        <v>-36.02</v>
       </c>
       <c r="K36" t="n">
-        <v>-92.81999999999999</v>
+        <v>-68.34999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>107.62</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:38:39</t>
+          <t>05:32:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="F37" t="n">
-        <v>3.32</v>
+        <v>6.09</v>
       </c>
       <c r="G37" t="n">
-        <v>252.5</v>
+        <v>242.2</v>
       </c>
       <c r="H37" t="n">
-        <v>24.5</v>
+        <v>67.2</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-50.67</v>
+        <v>-45.78</v>
       </c>
       <c r="K37" t="n">
-        <v>74.51000000000001</v>
+        <v>51.07</v>
       </c>
       <c r="L37" t="n">
-        <v>90.11</v>
+        <v>68.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:42:46</t>
+          <t>05:36:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="F38" t="n">
-        <v>1.79</v>
+        <v>6.09</v>
       </c>
       <c r="G38" t="n">
-        <v>259.6</v>
+        <v>248.2</v>
       </c>
       <c r="H38" t="n">
-        <v>22.2</v>
+        <v>36.3</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>74.51000000000001</v>
+        <v>-111.6</v>
       </c>
       <c r="K38" t="n">
-        <v>0.23</v>
+        <v>39.99</v>
       </c>
       <c r="L38" t="n">
-        <v>74.51000000000001</v>
+        <v>118.55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:45:10</t>
+          <t>05:37:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="F39" t="n">
-        <v>6.09</v>
+        <v>5.18</v>
       </c>
       <c r="G39" t="n">
-        <v>242.2</v>
+        <v>256</v>
       </c>
       <c r="H39" t="n">
-        <v>26.9</v>
+        <v>43.9</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-34.04</v>
+        <v>93.73</v>
       </c>
       <c r="K39" t="n">
-        <v>-132.68</v>
+        <v>44.33</v>
       </c>
       <c r="L39" t="n">
-        <v>136.97</v>
+        <v>103.68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:46:50</t>
+          <t>05:38:31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="F40" t="n">
-        <v>4.48</v>
+        <v>2.81</v>
       </c>
       <c r="G40" t="n">
-        <v>246.2</v>
+        <v>267.6</v>
       </c>
       <c r="H40" t="n">
-        <v>20.2</v>
+        <v>44.7</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-62.58</v>
+        <v>51.36</v>
       </c>
       <c r="K40" t="n">
-        <v>117</v>
+        <v>-88.94</v>
       </c>
       <c r="L40" t="n">
-        <v>132.69</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:51:02</t>
+          <t>05:43:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.85</v>
+        <v>3.02</v>
       </c>
       <c r="F41" t="n">
-        <v>5.35</v>
+        <v>6.09</v>
       </c>
       <c r="G41" t="n">
-        <v>261.8</v>
+        <v>257</v>
       </c>
       <c r="H41" t="n">
-        <v>19.9</v>
+        <v>32.1</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.05</v>
+        <v>-40.34</v>
       </c>
       <c r="K41" t="n">
-        <v>272.79</v>
+        <v>-179.16</v>
       </c>
       <c r="L41" t="n">
-        <v>273.06</v>
+        <v>183.65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:52:52</t>
+          <t>05:44:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="F42" t="n">
-        <v>3.33</v>
+        <v>6.09</v>
       </c>
       <c r="G42" t="n">
-        <v>267.3</v>
+        <v>246.7</v>
       </c>
       <c r="H42" t="n">
         <v>22.3</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-157.84</v>
+        <v>-149.32</v>
       </c>
       <c r="K42" t="n">
-        <v>-130.18</v>
+        <v>46.8</v>
       </c>
       <c r="L42" t="n">
-        <v>204.6</v>
+        <v>156.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:53:38</t>
+          <t>05:46:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="F43" t="n">
-        <v>4.61</v>
+        <v>3.05</v>
       </c>
       <c r="G43" t="n">
-        <v>262.6</v>
+        <v>250.9</v>
       </c>
       <c r="H43" t="n">
-        <v>18.7</v>
+        <v>60.5</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-27.94</v>
+        <v>154.35</v>
       </c>
       <c r="K43" t="n">
-        <v>229.4</v>
+        <v>-11.12</v>
       </c>
       <c r="L43" t="n">
-        <v>231.09</v>
+        <v>154.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:01:49</t>
+          <t>05:53:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="F44" t="n">
-        <v>5.91</v>
+        <v>6.09</v>
       </c>
       <c r="G44" t="n">
-        <v>246.5</v>
+        <v>259.4</v>
       </c>
       <c r="H44" t="n">
-        <v>20.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.38</v>
+        <v>-26.78</v>
       </c>
       <c r="K44" t="n">
-        <v>-55.36</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>73.52</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:02:47</t>
+          <t>05:56:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="F45" t="n">
         <v>6.09</v>
       </c>
       <c r="G45" t="n">
-        <v>245.9</v>
+        <v>245</v>
       </c>
       <c r="H45" t="n">
-        <v>30.1</v>
+        <v>59.7</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>38.05</v>
+        <v>31.97</v>
       </c>
       <c r="K45" t="n">
-        <v>41.99</v>
+        <v>19.9</v>
       </c>
       <c r="L45" t="n">
-        <v>56.67</v>
+        <v>37.66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:03:58</t>
+          <t>05:57:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="F46" t="n">
-        <v>2.96</v>
+        <v>5.58</v>
       </c>
       <c r="G46" t="n">
-        <v>249.7</v>
+        <v>245.7</v>
       </c>
       <c r="H46" t="n">
-        <v>22.7</v>
+        <v>2.6</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-47.17</v>
+        <v>-36.94</v>
       </c>
       <c r="K46" t="n">
-        <v>-15.09</v>
+        <v>7.24</v>
       </c>
       <c r="L46" t="n">
-        <v>49.52</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:08:50</t>
+          <t>06:02:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="F47" t="n">
-        <v>4.79</v>
+        <v>6.09</v>
       </c>
       <c r="G47" t="n">
-        <v>260.1</v>
+        <v>266.8</v>
       </c>
       <c r="H47" t="n">
-        <v>20.8</v>
+        <v>41</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>61.79</v>
+        <v>-40.15</v>
       </c>
       <c r="K47" t="n">
-        <v>3.57</v>
+        <v>-27.02</v>
       </c>
       <c r="L47" t="n">
-        <v>61.89</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:10:02</t>
+          <t>06:04:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="F48" t="n">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="G48" t="n">
-        <v>244.6</v>
+        <v>236.4</v>
       </c>
       <c r="H48" t="n">
-        <v>23.2</v>
+        <v>39.4</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>17.31</v>
+        <v>-42.06</v>
       </c>
       <c r="K48" t="n">
-        <v>89.42</v>
+        <v>33.61</v>
       </c>
       <c r="L48" t="n">
-        <v>91.06999999999999</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:11:13</t>
+          <t>06:05:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F49" t="n">
         <v>6.09</v>
       </c>
       <c r="G49" t="n">
-        <v>260.6</v>
+        <v>245.2</v>
       </c>
       <c r="H49" t="n">
-        <v>31.2</v>
+        <v>40.4</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>46.57</v>
+        <v>-40.19</v>
       </c>
       <c r="K49" t="n">
-        <v>-41.33</v>
+        <v>-28.91</v>
       </c>
       <c r="L49" t="n">
-        <v>62.27</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:15:33</t>
+          <t>06:10:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="F50" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
       <c r="G50" t="n">
-        <v>249.4</v>
+        <v>246.7</v>
       </c>
       <c r="H50" t="n">
-        <v>26.8</v>
+        <v>58.3</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-30.77</v>
+        <v>-44.19</v>
       </c>
       <c r="K50" t="n">
-        <v>-108.55</v>
+        <v>55.88</v>
       </c>
       <c r="L50" t="n">
-        <v>112.83</v>
+        <v>71.23999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:16:38</t>
+          <t>06:12:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="F51" t="n">
-        <v>4.27</v>
+        <v>3.06</v>
       </c>
       <c r="G51" t="n">
-        <v>245.2</v>
+        <v>258.5</v>
       </c>
       <c r="H51" t="n">
-        <v>21</v>
+        <v>61.1</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>69.05</v>
+        <v>77.39</v>
       </c>
       <c r="K51" t="n">
-        <v>-24.51</v>
+        <v>5.98</v>
       </c>
       <c r="L51" t="n">
-        <v>73.27</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:18:15</t>
+          <t>06:15:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="F52" t="n">
-        <v>4.56</v>
+        <v>5.84</v>
       </c>
       <c r="G52" t="n">
-        <v>236.4</v>
+        <v>248.3</v>
       </c>
       <c r="H52" t="n">
-        <v>17.4</v>
+        <v>47.9</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>88.75</v>
+        <v>-30.15</v>
       </c>
       <c r="K52" t="n">
-        <v>81.93000000000001</v>
+        <v>-84.36</v>
       </c>
       <c r="L52" t="n">
-        <v>120.79</v>
+        <v>89.59</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:23:01</t>
+          <t>06:20:52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="F53" t="n">
-        <v>3.37</v>
+        <v>5.8</v>
       </c>
       <c r="G53" t="n">
-        <v>259.4</v>
+        <v>250.6</v>
       </c>
       <c r="H53" t="n">
-        <v>20.8</v>
+        <v>61.1</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-118.23</v>
+        <v>123.64</v>
       </c>
       <c r="K53" t="n">
-        <v>-35.95</v>
+        <v>-5.26</v>
       </c>
       <c r="L53" t="n">
-        <v>123.57</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:24:57</t>
+          <t>06:23:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="F54" t="n">
-        <v>5.67</v>
+        <v>5.25</v>
       </c>
       <c r="G54" t="n">
-        <v>251.9</v>
+        <v>260.4</v>
       </c>
       <c r="H54" t="n">
-        <v>24.8</v>
+        <v>37.8</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-114.23</v>
+        <v>-86.40000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-83.05</v>
+        <v>-8.25</v>
       </c>
       <c r="L54" t="n">
-        <v>141.23</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:25:58</t>
+          <t>06:24:40</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="F55" t="n">
-        <v>4.4</v>
+        <v>5.03</v>
       </c>
       <c r="G55" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H55" t="n">
-        <v>17.7</v>
+        <v>32.8</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-173.31</v>
+        <v>-102.15</v>
       </c>
       <c r="K55" t="n">
-        <v>-28.22</v>
+        <v>13.1</v>
       </c>
       <c r="L55" t="n">
-        <v>175.59</v>
+        <v>102.98</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:30:36</t>
+          <t>06:30:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="F56" t="n">
-        <v>2.72</v>
+        <v>4.62</v>
       </c>
       <c r="G56" t="n">
-        <v>242.8</v>
+        <v>248.8</v>
       </c>
       <c r="H56" t="n">
-        <v>25.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-162.66</v>
+        <v>-128.53</v>
       </c>
       <c r="K56" t="n">
-        <v>-32.97</v>
+        <v>-59.54</v>
       </c>
       <c r="L56" t="n">
-        <v>165.96</v>
+        <v>141.65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:32:57</t>
+          <t>06:31:54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2434,31 +2434,31 @@
         <v>1.7</v>
       </c>
       <c r="F57" t="n">
-        <v>3.94</v>
+        <v>4.18</v>
       </c>
       <c r="G57" t="n">
-        <v>252.7</v>
+        <v>248.2</v>
       </c>
       <c r="H57" t="n">
-        <v>18.5</v>
+        <v>69.7</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>-201.51</v>
+        <v>2.65</v>
       </c>
       <c r="K57" t="n">
-        <v>99.14</v>
+        <v>143.41</v>
       </c>
       <c r="L57" t="n">
-        <v>224.58</v>
+        <v>143.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:33:45</t>
+          <t>06:34:09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="F58" t="n">
         <v>6.09</v>
       </c>
       <c r="G58" t="n">
-        <v>258.1</v>
+        <v>270.8</v>
       </c>
       <c r="H58" t="n">
-        <v>24.5</v>
+        <v>29.5</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>199.91</v>
+        <v>-110.36</v>
       </c>
       <c r="K58" t="n">
-        <v>17.56</v>
+        <v>-39.24</v>
       </c>
       <c r="L58" t="n">
-        <v>200.68</v>
+        <v>117.13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>06:42:35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.37</v>
+        <v>1.82</v>
       </c>
       <c r="F59" t="n">
-        <v>6.09</v>
+        <v>6.03</v>
       </c>
       <c r="G59" t="n">
-        <v>248.4</v>
+        <v>250.5</v>
       </c>
       <c r="H59" t="n">
-        <v>20.6</v>
+        <v>64.2</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-39.83</v>
+        <v>-15.48</v>
       </c>
       <c r="K59" t="n">
-        <v>-78.84999999999999</v>
+        <v>21.79</v>
       </c>
       <c r="L59" t="n">
-        <v>88.34</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:45:50</t>
+          <t>06:43:51</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="F60" t="n">
-        <v>3.38</v>
+        <v>6.09</v>
       </c>
       <c r="G60" t="n">
-        <v>252</v>
+        <v>244.3</v>
       </c>
       <c r="H60" t="n">
-        <v>30.8</v>
+        <v>88.7</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>-55.44</v>
+        <v>-22.56</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.05</v>
+        <v>26.16</v>
       </c>
       <c r="L60" t="n">
-        <v>55.44</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:47:09</t>
+          <t>06:45:26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="F61" t="n">
-        <v>6.09</v>
+        <v>5.52</v>
       </c>
       <c r="G61" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="H61" t="n">
-        <v>19.4</v>
+        <v>27.3</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>60.23</v>
+        <v>-34.02</v>
       </c>
       <c r="K61" t="n">
-        <v>6.86</v>
+        <v>2.24</v>
       </c>
       <c r="L61" t="n">
-        <v>60.62</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:52:05</t>
+          <t>06:50:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="F62" t="n">
-        <v>3.48</v>
+        <v>4.35</v>
       </c>
       <c r="G62" t="n">
-        <v>252.5</v>
+        <v>257</v>
       </c>
       <c r="H62" t="n">
-        <v>23.4</v>
+        <v>45.6</v>
       </c>
       <c r="I62" t="n">
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-42.34</v>
+        <v>28.67</v>
       </c>
       <c r="K62" t="n">
-        <v>-45.39</v>
+        <v>44.28</v>
       </c>
       <c r="L62" t="n">
-        <v>62.07</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:54:21</t>
+          <t>06:52:35</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="F63" t="n">
-        <v>6.09</v>
+        <v>3.52</v>
       </c>
       <c r="G63" t="n">
-        <v>248.8</v>
+        <v>255.7</v>
       </c>
       <c r="H63" t="n">
-        <v>20.8</v>
+        <v>29.5</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-20.63</v>
+        <v>-41.32</v>
       </c>
       <c r="K63" t="n">
-        <v>56.13</v>
+        <v>5.63</v>
       </c>
       <c r="L63" t="n">
-        <v>59.8</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:56:29</t>
+          <t>06:54:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="F64" t="n">
-        <v>4.82</v>
+        <v>3.93</v>
       </c>
       <c r="G64" t="n">
-        <v>245.3</v>
+        <v>241.5</v>
       </c>
       <c r="H64" t="n">
-        <v>21.9</v>
+        <v>33.6</v>
       </c>
       <c r="I64" t="n">
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-75.45999999999999</v>
+        <v>-45.63</v>
       </c>
       <c r="K64" t="n">
-        <v>64.84999999999999</v>
+        <v>-14.38</v>
       </c>
       <c r="L64" t="n">
-        <v>99.5</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:01:15</t>
+          <t>07:00:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="F65" t="n">
-        <v>6.09</v>
+        <v>2.58</v>
       </c>
       <c r="G65" t="n">
-        <v>240.5</v>
+        <v>256.9</v>
       </c>
       <c r="H65" t="n">
-        <v>19.5</v>
+        <v>51.5</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>59.27</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-63.19</v>
+        <v>-56.58</v>
       </c>
       <c r="L65" t="n">
-        <v>86.63</v>
+        <v>57.22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:03:14</t>
+          <t>07:03:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="F66" t="n">
-        <v>5.05</v>
+        <v>5.17</v>
       </c>
       <c r="G66" t="n">
-        <v>247.4</v>
+        <v>258.7</v>
       </c>
       <c r="H66" t="n">
-        <v>27.9</v>
+        <v>83.8</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-35.56</v>
+        <v>44.37</v>
       </c>
       <c r="K66" t="n">
-        <v>-142.5</v>
+        <v>63.55</v>
       </c>
       <c r="L66" t="n">
-        <v>146.87</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:04:47</t>
+          <t>07:05:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.66</v>
+        <v>2.01</v>
       </c>
       <c r="F67" t="n">
-        <v>3.88</v>
+        <v>6.09</v>
       </c>
       <c r="G67" t="n">
-        <v>235.8</v>
+        <v>251.7</v>
       </c>
       <c r="H67" t="n">
-        <v>13.9</v>
+        <v>53.7</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>37.84</v>
+        <v>3.77</v>
       </c>
       <c r="K67" t="n">
-        <v>-96.22</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>103.39</v>
+        <v>66.68000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:08:04</t>
+          <t>07:09:16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="F68" t="n">
-        <v>3.02</v>
+        <v>4.59</v>
       </c>
       <c r="G68" t="n">
-        <v>247.5</v>
+        <v>257.4</v>
       </c>
       <c r="H68" t="n">
-        <v>15.2</v>
+        <v>41.1</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>49.11</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>93.11</v>
+        <v>36.4</v>
       </c>
       <c r="L68" t="n">
-        <v>105.26</v>
+        <v>88.36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:09:29</t>
+          <t>07:11:11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="F69" t="n">
-        <v>4.21</v>
+        <v>6.09</v>
       </c>
       <c r="G69" t="n">
-        <v>243.5</v>
+        <v>239.3</v>
       </c>
       <c r="H69" t="n">
-        <v>22.4</v>
+        <v>30</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>130.03</v>
+        <v>144.24</v>
       </c>
       <c r="K69" t="n">
-        <v>32.88</v>
+        <v>16.59</v>
       </c>
       <c r="L69" t="n">
-        <v>134.12</v>
+        <v>145.19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:10:42</t>
+          <t>07:12:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="F70" t="n">
-        <v>3.93</v>
+        <v>6.09</v>
       </c>
       <c r="G70" t="n">
-        <v>242.7</v>
+        <v>250.7</v>
       </c>
       <c r="H70" t="n">
-        <v>21.5</v>
+        <v>42.8</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-81.67</v>
+        <v>-144.24</v>
       </c>
       <c r="K70" t="n">
-        <v>-101.13</v>
+        <v>0.78</v>
       </c>
       <c r="L70" t="n">
-        <v>129.99</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:14:30</t>
+          <t>07:17:19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="F71" t="n">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="G71" t="n">
-        <v>245.1</v>
+        <v>254.7</v>
       </c>
       <c r="H71" t="n">
-        <v>20.5</v>
+        <v>70.2</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-226.12</v>
+        <v>44.33</v>
       </c>
       <c r="K71" t="n">
-        <v>11.29</v>
+        <v>-222.43</v>
       </c>
       <c r="L71" t="n">
-        <v>226.4</v>
+        <v>226.81</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:16:26</t>
+          <t>07:18:04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="F72" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
       <c r="G72" t="n">
-        <v>235.9</v>
+        <v>253.4</v>
       </c>
       <c r="H72" t="n">
-        <v>24.9</v>
+        <v>57.2</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>115.6</v>
+        <v>24.7</v>
       </c>
       <c r="K72" t="n">
-        <v>-205.06</v>
+        <v>-131.33</v>
       </c>
       <c r="L72" t="n">
-        <v>235.4</v>
+        <v>133.63</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:17:41</t>
+          <t>07:19:50</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="F73" t="n">
-        <v>2.79</v>
+        <v>6.09</v>
       </c>
       <c r="G73" t="n">
-        <v>246</v>
+        <v>249.8</v>
       </c>
       <c r="H73" t="n">
-        <v>24.7</v>
+        <v>25.9</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>-201.63</v>
+        <v>-22.76</v>
       </c>
       <c r="K73" t="n">
-        <v>12.96</v>
+        <v>173.77</v>
       </c>
       <c r="L73" t="n">
-        <v>202.04</v>
+        <v>175.25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:25:01</t>
+          <t>07:29:56</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="F74" t="n">
-        <v>5.05</v>
+        <v>6.09</v>
       </c>
       <c r="G74" t="n">
-        <v>237.7</v>
+        <v>246.9</v>
       </c>
       <c r="H74" t="n">
-        <v>23.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>12.8</v>
+        <v>-4.05</v>
       </c>
       <c r="K74" t="n">
-        <v>-31.33</v>
+        <v>30.24</v>
       </c>
       <c r="L74" t="n">
-        <v>33.84</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:25:36</t>
+          <t>07:31:22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="F75" t="n">
-        <v>6.09</v>
+        <v>5.26</v>
       </c>
       <c r="G75" t="n">
-        <v>253.8</v>
+        <v>251.1</v>
       </c>
       <c r="H75" t="n">
-        <v>27.8</v>
+        <v>49</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-46.59</v>
+        <v>1.28</v>
       </c>
       <c r="K75" t="n">
-        <v>-15.73</v>
+        <v>33.31</v>
       </c>
       <c r="L75" t="n">
-        <v>49.18</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:28:09</t>
+          <t>07:32:22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="F76" t="n">
-        <v>6.09</v>
+        <v>4.84</v>
       </c>
       <c r="G76" t="n">
-        <v>255.8</v>
+        <v>242.8</v>
       </c>
       <c r="H76" t="n">
-        <v>23.7</v>
+        <v>51.5</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>31.35</v>
+        <v>-29.03</v>
       </c>
       <c r="K76" t="n">
-        <v>36.71</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>48.28</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:33:08</t>
+          <t>07:38:05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="F77" t="n">
-        <v>6.09</v>
+        <v>4.48</v>
       </c>
       <c r="G77" t="n">
-        <v>251.2</v>
+        <v>252.5</v>
       </c>
       <c r="H77" t="n">
-        <v>24</v>
+        <v>34.1</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>27.3</v>
+        <v>-12.1</v>
       </c>
       <c r="K77" t="n">
-        <v>-80.78</v>
+        <v>12.68</v>
       </c>
       <c r="L77" t="n">
-        <v>85.26000000000001</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:33:48</t>
+          <t>07:40:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="F78" t="n">
-        <v>4.11</v>
+        <v>5.18</v>
       </c>
       <c r="G78" t="n">
-        <v>249.3</v>
+        <v>240.5</v>
       </c>
       <c r="H78" t="n">
-        <v>23.5</v>
+        <v>35.8</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>37.02</v>
+        <v>-31.27</v>
       </c>
       <c r="K78" t="n">
-        <v>-54.91</v>
+        <v>-30.57</v>
       </c>
       <c r="L78" t="n">
-        <v>66.23</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:36:20</t>
+          <t>07:41:06</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="F79" t="n">
-        <v>4.72</v>
+        <v>4.24</v>
       </c>
       <c r="G79" t="n">
-        <v>245.5</v>
+        <v>253.4</v>
       </c>
       <c r="H79" t="n">
-        <v>27.8</v>
+        <v>23.5</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>60.73</v>
+        <v>-55.34</v>
       </c>
       <c r="K79" t="n">
-        <v>-33.23</v>
+        <v>-25.13</v>
       </c>
       <c r="L79" t="n">
-        <v>69.23</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:41:32</t>
+          <t>07:45:43</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="F80" t="n">
         <v>6.09</v>
       </c>
       <c r="G80" t="n">
-        <v>235</v>
+        <v>269.9</v>
       </c>
       <c r="H80" t="n">
-        <v>32.8</v>
+        <v>61.2</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-24.9</v>
+        <v>27.47</v>
       </c>
       <c r="K80" t="n">
-        <v>153.13</v>
+        <v>-82.26000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>155.14</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:42:49</t>
+          <t>07:48:08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="F81" t="n">
-        <v>5.19</v>
+        <v>6.09</v>
       </c>
       <c r="G81" t="n">
-        <v>242.5</v>
+        <v>265.4</v>
       </c>
       <c r="H81" t="n">
-        <v>19.9</v>
+        <v>24</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-71.81</v>
+        <v>58.53</v>
       </c>
       <c r="K81" t="n">
-        <v>-34.34</v>
+        <v>-11.06</v>
       </c>
       <c r="L81" t="n">
-        <v>79.59999999999999</v>
+        <v>59.57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:44:51</t>
+          <t>07:49:25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="F82" t="n">
-        <v>6.09</v>
+        <v>3.23</v>
       </c>
       <c r="G82" t="n">
-        <v>246.4</v>
+        <v>260.1</v>
       </c>
       <c r="H82" t="n">
-        <v>18.8</v>
+        <v>41.4</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-95.47</v>
+        <v>60</v>
       </c>
       <c r="K82" t="n">
-        <v>22.32</v>
+        <v>-80.5</v>
       </c>
       <c r="L82" t="n">
-        <v>98.04000000000001</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:49:32</t>
+          <t>07:53:06</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="F83" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="G83" t="n">
-        <v>247.2</v>
+        <v>250.4</v>
       </c>
       <c r="H83" t="n">
-        <v>25.9</v>
+        <v>48.8</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>-115.07</v>
+        <v>-0.51</v>
       </c>
       <c r="K83" t="n">
-        <v>-37.49</v>
+        <v>180.57</v>
       </c>
       <c r="L83" t="n">
-        <v>121.03</v>
+        <v>180.57</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:50:30</t>
+          <t>07:55:03</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="F84" t="n">
-        <v>4.66</v>
+        <v>6.09</v>
       </c>
       <c r="G84" t="n">
-        <v>245</v>
+        <v>248.2</v>
       </c>
       <c r="H84" t="n">
-        <v>26.9</v>
+        <v>38</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-77.15000000000001</v>
+        <v>-142.66</v>
       </c>
       <c r="K84" t="n">
-        <v>112.1</v>
+        <v>64.91</v>
       </c>
       <c r="L84" t="n">
-        <v>136.09</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:51:41</t>
+          <t>07:56:48</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="F85" t="n">
-        <v>3.56</v>
+        <v>6.09</v>
       </c>
       <c r="G85" t="n">
-        <v>250.1</v>
+        <v>237.9</v>
       </c>
       <c r="H85" t="n">
-        <v>28.8</v>
+        <v>17.4</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-81.55</v>
+        <v>64.05</v>
       </c>
       <c r="K85" t="n">
-        <v>35.5</v>
+        <v>66.62</v>
       </c>
       <c r="L85" t="n">
-        <v>88.94</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07:56:46</t>
+          <t>08:00:57</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="F86" t="n">
-        <v>3.84</v>
+        <v>6.09</v>
       </c>
       <c r="G86" t="n">
-        <v>255.3</v>
+        <v>241.7</v>
       </c>
       <c r="H86" t="n">
-        <v>20</v>
+        <v>80.8</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>70.84999999999999</v>
+        <v>-111.01</v>
       </c>
       <c r="K86" t="n">
-        <v>115.11</v>
+        <v>-122.48</v>
       </c>
       <c r="L86" t="n">
-        <v>135.16</v>
+        <v>165.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07:58:34</t>
+          <t>08:01:58</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>6.09</v>
+        <v>5.33</v>
       </c>
       <c r="G87" t="n">
-        <v>245.1</v>
+        <v>249.7</v>
       </c>
       <c r="H87" t="n">
-        <v>25.4</v>
+        <v>24.2</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-187.4</v>
+        <v>-140.8</v>
       </c>
       <c r="K87" t="n">
-        <v>-39.09</v>
+        <v>101.15</v>
       </c>
       <c r="L87" t="n">
-        <v>191.43</v>
+        <v>173.37</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:01:16</t>
+          <t>08:04:19</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="F88" t="n">
-        <v>5.5</v>
+        <v>6.09</v>
       </c>
       <c r="G88" t="n">
-        <v>253.2</v>
+        <v>265</v>
       </c>
       <c r="H88" t="n">
-        <v>23.3</v>
+        <v>33.5</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-19.38</v>
+        <v>-127.38</v>
       </c>
       <c r="K88" t="n">
-        <v>-201.23</v>
+        <v>119.78</v>
       </c>
       <c r="L88" t="n">
-        <v>202.16</v>
+        <v>174.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="F14" t="n">
-        <v>5.2</v>
+        <v>3.23</v>
       </c>
       <c r="G14" t="n">
-        <v>246.7</v>
+        <v>244.4</v>
       </c>
       <c r="H14" t="n">
-        <v>47.1</v>
+        <v>29.4</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.84</v>
+        <v>35.04</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.44</v>
+        <v>23.91</v>
       </c>
       <c r="L14" t="n">
-        <v>30.81</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:34:32</t>
+          <t>04:33:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="F15" t="n">
-        <v>3.61</v>
+        <v>6.09</v>
       </c>
       <c r="G15" t="n">
-        <v>261.2</v>
+        <v>241.5</v>
       </c>
       <c r="H15" t="n">
-        <v>51.4</v>
+        <v>40.4</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>33.41</v>
+        <v>31.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.26</v>
+        <v>-16.14</v>
       </c>
       <c r="L15" t="n">
-        <v>33.49</v>
+        <v>35.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:40</t>
+          <t>04:35:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="F16" t="n">
-        <v>6.09</v>
+        <v>4.32</v>
       </c>
       <c r="G16" t="n">
-        <v>252.3</v>
+        <v>249.2</v>
       </c>
       <c r="H16" t="n">
-        <v>18.3</v>
+        <v>47.9</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-22.84</v>
+        <v>-40.68</v>
       </c>
       <c r="K16" t="n">
-        <v>-28.49</v>
+        <v>6.56</v>
       </c>
       <c r="L16" t="n">
-        <v>36.52</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:33</t>
+          <t>04:39:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="F17" t="n">
-        <v>3.86</v>
+        <v>1.85</v>
       </c>
       <c r="G17" t="n">
-        <v>246.8</v>
+        <v>248.9</v>
       </c>
       <c r="H17" t="n">
-        <v>40.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>21.69</v>
+        <v>-36.06</v>
       </c>
       <c r="K17" t="n">
-        <v>-38.51</v>
+        <v>-29.37</v>
       </c>
       <c r="L17" t="n">
-        <v>44.2</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:18</t>
+          <t>04:41:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="F18" t="n">
-        <v>2.51</v>
+        <v>6.09</v>
       </c>
       <c r="G18" t="n">
-        <v>243.7</v>
+        <v>240.1</v>
       </c>
       <c r="H18" t="n">
-        <v>39.8</v>
+        <v>38.5</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>11.52</v>
+        <v>-65.52</v>
       </c>
       <c r="K18" t="n">
-        <v>34.03</v>
+        <v>16.19</v>
       </c>
       <c r="L18" t="n">
-        <v>35.93</v>
+        <v>67.48999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:43:35</t>
+          <t>04:42:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="F19" t="n">
-        <v>5.7</v>
+        <v>4.81</v>
       </c>
       <c r="G19" t="n">
-        <v>242.5</v>
+        <v>243.1</v>
       </c>
       <c r="H19" t="n">
-        <v>34.6</v>
+        <v>61.3</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-36.14</v>
+        <v>44.05</v>
       </c>
       <c r="K19" t="n">
-        <v>-24.38</v>
+        <v>30.51</v>
       </c>
       <c r="L19" t="n">
-        <v>43.59</v>
+        <v>53.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:46:53</t>
+          <t>04:47:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="G20" t="n">
-        <v>242.4</v>
+        <v>239.1</v>
       </c>
       <c r="H20" t="n">
-        <v>53.8</v>
+        <v>27.8</v>
       </c>
       <c r="I20" t="n">
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-59.17</v>
+        <v>-48.57</v>
       </c>
       <c r="K20" t="n">
-        <v>57.33</v>
+        <v>-77.02</v>
       </c>
       <c r="L20" t="n">
-        <v>82.39</v>
+        <v>91.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:48:18</t>
+          <t>04:49:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="F21" t="n">
-        <v>2.86</v>
+        <v>3.59</v>
       </c>
       <c r="G21" t="n">
-        <v>252.2</v>
+        <v>242.5</v>
       </c>
       <c r="H21" t="n">
-        <v>37</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>60.51</v>
+        <v>73.98</v>
       </c>
       <c r="K21" t="n">
-        <v>33.45</v>
+        <v>-139.57</v>
       </c>
       <c r="L21" t="n">
-        <v>69.14</v>
+        <v>157.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:50:34</t>
+          <t>04:50:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="F22" t="n">
-        <v>4.49</v>
+        <v>5.47</v>
       </c>
       <c r="G22" t="n">
-        <v>248.9</v>
+        <v>264.7</v>
       </c>
       <c r="H22" t="n">
-        <v>19.2</v>
+        <v>29.8</v>
       </c>
       <c r="I22" t="n">
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-54.76</v>
+        <v>-82.20999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>53.84</v>
+        <v>-8.98</v>
       </c>
       <c r="L22" t="n">
-        <v>76.8</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:54:40</t>
+          <t>04:54:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="F23" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>254.5</v>
+        <v>254.2</v>
       </c>
       <c r="H23" t="n">
-        <v>28.6</v>
+        <v>29.9</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>116.25</v>
+        <v>119.98</v>
       </c>
       <c r="K23" t="n">
-        <v>85.14</v>
+        <v>21.75</v>
       </c>
       <c r="L23" t="n">
-        <v>144.1</v>
+        <v>121.93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:56:32</t>
+          <t>04:56:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="F24" t="n">
         <v>6.09</v>
       </c>
       <c r="G24" t="n">
-        <v>238.5</v>
+        <v>252.5</v>
       </c>
       <c r="H24" t="n">
-        <v>86.59999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-86.31999999999999</v>
+        <v>93.72</v>
       </c>
       <c r="K24" t="n">
-        <v>108.81</v>
+        <v>108.93</v>
       </c>
       <c r="L24" t="n">
-        <v>138.89</v>
+        <v>143.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:58:27</t>
+          <t>04:58:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="F25" t="n">
-        <v>5.86</v>
+        <v>3.83</v>
       </c>
       <c r="G25" t="n">
-        <v>247.8</v>
+        <v>246.7</v>
       </c>
       <c r="H25" t="n">
-        <v>56.6</v>
+        <v>34.8</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>2.77</v>
+        <v>-151.49</v>
       </c>
       <c r="K25" t="n">
-        <v>-95.09</v>
+        <v>17.51</v>
       </c>
       <c r="L25" t="n">
-        <v>95.13</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:02:03</t>
+          <t>05:04:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="G26" t="n">
-        <v>245</v>
+        <v>244.6</v>
       </c>
       <c r="H26" t="n">
-        <v>68.09999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-111.02</v>
+        <v>-137.52</v>
       </c>
       <c r="K26" t="n">
-        <v>-66.95</v>
+        <v>127.47</v>
       </c>
       <c r="L26" t="n">
-        <v>129.65</v>
+        <v>187.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:03:46</t>
+          <t>05:06:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.55</v>
+        <v>1.99</v>
       </c>
       <c r="F27" t="n">
-        <v>5.41</v>
+        <v>6.09</v>
       </c>
       <c r="G27" t="n">
-        <v>271.2</v>
+        <v>243.6</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5</v>
+        <v>59.8</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-136.74</v>
+        <v>-114.27</v>
       </c>
       <c r="K27" t="n">
-        <v>47.73</v>
+        <v>-99.23</v>
       </c>
       <c r="L27" t="n">
-        <v>144.83</v>
+        <v>151.34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:06:06</t>
+          <t>05:08:49</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="F28" t="n">
-        <v>1.82</v>
+        <v>6.09</v>
       </c>
       <c r="G28" t="n">
-        <v>245.8</v>
+        <v>266.7</v>
       </c>
       <c r="H28" t="n">
-        <v>52.1</v>
+        <v>43.4</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>11.41</v>
+        <v>165.47</v>
       </c>
       <c r="K28" t="n">
-        <v>-131.54</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>132.03</v>
+        <v>184.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:15:40</t>
+          <t>05:17:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="F29" t="n">
-        <v>5.62</v>
+        <v>2.04</v>
       </c>
       <c r="G29" t="n">
-        <v>243.2</v>
+        <v>241.9</v>
       </c>
       <c r="H29" t="n">
-        <v>40.8</v>
+        <v>28.2</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.4</v>
+        <v>32.63</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.43</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>29.73</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:17:39</t>
+          <t>05:19:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="F30" t="n">
         <v>6.09</v>
       </c>
       <c r="G30" t="n">
-        <v>248.3</v>
+        <v>252.3</v>
       </c>
       <c r="H30" t="n">
-        <v>43.3</v>
+        <v>22.9</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>32.08</v>
+        <v>31.5</v>
       </c>
       <c r="K30" t="n">
-        <v>20.05</v>
+        <v>1.23</v>
       </c>
       <c r="L30" t="n">
-        <v>37.83</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:19:50</t>
+          <t>05:21:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="F31" t="n">
-        <v>2.93</v>
+        <v>6.09</v>
       </c>
       <c r="G31" t="n">
-        <v>242.6</v>
+        <v>253</v>
       </c>
       <c r="H31" t="n">
-        <v>40.6</v>
+        <v>23.8</v>
       </c>
       <c r="I31" t="n">
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.62</v>
+        <v>-58.74</v>
       </c>
       <c r="K31" t="n">
-        <v>-25.69</v>
+        <v>7.59</v>
       </c>
       <c r="L31" t="n">
-        <v>31.15</v>
+        <v>59.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:24:28</t>
+          <t>05:25:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,28 +1381,28 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="F32" t="n">
-        <v>3.89</v>
+        <v>6.09</v>
       </c>
       <c r="G32" t="n">
-        <v>259.2</v>
+        <v>234.7</v>
       </c>
       <c r="H32" t="n">
-        <v>39.8</v>
+        <v>42.1</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>33.75</v>
+        <v>-53.07</v>
       </c>
       <c r="K32" t="n">
-        <v>-26.22</v>
+        <v>13.98</v>
       </c>
       <c r="L32" t="n">
-        <v>42.74</v>
+        <v>54.88</v>
       </c>
     </row>
     <row r="33">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="F33" t="n">
-        <v>5.33</v>
+        <v>2.28</v>
       </c>
       <c r="G33" t="n">
-        <v>257.5</v>
+        <v>234.3</v>
       </c>
       <c r="H33" t="n">
-        <v>39.4</v>
+        <v>43.3</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>60.44</v>
+        <v>-2.72</v>
       </c>
       <c r="K33" t="n">
-        <v>-19.16</v>
+        <v>50.68</v>
       </c>
       <c r="L33" t="n">
-        <v>63.4</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:27:13</t>
+          <t>05:27:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="F34" t="n">
-        <v>2.42</v>
+        <v>5.47</v>
       </c>
       <c r="G34" t="n">
-        <v>251.1</v>
+        <v>248</v>
       </c>
       <c r="H34" t="n">
-        <v>55.7</v>
+        <v>52.6</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>6.44</v>
+        <v>-28.34</v>
       </c>
       <c r="K34" t="n">
-        <v>46.2</v>
+        <v>35.08</v>
       </c>
       <c r="L34" t="n">
-        <v>46.65</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:30:23</t>
+          <t>05:32:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="F35" t="n">
-        <v>3.78</v>
+        <v>5.07</v>
       </c>
       <c r="G35" t="n">
-        <v>251.5</v>
+        <v>255</v>
       </c>
       <c r="H35" t="n">
-        <v>22.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.48</v>
+        <v>-27.2</v>
       </c>
       <c r="K35" t="n">
-        <v>-73.56</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>74.3</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:31:08</t>
+          <t>05:34:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="F36" t="n">
-        <v>3.98</v>
+        <v>2.94</v>
       </c>
       <c r="G36" t="n">
-        <v>251.7</v>
+        <v>250.3</v>
       </c>
       <c r="H36" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-36.02</v>
+        <v>-9.75</v>
       </c>
       <c r="K36" t="n">
-        <v>-68.34999999999999</v>
+        <v>-90.98</v>
       </c>
       <c r="L36" t="n">
-        <v>77.26000000000001</v>
+        <v>91.51000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:32:28</t>
+          <t>05:37:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="F37" t="n">
         <v>6.09</v>
       </c>
       <c r="G37" t="n">
-        <v>242.2</v>
+        <v>262.1</v>
       </c>
       <c r="H37" t="n">
-        <v>67.2</v>
+        <v>48.9</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-45.78</v>
+        <v>-71.59999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>51.07</v>
+        <v>6.58</v>
       </c>
       <c r="L37" t="n">
-        <v>68.59</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:36:15</t>
+          <t>05:41:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="F38" t="n">
-        <v>6.09</v>
+        <v>4.23</v>
       </c>
       <c r="G38" t="n">
-        <v>248.2</v>
+        <v>243.8</v>
       </c>
       <c r="H38" t="n">
-        <v>36.3</v>
+        <v>30.9</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-111.6</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>39.99</v>
+        <v>39.53</v>
       </c>
       <c r="L38" t="n">
-        <v>118.55</v>
+        <v>85.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:37:41</t>
+          <t>05:43:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="F39" t="n">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
       <c r="G39" t="n">
-        <v>256</v>
+        <v>258.3</v>
       </c>
       <c r="H39" t="n">
-        <v>43.9</v>
+        <v>27.2</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>93.73</v>
+        <v>-44.71</v>
       </c>
       <c r="K39" t="n">
-        <v>44.33</v>
+        <v>107.27</v>
       </c>
       <c r="L39" t="n">
-        <v>103.68</v>
+        <v>116.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:38:31</t>
+          <t>05:46:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="F40" t="n">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="G40" t="n">
-        <v>267.6</v>
+        <v>250</v>
       </c>
       <c r="H40" t="n">
-        <v>44.7</v>
+        <v>43.4</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>51.36</v>
+        <v>-66.52</v>
       </c>
       <c r="K40" t="n">
-        <v>-88.94</v>
+        <v>83.59</v>
       </c>
       <c r="L40" t="n">
-        <v>102.7</v>
+        <v>106.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:43:29</t>
+          <t>05:51:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.02</v>
+        <v>1.98</v>
       </c>
       <c r="F41" t="n">
         <v>6.09</v>
       </c>
       <c r="G41" t="n">
-        <v>257</v>
+        <v>254.3</v>
       </c>
       <c r="H41" t="n">
-        <v>32.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-40.34</v>
+        <v>-83.66</v>
       </c>
       <c r="K41" t="n">
-        <v>-179.16</v>
+        <v>156.18</v>
       </c>
       <c r="L41" t="n">
-        <v>183.65</v>
+        <v>177.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:44:47</t>
+          <t>05:53:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="F42" t="n">
         <v>6.09</v>
       </c>
       <c r="G42" t="n">
-        <v>246.7</v>
+        <v>239.4</v>
       </c>
       <c r="H42" t="n">
-        <v>22.3</v>
+        <v>15.7</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-149.32</v>
+        <v>-172.74</v>
       </c>
       <c r="K42" t="n">
-        <v>46.8</v>
+        <v>132.95</v>
       </c>
       <c r="L42" t="n">
-        <v>156.48</v>
+        <v>217.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:46:19</t>
+          <t>05:55:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="F43" t="n">
-        <v>3.05</v>
+        <v>6.09</v>
       </c>
       <c r="G43" t="n">
-        <v>250.9</v>
+        <v>243.4</v>
       </c>
       <c r="H43" t="n">
-        <v>60.5</v>
+        <v>21.6</v>
       </c>
       <c r="I43" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>154.35</v>
+        <v>-196.46</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.12</v>
+        <v>55.94</v>
       </c>
       <c r="L43" t="n">
-        <v>154.75</v>
+        <v>204.27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05:53:40</t>
+          <t>06:04:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="F44" t="n">
         <v>6.09</v>
       </c>
       <c r="G44" t="n">
-        <v>259.4</v>
+        <v>246.6</v>
       </c>
       <c r="H44" t="n">
-        <v>67.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-26.78</v>
+        <v>26.72</v>
       </c>
       <c r="K44" t="n">
-        <v>9.890000000000001</v>
+        <v>-22.91</v>
       </c>
       <c r="L44" t="n">
-        <v>28.55</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05:56:26</t>
+          <t>06:06:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="F45" t="n">
-        <v>6.09</v>
+        <v>4.59</v>
       </c>
       <c r="G45" t="n">
-        <v>245</v>
+        <v>253.8</v>
       </c>
       <c r="H45" t="n">
-        <v>59.7</v>
+        <v>20.9</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>31.97</v>
+        <v>35.42</v>
       </c>
       <c r="K45" t="n">
-        <v>19.9</v>
+        <v>-3.47</v>
       </c>
       <c r="L45" t="n">
-        <v>37.66</v>
+        <v>35.59</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05:57:33</t>
+          <t>06:09:03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="F46" t="n">
-        <v>5.58</v>
+        <v>4.89</v>
       </c>
       <c r="G46" t="n">
-        <v>245.7</v>
+        <v>262.9</v>
       </c>
       <c r="H46" t="n">
-        <v>2.6</v>
+        <v>38.1</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-36.94</v>
+        <v>-14.85</v>
       </c>
       <c r="K46" t="n">
-        <v>7.24</v>
+        <v>-24.98</v>
       </c>
       <c r="L46" t="n">
-        <v>37.64</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:02:14</t>
+          <t>06:14:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="F47" t="n">
-        <v>6.09</v>
+        <v>4.2</v>
       </c>
       <c r="G47" t="n">
-        <v>266.8</v>
+        <v>248</v>
       </c>
       <c r="H47" t="n">
-        <v>41</v>
+        <v>37.2</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-40.15</v>
+        <v>-39.05</v>
       </c>
       <c r="K47" t="n">
-        <v>-27.02</v>
+        <v>-44.62</v>
       </c>
       <c r="L47" t="n">
-        <v>48.4</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:04:10</t>
+          <t>06:15:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="F48" t="n">
-        <v>4.3</v>
+        <v>1.88</v>
       </c>
       <c r="G48" t="n">
-        <v>236.4</v>
+        <v>231.1</v>
       </c>
       <c r="H48" t="n">
-        <v>39.4</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I48" t="n">
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-42.06</v>
+        <v>11.34</v>
       </c>
       <c r="K48" t="n">
-        <v>33.61</v>
+        <v>-58.6</v>
       </c>
       <c r="L48" t="n">
-        <v>53.83</v>
+        <v>59.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:05:52</t>
+          <t>06:18:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="F49" t="n">
-        <v>6.09</v>
+        <v>2.19</v>
       </c>
       <c r="G49" t="n">
-        <v>245.2</v>
+        <v>246</v>
       </c>
       <c r="H49" t="n">
-        <v>40.4</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-40.19</v>
+        <v>29.04</v>
       </c>
       <c r="K49" t="n">
-        <v>-28.91</v>
+        <v>-50.88</v>
       </c>
       <c r="L49" t="n">
-        <v>49.51</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:10:20</t>
+          <t>06:23:32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="F50" t="n">
-        <v>6.07</v>
+        <v>2.53</v>
       </c>
       <c r="G50" t="n">
-        <v>246.7</v>
+        <v>253.9</v>
       </c>
       <c r="H50" t="n">
-        <v>58.3</v>
+        <v>34.8</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-44.19</v>
+        <v>-93.09</v>
       </c>
       <c r="K50" t="n">
-        <v>55.88</v>
+        <v>14.34</v>
       </c>
       <c r="L50" t="n">
-        <v>71.23999999999999</v>
+        <v>94.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:12:34</t>
+          <t>06:25:58</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="F51" t="n">
-        <v>3.06</v>
+        <v>4.64</v>
       </c>
       <c r="G51" t="n">
-        <v>258.5</v>
+        <v>242.8</v>
       </c>
       <c r="H51" t="n">
-        <v>61.1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>77.39</v>
+        <v>-23.81</v>
       </c>
       <c r="K51" t="n">
-        <v>5.98</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>77.62</v>
+        <v>97.42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:15:01</t>
+          <t>06:27:39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="F52" t="n">
-        <v>5.84</v>
+        <v>6.09</v>
       </c>
       <c r="G52" t="n">
-        <v>248.3</v>
+        <v>249</v>
       </c>
       <c r="H52" t="n">
-        <v>47.9</v>
+        <v>37.7</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-30.15</v>
+        <v>-50.4</v>
       </c>
       <c r="K52" t="n">
-        <v>-84.36</v>
+        <v>-56.62</v>
       </c>
       <c r="L52" t="n">
-        <v>89.59</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:20:52</t>
+          <t>06:32:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="F53" t="n">
-        <v>5.8</v>
+        <v>4.86</v>
       </c>
       <c r="G53" t="n">
-        <v>250.6</v>
+        <v>242</v>
       </c>
       <c r="H53" t="n">
-        <v>61.1</v>
+        <v>35.6</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>123.64</v>
+        <v>27.58</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.26</v>
+        <v>-115.48</v>
       </c>
       <c r="L53" t="n">
-        <v>123.75</v>
+        <v>118.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:23:02</t>
+          <t>06:34:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="F54" t="n">
-        <v>5.25</v>
+        <v>2.05</v>
       </c>
       <c r="G54" t="n">
-        <v>260.4</v>
+        <v>245.8</v>
       </c>
       <c r="H54" t="n">
-        <v>37.8</v>
+        <v>19.3</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-86.40000000000001</v>
+        <v>144.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.25</v>
+        <v>7.36</v>
       </c>
       <c r="L54" t="n">
-        <v>86.8</v>
+        <v>144.61</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:24:40</t>
+          <t>06:35:28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="F55" t="n">
-        <v>5.03</v>
+        <v>4.8</v>
       </c>
       <c r="G55" t="n">
-        <v>252</v>
+        <v>249.6</v>
       </c>
       <c r="H55" t="n">
-        <v>32.8</v>
+        <v>27.4</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-102.15</v>
+        <v>-143.07</v>
       </c>
       <c r="K55" t="n">
-        <v>13.1</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>102.98</v>
+        <v>157.35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:30:30</t>
+          <t>06:39:32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="F56" t="n">
-        <v>4.62</v>
+        <v>4.05</v>
       </c>
       <c r="G56" t="n">
-        <v>248.8</v>
+        <v>260.1</v>
       </c>
       <c r="H56" t="n">
-        <v>75.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-128.53</v>
+        <v>125.58</v>
       </c>
       <c r="K56" t="n">
-        <v>-59.54</v>
+        <v>134.52</v>
       </c>
       <c r="L56" t="n">
-        <v>141.65</v>
+        <v>184.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:31:54</t>
+          <t>06:42:05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="F57" t="n">
-        <v>4.18</v>
+        <v>6.09</v>
       </c>
       <c r="G57" t="n">
-        <v>248.2</v>
+        <v>248.6</v>
       </c>
       <c r="H57" t="n">
-        <v>69.7</v>
+        <v>69.2</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>2.65</v>
+        <v>68.53</v>
       </c>
       <c r="K57" t="n">
-        <v>143.41</v>
+        <v>-159.43</v>
       </c>
       <c r="L57" t="n">
-        <v>143.43</v>
+        <v>173.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:34:09</t>
+          <t>06:43:49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.63</v>
+        <v>1.81</v>
       </c>
       <c r="F58" t="n">
-        <v>6.09</v>
+        <v>5.63</v>
       </c>
       <c r="G58" t="n">
-        <v>270.8</v>
+        <v>249.3</v>
       </c>
       <c r="H58" t="n">
-        <v>29.5</v>
+        <v>24.7</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-110.36</v>
+        <v>45.72</v>
       </c>
       <c r="K58" t="n">
-        <v>-39.24</v>
+        <v>163.47</v>
       </c>
       <c r="L58" t="n">
-        <v>117.13</v>
+        <v>169.74</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:42:35</t>
+          <t>06:53:13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="F59" t="n">
-        <v>6.03</v>
+        <v>6.09</v>
       </c>
       <c r="G59" t="n">
-        <v>250.5</v>
+        <v>247.5</v>
       </c>
       <c r="H59" t="n">
-        <v>64.2</v>
+        <v>51.2</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-15.48</v>
+        <v>-4.31</v>
       </c>
       <c r="K59" t="n">
-        <v>21.79</v>
+        <v>28.48</v>
       </c>
       <c r="L59" t="n">
-        <v>26.73</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:43:51</t>
+          <t>06:55:44</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="F60" t="n">
-        <v>6.09</v>
+        <v>5.69</v>
       </c>
       <c r="G60" t="n">
-        <v>244.3</v>
+        <v>258.8</v>
       </c>
       <c r="H60" t="n">
-        <v>88.7</v>
+        <v>37.7</v>
       </c>
       <c r="I60" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-22.56</v>
+        <v>-24.05</v>
       </c>
       <c r="K60" t="n">
-        <v>26.16</v>
+        <v>-23.21</v>
       </c>
       <c r="L60" t="n">
-        <v>34.55</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:45:26</t>
+          <t>06:57:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="F61" t="n">
-        <v>5.52</v>
+        <v>5.47</v>
       </c>
       <c r="G61" t="n">
-        <v>258</v>
+        <v>254.8</v>
       </c>
       <c r="H61" t="n">
-        <v>27.3</v>
+        <v>53.6</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-34.02</v>
+        <v>-21.7</v>
       </c>
       <c r="K61" t="n">
-        <v>2.24</v>
+        <v>27.03</v>
       </c>
       <c r="L61" t="n">
-        <v>34.1</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:50:01</t>
+          <t>07:01:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="F62" t="n">
-        <v>4.35</v>
+        <v>3.99</v>
       </c>
       <c r="G62" t="n">
-        <v>257</v>
+        <v>240.4</v>
       </c>
       <c r="H62" t="n">
-        <v>45.6</v>
+        <v>14.6</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>28.67</v>
+        <v>-58.56</v>
       </c>
       <c r="K62" t="n">
-        <v>44.28</v>
+        <v>8.57</v>
       </c>
       <c r="L62" t="n">
-        <v>52.75</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:52:35</t>
+          <t>07:02:30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="F63" t="n">
-        <v>3.52</v>
+        <v>2.08</v>
       </c>
       <c r="G63" t="n">
-        <v>255.7</v>
+        <v>249.4</v>
       </c>
       <c r="H63" t="n">
-        <v>29.5</v>
+        <v>51.6</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-41.32</v>
+        <v>-42.14</v>
       </c>
       <c r="K63" t="n">
-        <v>5.63</v>
+        <v>-7.26</v>
       </c>
       <c r="L63" t="n">
-        <v>41.7</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:54:27</t>
+          <t>07:04:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="F64" t="n">
-        <v>3.93</v>
+        <v>6.09</v>
       </c>
       <c r="G64" t="n">
-        <v>241.5</v>
+        <v>255.9</v>
       </c>
       <c r="H64" t="n">
-        <v>33.6</v>
+        <v>40.8</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-45.63</v>
+        <v>-49.75</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.38</v>
+        <v>-39.18</v>
       </c>
       <c r="L64" t="n">
-        <v>47.84</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:00:19</t>
+          <t>07:09:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="F65" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="G65" t="n">
-        <v>256.9</v>
+        <v>260.4</v>
       </c>
       <c r="H65" t="n">
-        <v>51.5</v>
+        <v>37.8</v>
       </c>
       <c r="I65" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>8.529999999999999</v>
+        <v>-62.66</v>
       </c>
       <c r="K65" t="n">
-        <v>-56.58</v>
+        <v>-5.13</v>
       </c>
       <c r="L65" t="n">
-        <v>57.22</v>
+        <v>62.87</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:03:00</t>
+          <t>07:11:18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="F66" t="n">
-        <v>5.17</v>
+        <v>5.35</v>
       </c>
       <c r="G66" t="n">
-        <v>258.7</v>
+        <v>244.6</v>
       </c>
       <c r="H66" t="n">
-        <v>83.8</v>
+        <v>11.5</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>44.37</v>
+        <v>-49.11</v>
       </c>
       <c r="K66" t="n">
-        <v>63.55</v>
+        <v>27.04</v>
       </c>
       <c r="L66" t="n">
-        <v>77.5</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:05:00</t>
+          <t>07:13:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="F67" t="n">
         <v>6.09</v>
       </c>
       <c r="G67" t="n">
-        <v>251.7</v>
+        <v>248.8</v>
       </c>
       <c r="H67" t="n">
-        <v>53.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>3.77</v>
+        <v>-78.41</v>
       </c>
       <c r="K67" t="n">
-        <v>66.56999999999999</v>
+        <v>-37.06</v>
       </c>
       <c r="L67" t="n">
-        <v>66.68000000000001</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:09:16</t>
+          <t>07:17:12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="F68" t="n">
-        <v>4.59</v>
+        <v>4.47</v>
       </c>
       <c r="G68" t="n">
-        <v>257.4</v>
+        <v>259.4</v>
       </c>
       <c r="H68" t="n">
-        <v>41.1</v>
+        <v>24.7</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>80.51000000000001</v>
+        <v>91.11</v>
       </c>
       <c r="K68" t="n">
-        <v>36.4</v>
+        <v>-59.69</v>
       </c>
       <c r="L68" t="n">
-        <v>88.36</v>
+        <v>108.92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:11:11</t>
+          <t>07:18:35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="F69" t="n">
-        <v>6.09</v>
+        <v>5.35</v>
       </c>
       <c r="G69" t="n">
-        <v>239.3</v>
+        <v>243.3</v>
       </c>
       <c r="H69" t="n">
-        <v>30</v>
+        <v>37.3</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>144.24</v>
+        <v>-30.65</v>
       </c>
       <c r="K69" t="n">
-        <v>16.59</v>
+        <v>-43.35</v>
       </c>
       <c r="L69" t="n">
-        <v>145.19</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:12:53</t>
+          <t>07:21:07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="F70" t="n">
         <v>6.09</v>
       </c>
       <c r="G70" t="n">
-        <v>250.7</v>
+        <v>257.4</v>
       </c>
       <c r="H70" t="n">
-        <v>42.8</v>
+        <v>51.4</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-144.24</v>
+        <v>-14.62</v>
       </c>
       <c r="K70" t="n">
-        <v>0.78</v>
+        <v>-140.88</v>
       </c>
       <c r="L70" t="n">
-        <v>144.24</v>
+        <v>141.64</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:17:19</t>
+          <t>07:25:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="F71" t="n">
-        <v>5.95</v>
+        <v>3.18</v>
       </c>
       <c r="G71" t="n">
-        <v>254.7</v>
+        <v>267</v>
       </c>
       <c r="H71" t="n">
-        <v>70.2</v>
+        <v>62.8</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>44.33</v>
+        <v>154.15</v>
       </c>
       <c r="K71" t="n">
-        <v>-222.43</v>
+        <v>-104.7</v>
       </c>
       <c r="L71" t="n">
-        <v>226.81</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:18:04</t>
+          <t>07:27:44</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="F72" t="n">
         <v>6.09</v>
       </c>
       <c r="G72" t="n">
-        <v>253.4</v>
+        <v>240</v>
       </c>
       <c r="H72" t="n">
-        <v>57.2</v>
+        <v>42.9</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>24.7</v>
+        <v>92.66</v>
       </c>
       <c r="K72" t="n">
-        <v>-131.33</v>
+        <v>-193.29</v>
       </c>
       <c r="L72" t="n">
-        <v>133.63</v>
+        <v>214.35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:19:50</t>
+          <t>07:29:29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="F73" t="n">
         <v>6.09</v>
       </c>
       <c r="G73" t="n">
-        <v>249.8</v>
+        <v>249.7</v>
       </c>
       <c r="H73" t="n">
-        <v>25.9</v>
+        <v>20.7</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-22.76</v>
+        <v>173.7</v>
       </c>
       <c r="K73" t="n">
-        <v>173.77</v>
+        <v>13.52</v>
       </c>
       <c r="L73" t="n">
-        <v>175.25</v>
+        <v>174.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:29:56</t>
+          <t>07:38:21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="F74" t="n">
-        <v>6.09</v>
+        <v>4.97</v>
       </c>
       <c r="G74" t="n">
-        <v>246.9</v>
+        <v>237.2</v>
       </c>
       <c r="H74" t="n">
-        <v>65.59999999999999</v>
+        <v>22.9</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.05</v>
+        <v>23.7</v>
       </c>
       <c r="K74" t="n">
-        <v>30.24</v>
+        <v>21.35</v>
       </c>
       <c r="L74" t="n">
-        <v>30.51</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:31:22</t>
+          <t>07:39:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="F75" t="n">
-        <v>5.26</v>
+        <v>6.09</v>
       </c>
       <c r="G75" t="n">
-        <v>251.1</v>
+        <v>227.9</v>
       </c>
       <c r="H75" t="n">
-        <v>49</v>
+        <v>33.8</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>1.28</v>
+        <v>29.13</v>
       </c>
       <c r="K75" t="n">
-        <v>33.31</v>
+        <v>-0.19</v>
       </c>
       <c r="L75" t="n">
-        <v>33.34</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:32:22</t>
+          <t>07:40:43</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="F76" t="n">
-        <v>4.84</v>
+        <v>5.62</v>
       </c>
       <c r="G76" t="n">
-        <v>242.8</v>
+        <v>245.4</v>
       </c>
       <c r="H76" t="n">
-        <v>51.5</v>
+        <v>4.5</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-29.03</v>
+        <v>16.65</v>
       </c>
       <c r="K76" t="n">
-        <v>8.470000000000001</v>
+        <v>-35.92</v>
       </c>
       <c r="L76" t="n">
-        <v>30.24</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:38:05</t>
+          <t>07:44:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="F77" t="n">
-        <v>4.48</v>
+        <v>6.09</v>
       </c>
       <c r="G77" t="n">
-        <v>252.5</v>
+        <v>247.3</v>
       </c>
       <c r="H77" t="n">
-        <v>34.1</v>
+        <v>35.8</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-12.1</v>
+        <v>44.14</v>
       </c>
       <c r="K77" t="n">
-        <v>12.68</v>
+        <v>-43.45</v>
       </c>
       <c r="L77" t="n">
-        <v>17.53</v>
+        <v>61.94</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:40:01</t>
+          <t>07:45:54</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="F78" t="n">
-        <v>5.18</v>
+        <v>4.45</v>
       </c>
       <c r="G78" t="n">
-        <v>240.5</v>
+        <v>249</v>
       </c>
       <c r="H78" t="n">
-        <v>35.8</v>
+        <v>63.9</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-31.27</v>
+        <v>42.64</v>
       </c>
       <c r="K78" t="n">
-        <v>-30.57</v>
+        <v>-46.68</v>
       </c>
       <c r="L78" t="n">
-        <v>43.72</v>
+        <v>63.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:41:06</t>
+          <t>07:48:22</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="F79" t="n">
-        <v>4.24</v>
+        <v>6.09</v>
       </c>
       <c r="G79" t="n">
-        <v>253.4</v>
+        <v>257.7</v>
       </c>
       <c r="H79" t="n">
-        <v>23.5</v>
+        <v>28.3</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.34</v>
+        <v>-54.65</v>
       </c>
       <c r="K79" t="n">
-        <v>-25.13</v>
+        <v>-24.93</v>
       </c>
       <c r="L79" t="n">
-        <v>60.78</v>
+        <v>60.07</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:45:43</t>
+          <t>07:52:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="F80" t="n">
-        <v>6.09</v>
+        <v>4.79</v>
       </c>
       <c r="G80" t="n">
-        <v>269.9</v>
+        <v>246.6</v>
       </c>
       <c r="H80" t="n">
-        <v>61.2</v>
+        <v>20.1</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>27.47</v>
+        <v>-39.32</v>
       </c>
       <c r="K80" t="n">
-        <v>-82.26000000000001</v>
+        <v>66.86</v>
       </c>
       <c r="L80" t="n">
-        <v>86.73</v>
+        <v>77.56999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:48:08</t>
+          <t>07:54:51</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="F81" t="n">
         <v>6.09</v>
       </c>
       <c r="G81" t="n">
-        <v>265.4</v>
+        <v>254.4</v>
       </c>
       <c r="H81" t="n">
-        <v>24</v>
+        <v>60.6</v>
       </c>
       <c r="I81" t="n">
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>58.53</v>
+        <v>59.19</v>
       </c>
       <c r="K81" t="n">
-        <v>-11.06</v>
+        <v>-63.22</v>
       </c>
       <c r="L81" t="n">
-        <v>59.57</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:49:25</t>
+          <t>07:56:56</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="F82" t="n">
-        <v>3.23</v>
+        <v>6.09</v>
       </c>
       <c r="G82" t="n">
-        <v>260.1</v>
+        <v>256.7</v>
       </c>
       <c r="H82" t="n">
-        <v>41.4</v>
+        <v>46.6</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>60</v>
+        <v>-30.82</v>
       </c>
       <c r="K82" t="n">
-        <v>-80.5</v>
+        <v>95.89</v>
       </c>
       <c r="L82" t="n">
-        <v>100.4</v>
+        <v>100.72</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:53:06</t>
+          <t>08:01:44</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="F83" t="n">
-        <v>5.92</v>
+        <v>6.09</v>
       </c>
       <c r="G83" t="n">
-        <v>250.4</v>
+        <v>251.8</v>
       </c>
       <c r="H83" t="n">
-        <v>48.8</v>
+        <v>11.4</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.51</v>
+        <v>-43.11</v>
       </c>
       <c r="K83" t="n">
-        <v>180.57</v>
+        <v>149.63</v>
       </c>
       <c r="L83" t="n">
-        <v>180.57</v>
+        <v>155.71</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:55:03</t>
+          <t>08:02:43</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="F84" t="n">
-        <v>6.09</v>
+        <v>2.45</v>
       </c>
       <c r="G84" t="n">
-        <v>248.2</v>
+        <v>254.4</v>
       </c>
       <c r="H84" t="n">
-        <v>38</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I84" t="n">
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-142.66</v>
+        <v>-94.23999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>64.91</v>
+        <v>-111.01</v>
       </c>
       <c r="L84" t="n">
-        <v>156.73</v>
+        <v>145.62</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:56:48</t>
+          <t>08:04:42</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="F85" t="n">
         <v>6.09</v>
       </c>
       <c r="G85" t="n">
-        <v>237.9</v>
+        <v>241.5</v>
       </c>
       <c r="H85" t="n">
-        <v>17.4</v>
+        <v>26</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>64.05</v>
+        <v>106.92</v>
       </c>
       <c r="K85" t="n">
-        <v>66.62</v>
+        <v>106.65</v>
       </c>
       <c r="L85" t="n">
-        <v>92.41</v>
+        <v>151.01</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:00:57</t>
+          <t>08:10:10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="F86" t="n">
-        <v>6.09</v>
+        <v>5.7</v>
       </c>
       <c r="G86" t="n">
-        <v>241.7</v>
+        <v>245.2</v>
       </c>
       <c r="H86" t="n">
-        <v>80.8</v>
+        <v>29.8</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-111.01</v>
+        <v>-173.95</v>
       </c>
       <c r="K86" t="n">
-        <v>-122.48</v>
+        <v>-72.47</v>
       </c>
       <c r="L86" t="n">
-        <v>165.3</v>
+        <v>188.44</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:01:58</t>
+          <t>08:11:59</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="F87" t="n">
-        <v>5.33</v>
+        <v>5.99</v>
       </c>
       <c r="G87" t="n">
-        <v>249.7</v>
+        <v>266.2</v>
       </c>
       <c r="H87" t="n">
-        <v>24.2</v>
+        <v>18.2</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-140.8</v>
+        <v>146.49</v>
       </c>
       <c r="K87" t="n">
-        <v>101.15</v>
+        <v>-58.77</v>
       </c>
       <c r="L87" t="n">
-        <v>173.37</v>
+        <v>157.84</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:04:19</t>
+          <t>08:13:43</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="F88" t="n">
         <v>6.09</v>
       </c>
       <c r="G88" t="n">
-        <v>265</v>
+        <v>248.5</v>
       </c>
       <c r="H88" t="n">
-        <v>33.5</v>
+        <v>46.8</v>
       </c>
       <c r="I88" t="n">
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-127.38</v>
+        <v>147</v>
       </c>
       <c r="K88" t="n">
-        <v>119.78</v>
+        <v>-62.82</v>
       </c>
       <c r="L88" t="n">
-        <v>174.85</v>
+        <v>159.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-29.xlsx
+++ b/output/2024-06-29.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>5.82</v>
+        <v>5.31</v>
       </c>
       <c r="K14" t="n">
-        <v>54.39</v>
+        <v>49.64</v>
       </c>
       <c r="L14" t="n">
-        <v>54.7</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>37.4</v>
+        <v>37.19</v>
       </c>
       <c r="K15" t="n">
         <v>0.55</v>
       </c>
       <c r="L15" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-24.84</v>
+        <v>-26.3</v>
       </c>
       <c r="K16" t="n">
-        <v>20.73</v>
+        <v>21.95</v>
       </c>
       <c r="L16" t="n">
-        <v>32.35</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-50.18</v>
+        <v>-50.35</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.53</v>
+        <v>-3.54</v>
       </c>
       <c r="L17" t="n">
-        <v>50.31</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-37.54</v>
+        <v>-41.01</v>
       </c>
       <c r="K18" t="n">
-        <v>-29.16</v>
+        <v>-31.86</v>
       </c>
       <c r="L18" t="n">
-        <v>47.54</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-21</v>
+        <v>-20.89</v>
       </c>
       <c r="K19" t="n">
-        <v>-61.09</v>
+        <v>-60.77</v>
       </c>
       <c r="L19" t="n">
-        <v>64.59999999999999</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-19.44</v>
+        <v>-21.39</v>
       </c>
       <c r="K20" t="n">
-        <v>63.78</v>
+        <v>70.17</v>
       </c>
       <c r="L20" t="n">
-        <v>66.68000000000001</v>
+        <v>73.36</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-50.58</v>
+        <v>-58.73</v>
       </c>
       <c r="K21" t="n">
-        <v>-19.28</v>
+        <v>-22.38</v>
       </c>
       <c r="L21" t="n">
-        <v>54.13</v>
+        <v>62.85</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>93.23999999999999</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>4.69</v>
+        <v>4.82</v>
       </c>
       <c r="L22" t="n">
-        <v>93.36</v>
+        <v>95.91</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>93.89</v>
+        <v>109.47</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.08</v>
+        <v>-5.93</v>
       </c>
       <c r="L23" t="n">
-        <v>94.03</v>
+        <v>109.63</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-60.2</v>
+        <v>-68.25</v>
       </c>
       <c r="K24" t="n">
-        <v>-75.89</v>
+        <v>-86.04000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>96.87</v>
+        <v>109.82</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-39.41</v>
+        <v>-48.33</v>
       </c>
       <c r="K25" t="n">
-        <v>19.57</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>44</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-151.95</v>
+        <v>-171.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-37.67</v>
+        <v>-42.45</v>
       </c>
       <c r="L26" t="n">
-        <v>156.55</v>
+        <v>176.38</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-160.9</v>
+        <v>-182.06</v>
       </c>
       <c r="K27" t="n">
-        <v>-35.08</v>
+        <v>-39.7</v>
       </c>
       <c r="L27" t="n">
-        <v>164.68</v>
+        <v>186.34</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>121.64</v>
+        <v>135.31</v>
       </c>
       <c r="K28" t="n">
-        <v>134.26</v>
+        <v>149.35</v>
       </c>
       <c r="L28" t="n">
-        <v>181.16</v>
+        <v>201.53</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.43</v>
+        <v>-13.69</v>
       </c>
       <c r="K29" t="n">
-        <v>33.89</v>
+        <v>34.55</v>
       </c>
       <c r="L29" t="n">
-        <v>36.45</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.76</v>
+        <v>-4.28</v>
       </c>
       <c r="K30" t="n">
-        <v>60.63</v>
+        <v>54.5</v>
       </c>
       <c r="L30" t="n">
-        <v>60.81</v>
+        <v>54.67</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-38.85</v>
+        <v>-37.12</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.63</v>
+        <v>-28.31</v>
       </c>
       <c r="L31" t="n">
-        <v>48.86</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.53</v>
+        <v>-3.43</v>
       </c>
       <c r="K32" t="n">
-        <v>59.82</v>
+        <v>58.07</v>
       </c>
       <c r="L32" t="n">
-        <v>59.92</v>
+        <v>58.17</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>59.16</v>
+        <v>57.13</v>
       </c>
       <c r="K33" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="L33" t="n">
-        <v>59.23</v>
+        <v>57.19</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-30.28</v>
+        <v>-28.74</v>
       </c>
       <c r="K34" t="n">
-        <v>70.39</v>
+        <v>66.81</v>
       </c>
       <c r="L34" t="n">
-        <v>76.63</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-70.97</v>
+        <v>-74.63</v>
       </c>
       <c r="K35" t="n">
-        <v>46.17</v>
+        <v>48.55</v>
       </c>
       <c r="L35" t="n">
-        <v>84.66</v>
+        <v>89.03</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>10.95</v>
+        <v>12.5</v>
       </c>
       <c r="K36" t="n">
-        <v>-8.039999999999999</v>
+        <v>-9.18</v>
       </c>
       <c r="L36" t="n">
-        <v>13.58</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-72.98</v>
+        <v>-78.72</v>
       </c>
       <c r="K37" t="n">
-        <v>-19.73</v>
+        <v>-21.28</v>
       </c>
       <c r="L37" t="n">
-        <v>75.59999999999999</v>
+        <v>81.54000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-49.05</v>
+        <v>-53.6</v>
       </c>
       <c r="K38" t="n">
-        <v>-86.03</v>
+        <v>-94.01000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>99.02</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-59.26</v>
+        <v>-67.36</v>
       </c>
       <c r="K39" t="n">
-        <v>93.58</v>
+        <v>106.37</v>
       </c>
       <c r="L39" t="n">
-        <v>110.77</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>69.67</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="L40" t="n">
-        <v>69.68000000000001</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-27.56</v>
+        <v>-31.93</v>
       </c>
       <c r="K41" t="n">
-        <v>-144.37</v>
+        <v>-167.26</v>
       </c>
       <c r="L41" t="n">
-        <v>146.97</v>
+        <v>170.28</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-60.87</v>
+        <v>-70.15000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>137.75</v>
+        <v>158.74</v>
       </c>
       <c r="L42" t="n">
-        <v>150.6</v>
+        <v>173.55</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>7.73</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>234.94</v>
+        <v>249.32</v>
       </c>
       <c r="L43" t="n">
-        <v>235.07</v>
+        <v>249.45</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-27.33</v>
+        <v>-27.06</v>
       </c>
       <c r="K44" t="n">
-        <v>-28.35</v>
+        <v>-28.06</v>
       </c>
       <c r="L44" t="n">
-        <v>39.38</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="K45" t="n">
-        <v>50.98</v>
+        <v>47.7</v>
       </c>
       <c r="L45" t="n">
-        <v>51</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-42.78</v>
+        <v>-39.39</v>
       </c>
       <c r="K46" t="n">
-        <v>-49.18</v>
+        <v>-45.29</v>
       </c>
       <c r="L46" t="n">
-        <v>65.18000000000001</v>
+        <v>60.02</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>49.82</v>
+        <v>48.31</v>
       </c>
       <c r="K47" t="n">
-        <v>55.31</v>
+        <v>53.63</v>
       </c>
       <c r="L47" t="n">
-        <v>74.44</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-70.81999999999999</v>
+        <v>-67.83</v>
       </c>
       <c r="K48" t="n">
-        <v>-22.68</v>
+        <v>-21.72</v>
       </c>
       <c r="L48" t="n">
-        <v>74.36</v>
+        <v>71.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>51.49</v>
+        <v>54.89</v>
       </c>
       <c r="K49" t="n">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="L49" t="n">
-        <v>51.56</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>21.24</v>
+        <v>21.15</v>
       </c>
       <c r="K50" t="n">
-        <v>110.21</v>
+        <v>109.71</v>
       </c>
       <c r="L50" t="n">
-        <v>112.24</v>
+        <v>111.73</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>59.94</v>
+        <v>65.73</v>
       </c>
       <c r="K51" t="n">
-        <v>-52.94</v>
+        <v>-58.05</v>
       </c>
       <c r="L51" t="n">
-        <v>79.97</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-23.81</v>
+        <v>-24.58</v>
       </c>
       <c r="K52" t="n">
-        <v>-94.54000000000001</v>
+        <v>-97.59</v>
       </c>
       <c r="L52" t="n">
-        <v>97.48999999999999</v>
+        <v>100.64</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>77.83</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-22.64</v>
+        <v>-27.39</v>
       </c>
       <c r="L53" t="n">
-        <v>81.06</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>96.01000000000001</v>
+        <v>101.23</v>
       </c>
       <c r="K54" t="n">
-        <v>88.06</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>130.28</v>
+        <v>137.37</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-93.64</v>
+        <v>-104.17</v>
       </c>
       <c r="K55" t="n">
-        <v>-31.21</v>
+        <v>-34.72</v>
       </c>
       <c r="L55" t="n">
-        <v>98.70999999999999</v>
+        <v>109.81</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-121.61</v>
+        <v>-142.95</v>
       </c>
       <c r="K56" t="n">
-        <v>-94.84999999999999</v>
+        <v>-111.5</v>
       </c>
       <c r="L56" t="n">
-        <v>154.22</v>
+        <v>181.29</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-188.39</v>
+        <v>-203.96</v>
       </c>
       <c r="K57" t="n">
-        <v>-30.95</v>
+        <v>-33.51</v>
       </c>
       <c r="L57" t="n">
-        <v>190.91</v>
+        <v>206.7</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-138.99</v>
+        <v>-163.91</v>
       </c>
       <c r="K58" t="n">
-        <v>-14.29</v>
+        <v>-16.85</v>
       </c>
       <c r="L58" t="n">
-        <v>139.72</v>
+        <v>164.78</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-39.14</v>
+        <v>-37.29</v>
       </c>
       <c r="K59" t="n">
-        <v>23.72</v>
+        <v>22.6</v>
       </c>
       <c r="L59" t="n">
-        <v>45.77</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>37.24</v>
+        <v>38.28</v>
       </c>
       <c r="K60" t="n">
-        <v>4.32</v>
+        <v>4.45</v>
       </c>
       <c r="L60" t="n">
-        <v>37.49</v>
+        <v>38.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-29.39</v>
+        <v>-27.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-58.78</v>
+        <v>-54.59</v>
       </c>
       <c r="L61" t="n">
-        <v>65.72</v>
+        <v>61.03</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-55.9</v>
+        <v>-54.35</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L62" t="n">
-        <v>55.9</v>
+        <v>54.35</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>61.07</v>
+        <v>59.97</v>
       </c>
       <c r="K63" t="n">
-        <v>6.95</v>
+        <v>6.82</v>
       </c>
       <c r="L63" t="n">
-        <v>61.46</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-31.73</v>
+        <v>-32.34</v>
       </c>
       <c r="K64" t="n">
-        <v>-34.87</v>
+        <v>-35.55</v>
       </c>
       <c r="L64" t="n">
-        <v>47.15</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-20.45</v>
+        <v>-23.8</v>
       </c>
       <c r="K65" t="n">
-        <v>55.86</v>
+        <v>65.03</v>
       </c>
       <c r="L65" t="n">
-        <v>59.49</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-88.68000000000001</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>76.23</v>
+        <v>75.64</v>
       </c>
       <c r="L66" t="n">
-        <v>116.95</v>
+        <v>116.03</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>54.28</v>
+        <v>59.37</v>
       </c>
       <c r="K67" t="n">
-        <v>-49.91</v>
+        <v>-54.59</v>
       </c>
       <c r="L67" t="n">
-        <v>73.73</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-41.8</v>
+        <v>-41.68</v>
       </c>
       <c r="K68" t="n">
-        <v>-174.8</v>
+        <v>-174.3</v>
       </c>
       <c r="L68" t="n">
-        <v>179.72</v>
+        <v>179.21</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>41.42</v>
+        <v>44.94</v>
       </c>
       <c r="K69" t="n">
-        <v>-97.23</v>
+        <v>-105.49</v>
       </c>
       <c r="L69" t="n">
-        <v>105.68</v>
+        <v>114.66</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>50.08</v>
+        <v>56.35</v>
       </c>
       <c r="K70" t="n">
-        <v>77.48999999999999</v>
+        <v>87.19</v>
       </c>
       <c r="L70" t="n">
-        <v>92.26000000000001</v>
+        <v>103.82</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>143.17</v>
+        <v>164.03</v>
       </c>
       <c r="K71" t="n">
-        <v>39.34</v>
+        <v>45.08</v>
       </c>
       <c r="L71" t="n">
-        <v>148.47</v>
+        <v>170.11</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-106.11</v>
+        <v>-119.22</v>
       </c>
       <c r="K72" t="n">
-        <v>-137.46</v>
+        <v>-154.44</v>
       </c>
       <c r="L72" t="n">
-        <v>173.65</v>
+        <v>195.11</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-169.85</v>
+        <v>-188.46</v>
       </c>
       <c r="K73" t="n">
-        <v>18.3</v>
+        <v>20.31</v>
       </c>
       <c r="L73" t="n">
-        <v>170.83</v>
+        <v>189.55</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>26.35</v>
+        <v>25.9</v>
       </c>
       <c r="K74" t="n">
-        <v>-32.78</v>
+        <v>-32.22</v>
       </c>
       <c r="L74" t="n">
-        <v>42.05</v>
+        <v>41.33</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-38.73</v>
+        <v>-39.45</v>
       </c>
       <c r="K75" t="n">
-        <v>6.91</v>
+        <v>7.04</v>
       </c>
       <c r="L75" t="n">
-        <v>39.35</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>11.81</v>
+        <v>13</v>
       </c>
       <c r="K76" t="n">
-        <v>-27.14</v>
+        <v>-29.86</v>
       </c>
       <c r="L76" t="n">
-        <v>29.6</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-39.94</v>
+        <v>-42.35</v>
       </c>
       <c r="K77" t="n">
-        <v>-13.38</v>
+        <v>-14.19</v>
       </c>
       <c r="L77" t="n">
-        <v>42.12</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>35.38</v>
+        <v>35.43</v>
       </c>
       <c r="K78" t="n">
-        <v>41.28</v>
+        <v>41.34</v>
       </c>
       <c r="L78" t="n">
-        <v>54.37</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>19.42</v>
+        <v>19.48</v>
       </c>
       <c r="K79" t="n">
-        <v>-54.1</v>
+        <v>-54.26</v>
       </c>
       <c r="L79" t="n">
-        <v>57.49</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>42.49</v>
+        <v>46.29</v>
       </c>
       <c r="K80" t="n">
-        <v>-63.03</v>
+        <v>-68.67</v>
       </c>
       <c r="L80" t="n">
-        <v>76.01000000000001</v>
+        <v>82.81</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-26.95</v>
+        <v>-28.56</v>
       </c>
       <c r="K81" t="n">
-        <v>-81.98999999999999</v>
+        <v>-86.89</v>
       </c>
       <c r="L81" t="n">
-        <v>86.31</v>
+        <v>91.47</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-98.25</v>
+        <v>-100.9</v>
       </c>
       <c r="K82" t="n">
-        <v>-45.97</v>
+        <v>-47.21</v>
       </c>
       <c r="L82" t="n">
-        <v>108.47</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-57.96</v>
+        <v>-62.49</v>
       </c>
       <c r="K83" t="n">
-        <v>100.24</v>
+        <v>108.07</v>
       </c>
       <c r="L83" t="n">
-        <v>115.79</v>
+        <v>124.83</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-69.66</v>
+        <v>-77.73</v>
       </c>
       <c r="K84" t="n">
-        <v>-69.61</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>98.48</v>
+        <v>109.89</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-100.53</v>
+        <v>-114.18</v>
       </c>
       <c r="K85" t="n">
-        <v>-30.29</v>
+        <v>-34.4</v>
       </c>
       <c r="L85" t="n">
-        <v>104.99</v>
+        <v>119.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-89.65000000000001</v>
+        <v>-101.34</v>
       </c>
       <c r="K86" t="n">
-        <v>157.79</v>
+        <v>178.37</v>
       </c>
       <c r="L86" t="n">
-        <v>181.48</v>
+        <v>205.15</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-96.15000000000001</v>
+        <v>-119.47</v>
       </c>
       <c r="K87" t="n">
-        <v>64.97</v>
+        <v>80.73</v>
       </c>
       <c r="L87" t="n">
-        <v>116.04</v>
+        <v>144.18</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>88.64</v>
+        <v>105.73</v>
       </c>
       <c r="K88" t="n">
-        <v>84.47</v>
+        <v>100.75</v>
       </c>
       <c r="L88" t="n">
-        <v>122.44</v>
+        <v>146.05</v>
       </c>
     </row>
   </sheetData>
